--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131273413</v>
+        <v>131273397</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546491</v>
+        <v>546296</v>
       </c>
       <c r="R2" t="n">
-        <v>6998962</v>
+        <v>6999259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131273422</v>
+        <v>131275180</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546111</v>
+        <v>546406</v>
       </c>
       <c r="R3" t="n">
-        <v>6999297</v>
+        <v>6999201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,17 +904,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275215</v>
+        <v>131275187</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546164</v>
+        <v>546202</v>
       </c>
       <c r="R4" t="n">
-        <v>6999199</v>
+        <v>6999223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,17 +1030,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131273397</v>
+        <v>131273413</v>
       </c>
       <c r="B5" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546296</v>
+        <v>546491</v>
       </c>
       <c r="R5" t="n">
-        <v>6999259</v>
+        <v>6998962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,11 +1134,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1146,22 +1151,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275180</v>
+        <v>131273422</v>
       </c>
       <c r="B6" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546406</v>
+        <v>546111</v>
       </c>
       <c r="R6" t="n">
-        <v>6999201</v>
+        <v>6999297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131275187</v>
+        <v>131275215</v>
       </c>
       <c r="B7" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546202</v>
+        <v>546164</v>
       </c>
       <c r="R7" t="n">
-        <v>6999223</v>
+        <v>6999199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131276476</v>
+        <v>131275145</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546050</v>
+        <v>546148</v>
       </c>
       <c r="R9" t="n">
-        <v>6999453</v>
+        <v>6999078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275145</v>
+        <v>131275160</v>
       </c>
       <c r="B10" t="n">
         <v>57884</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546148</v>
+        <v>546104</v>
       </c>
       <c r="R10" t="n">
-        <v>6999078</v>
+        <v>6999263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131275160</v>
+        <v>131276476</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546104</v>
+        <v>546050</v>
       </c>
       <c r="R11" t="n">
-        <v>6999263</v>
+        <v>6999453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273421</v>
+        <v>131273375</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,26 +1967,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546167</v>
+        <v>546088</v>
       </c>
       <c r="R12" t="n">
-        <v>6999264</v>
+        <v>6999337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,13 +2037,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2057,9 +2066,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2077,10 +2091,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131273391</v>
+        <v>131275142</v>
       </c>
       <c r="B13" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,28 +2102,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2119,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546139</v>
       </c>
       <c r="R13" t="n">
-        <v>6998921</v>
+        <v>6999063</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,13 +2172,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2174,22 +2193,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,10 +2221,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131275185</v>
+        <v>131275131</v>
       </c>
       <c r="B14" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2218,26 +2232,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2245,10 +2264,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546230</v>
+        <v>546445</v>
       </c>
       <c r="R14" t="n">
-        <v>6999202</v>
+        <v>6998989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,7 +2304,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,7 +2313,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2305,22 +2323,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2338,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131273407</v>
+        <v>131275156</v>
       </c>
       <c r="B15" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,28 +2362,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2380,10 +2394,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546227</v>
+        <v>546115</v>
       </c>
       <c r="R15" t="n">
-        <v>6999437</v>
+        <v>6999245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2420,7 +2434,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,7 +2443,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2440,22 +2453,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2473,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131276484</v>
+        <v>131273368</v>
       </c>
       <c r="B16" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,26 +2492,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2511,10 +2524,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546500</v>
+        <v>546097</v>
       </c>
       <c r="R16" t="n">
-        <v>6998983</v>
+        <v>6999266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2549,13 +2562,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2566,22 +2583,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2599,10 +2611,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131275184</v>
+        <v>131275150</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,26 +2622,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2637,10 +2654,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546300</v>
+        <v>546123</v>
       </c>
       <c r="R17" t="n">
-        <v>6999066</v>
+        <v>6999192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2675,19 +2692,38 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2705,10 +2741,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131275192</v>
+        <v>131275153</v>
       </c>
       <c r="B18" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2716,26 +2752,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2743,10 +2784,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546168</v>
+        <v>546126</v>
       </c>
       <c r="R18" t="n">
-        <v>6999218</v>
+        <v>6999216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2781,13 +2822,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2798,22 +2843,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2831,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131273396</v>
+        <v>131275163</v>
       </c>
       <c r="B19" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2842,28 +2882,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2873,10 +2914,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546277</v>
+        <v>546096</v>
       </c>
       <c r="R19" t="n">
-        <v>6999264</v>
+        <v>6999292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2913,7 +2954,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,7 +2963,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2933,27 +2973,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2971,10 +3001,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131275142</v>
+        <v>131273421</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,31 +3012,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3014,10 +3039,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546139</v>
+        <v>546167</v>
       </c>
       <c r="R20" t="n">
-        <v>6999063</v>
+        <v>6999264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3052,17 +3077,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3101,10 +3122,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131273375</v>
+        <v>131273391</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3112,29 +3133,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3144,10 +3164,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546088</v>
+        <v>546459</v>
       </c>
       <c r="R21" t="n">
-        <v>6999337</v>
+        <v>6998921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3182,17 +3202,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3203,22 +3219,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3236,10 +3252,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131275131</v>
+        <v>131275185</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3247,31 +3263,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3279,10 +3290,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546445</v>
+        <v>546230</v>
       </c>
       <c r="R22" t="n">
-        <v>6998989</v>
+        <v>6999202</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,7 +3330,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3328,6 +3339,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3338,17 +3350,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3366,10 +3383,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131275156</v>
+        <v>131273407</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3377,29 +3394,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3409,10 +3425,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546115</v>
+        <v>546227</v>
       </c>
       <c r="R23" t="n">
-        <v>6999245</v>
+        <v>6999437</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3449,7 +3465,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3458,6 +3474,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3468,17 +3485,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3496,10 +3518,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131273368</v>
+        <v>131276484</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3507,31 +3529,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3539,10 +3556,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546097</v>
+        <v>546500</v>
       </c>
       <c r="R24" t="n">
-        <v>6999266</v>
+        <v>6998983</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3577,17 +3594,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3598,17 +3611,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3626,10 +3644,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131275150</v>
+        <v>131275184</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3637,31 +3655,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3669,10 +3682,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546123</v>
+        <v>546300</v>
       </c>
       <c r="R25" t="n">
-        <v>6999192</v>
+        <v>6999066</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3707,38 +3720,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3756,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131275153</v>
+        <v>131275192</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,31 +3761,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3799,10 +3788,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546126</v>
+        <v>546168</v>
       </c>
       <c r="R26" t="n">
-        <v>6999216</v>
+        <v>6999218</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3837,17 +3826,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3858,17 +3843,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3886,10 +3876,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131275163</v>
+        <v>131273396</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3897,29 +3887,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3929,10 +3918,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546096</v>
+        <v>546277</v>
       </c>
       <c r="R27" t="n">
-        <v>6999292</v>
+        <v>6999264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3969,7 +3958,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3978,6 +3967,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3988,17 +3978,27 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131275176</v>
+        <v>131275206</v>
       </c>
       <c r="B28" t="n">
-        <v>75335</v>
+        <v>78258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1460</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546399</v>
+        <v>546408</v>
       </c>
       <c r="R28" t="n">
-        <v>6998994</v>
+        <v>6999129</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275175</v>
+        <v>131275176</v>
       </c>
       <c r="B29" t="n">
-        <v>75335</v>
+        <v>75336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546372</v>
+        <v>546399</v>
       </c>
       <c r="R29" t="n">
-        <v>6998999</v>
+        <v>6998994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark av gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4273,10 +4268,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275191</v>
+        <v>131275175</v>
       </c>
       <c r="B30" t="n">
-        <v>80350</v>
+        <v>75336</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4284,21 +4279,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4311,10 +4306,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546174</v>
+        <v>546372</v>
       </c>
       <c r="R30" t="n">
-        <v>6999215</v>
+        <v>6998999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4351,7 +4346,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På bark av gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,12 +4366,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4386,7 +4381,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4404,10 +4399,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275201</v>
+        <v>131275191</v>
       </c>
       <c r="B31" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546222</v>
+        <v>546174</v>
       </c>
       <c r="R31" t="n">
-        <v>6999418</v>
+        <v>6999215</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4480,6 +4475,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275178</v>
+        <v>131275201</v>
       </c>
       <c r="B32" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546403</v>
+        <v>546222</v>
       </c>
       <c r="R32" t="n">
-        <v>6999213</v>
+        <v>6999418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4619,6 +4619,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4636,10 +4656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275206</v>
+        <v>131275178</v>
       </c>
       <c r="B33" t="n">
-        <v>78257</v>
+        <v>80351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,21 +4667,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4674,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546408</v>
+        <v>546403</v>
       </c>
       <c r="R33" t="n">
-        <v>6999129</v>
+        <v>6999213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,26 +4745,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4765,7 +4765,7 @@
         <v>131276490</v>
       </c>
       <c r="B34" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>131276489</v>
       </c>
       <c r="B35" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>131275193</v>
       </c>
       <c r="B36" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>131273389</v>
       </c>
       <c r="B37" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>131276492</v>
       </c>
       <c r="B38" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131275213</v>
+        <v>131273410</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546481</v>
+        <v>546342</v>
       </c>
       <c r="R43" t="n">
-        <v>6998980</v>
+        <v>6999195</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6019,10 +6019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131275182</v>
+        <v>131273426</v>
       </c>
       <c r="B44" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6030,21 +6030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546357</v>
+        <v>546172</v>
       </c>
       <c r="R44" t="n">
-        <v>6999022</v>
+        <v>6999385</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6095,6 +6095,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6108,6 +6113,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6125,10 +6145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131276487</v>
+        <v>131275213</v>
       </c>
       <c r="B45" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6136,21 +6156,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6163,10 +6183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546313</v>
+        <v>546481</v>
       </c>
       <c r="R45" t="n">
-        <v>6999060</v>
+        <v>6998980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6218,22 +6238,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6251,41 +6266,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131273381</v>
+        <v>131275182</v>
       </c>
       <c r="B46" t="n">
-        <v>80379</v>
+        <v>80351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6293,10 +6304,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546353</v>
+        <v>546357</v>
       </c>
       <c r="R46" t="n">
-        <v>6999084</v>
+        <v>6999022</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6331,11 +6342,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6349,26 +6355,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6386,10 +6372,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131275194</v>
+        <v>131276487</v>
       </c>
       <c r="B47" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6424,10 +6410,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546153</v>
+        <v>546313</v>
       </c>
       <c r="R47" t="n">
-        <v>6999210</v>
+        <v>6999060</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6462,11 +6448,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6484,12 +6465,12 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -6499,7 +6480,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6517,37 +6498,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131273410</v>
+        <v>131273381</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>80380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6555,10 +6540,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546342</v>
+        <v>546353</v>
       </c>
       <c r="R48" t="n">
-        <v>6999195</v>
+        <v>6999084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6593,6 +6578,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6610,17 +6600,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6638,10 +6633,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131273426</v>
+        <v>131275194</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6649,21 +6644,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6676,10 +6671,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546172</v>
+        <v>546153</v>
       </c>
       <c r="R49" t="n">
-        <v>6999385</v>
+        <v>6999210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6716,7 +6711,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6736,17 +6731,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6767,7 +6767,7 @@
         <v>131273401</v>
       </c>
       <c r="B50" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>131273406</v>
       </c>
       <c r="B51" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131276478</v>
+        <v>131273374</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546058</v>
+        <v>546094</v>
       </c>
       <c r="R52" t="n">
-        <v>6999435</v>
+        <v>6999322</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7140,9 +7140,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7160,7 +7165,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131275139</v>
+        <v>131275151</v>
       </c>
       <c r="B53" t="n">
         <v>57884</v>
@@ -7203,10 +7208,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546151</v>
+        <v>546124</v>
       </c>
       <c r="R53" t="n">
-        <v>6999044</v>
+        <v>6999206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7290,7 +7295,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131273374</v>
+        <v>131275159</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -7323,7 +7328,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7333,10 +7338,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546094</v>
+        <v>546099</v>
       </c>
       <c r="R54" t="n">
-        <v>6999322</v>
+        <v>6999277</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7373,7 +7378,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7400,14 +7405,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131275151</v>
+        <v>131276478</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546124</v>
+        <v>546058</v>
       </c>
       <c r="R55" t="n">
-        <v>6999206</v>
+        <v>6999435</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7555,7 +7555,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131275159</v>
+        <v>131275139</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -7588,7 +7588,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546099</v>
+        <v>546151</v>
       </c>
       <c r="R56" t="n">
-        <v>6999277</v>
+        <v>6999044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7688,7 +7688,7 @@
         <v>131273412</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131275129</v>
+        <v>131275195</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,31 +7817,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546338</v>
+        <v>546150</v>
       </c>
       <c r="R58" t="n">
-        <v>6999380</v>
+        <v>6999197</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7887,17 +7882,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7908,17 +7899,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7936,10 +7932,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273373</v>
+        <v>131273394</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7947,29 +7943,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7979,10 +7974,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546097</v>
+        <v>546346</v>
       </c>
       <c r="R59" t="n">
-        <v>6999307</v>
+        <v>6999078</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8019,7 +8014,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8028,6 +8023,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8038,22 +8034,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8071,10 +8067,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276475</v>
+        <v>131276488</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8082,31 +8078,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8114,10 +8105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546338</v>
+        <v>546062</v>
       </c>
       <c r="R60" t="n">
-        <v>6999168</v>
+        <v>6999441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8152,17 +8143,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8173,17 +8160,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8201,10 +8193,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131275195</v>
+        <v>131276491</v>
       </c>
       <c r="B61" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8239,10 +8231,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546150</v>
+        <v>546074</v>
       </c>
       <c r="R61" t="n">
-        <v>6999197</v>
+        <v>6999366</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8294,12 +8286,12 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -8309,7 +8301,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8327,10 +8319,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131273394</v>
+        <v>131275129</v>
       </c>
       <c r="B62" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8338,28 +8330,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8369,10 +8362,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>546346</v>
+        <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999078</v>
+        <v>6999380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8409,7 +8402,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Fertila bålar på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8418,7 +8411,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8429,22 +8421,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8462,10 +8449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131276488</v>
+        <v>131273373</v>
       </c>
       <c r="B63" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8473,26 +8460,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8500,10 +8492,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546062</v>
+        <v>546097</v>
       </c>
       <c r="R63" t="n">
-        <v>6999441</v>
+        <v>6999307</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8538,13 +8530,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8555,22 +8551,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8588,10 +8584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276491</v>
+        <v>131276475</v>
       </c>
       <c r="B64" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8599,26 +8595,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8626,10 +8627,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546074</v>
+        <v>546338</v>
       </c>
       <c r="R64" t="n">
-        <v>6999366</v>
+        <v>6999168</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8664,13 +8665,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8681,22 +8686,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131273371</v>
+        <v>131273414</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,31 +8725,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8757,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546089</v>
+        <v>546430</v>
       </c>
       <c r="R65" t="n">
-        <v>6999267</v>
+        <v>6998969</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8795,17 +8790,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8835,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131276481</v>
+        <v>131273420</v>
       </c>
       <c r="B66" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8855,31 +8846,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8887,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546070</v>
+        <v>546204</v>
       </c>
       <c r="R66" t="n">
-        <v>6999374</v>
+        <v>6999267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8927,7 +8913,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8936,6 +8922,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8974,10 +8961,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273372</v>
+        <v>131273416</v>
       </c>
       <c r="B67" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8985,31 +8972,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9017,10 +8999,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546089</v>
+        <v>546387</v>
       </c>
       <c r="R67" t="n">
-        <v>6999297</v>
+        <v>6999068</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9057,7 +9039,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9066,6 +9048,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9084,14 +9067,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9109,10 +9087,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131275211</v>
+        <v>131275200</v>
       </c>
       <c r="B68" t="n">
-        <v>91833</v>
+        <v>80351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9120,26 +9098,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9147,10 +9125,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546185</v>
+        <v>546174</v>
       </c>
       <c r="R68" t="n">
-        <v>6999135</v>
+        <v>6999354</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9202,17 +9180,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9230,10 +9213,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273414</v>
+        <v>131273384</v>
       </c>
       <c r="B69" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9241,37 +9224,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546430</v>
+        <v>546286</v>
       </c>
       <c r="R69" t="n">
-        <v>6998969</v>
+        <v>6999257</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9306,35 +9286,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Fertil med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9351,10 +9315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273420</v>
+        <v>131273386</v>
       </c>
       <c r="B70" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9362,26 +9326,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9389,10 +9357,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546204</v>
+        <v>546294</v>
       </c>
       <c r="R70" t="n">
-        <v>6999267</v>
+        <v>6999434</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9429,7 +9397,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9449,17 +9417,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9477,10 +9450,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131275200</v>
+        <v>131273371</v>
       </c>
       <c r="B71" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9488,26 +9461,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9515,10 +9493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546174</v>
+        <v>546089</v>
       </c>
       <c r="R71" t="n">
-        <v>6999354</v>
+        <v>6999267</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9553,13 +9531,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9570,22 +9552,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9603,10 +9580,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273384</v>
+        <v>131276481</v>
       </c>
       <c r="B72" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9614,34 +9591,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546286</v>
+        <v>546070</v>
       </c>
       <c r="R72" t="n">
-        <v>6999257</v>
+        <v>6999374</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9678,7 +9663,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9689,6 +9674,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9705,10 +9710,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273386</v>
+        <v>131273372</v>
       </c>
       <c r="B73" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9716,28 +9721,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9747,10 +9753,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546294</v>
+        <v>546089</v>
       </c>
       <c r="R73" t="n">
-        <v>6999434</v>
+        <v>6999297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9787,7 +9793,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9796,7 +9802,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9807,22 +9812,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9840,10 +9845,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273416</v>
+        <v>131275211</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9851,26 +9856,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9878,10 +9883,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546387</v>
+        <v>546185</v>
       </c>
       <c r="R74" t="n">
-        <v>6999068</v>
+        <v>6999135</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9914,11 +9919,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10361,7 +10361,7 @@
         <v>131276486</v>
       </c>
       <c r="B78" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>131275181</v>
       </c>
       <c r="B79" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>131273393</v>
       </c>
       <c r="B80" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>131275202</v>
       </c>
       <c r="B81" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>131273402</v>
       </c>
       <c r="B82" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>131273392</v>
       </c>
       <c r="B83" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>131275170</v>
       </c>
       <c r="B84" t="n">
-        <v>83216</v>
+        <v>83217</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131275164</v>
+        <v>131275204</v>
       </c>
       <c r="B85" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11265,31 +11265,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11297,10 +11292,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546097</v>
+        <v>546244</v>
       </c>
       <c r="R85" t="n">
-        <v>6999287</v>
+        <v>6999418</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11335,17 +11330,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11356,17 +11347,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11384,10 +11380,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131275204</v>
+        <v>131276483</v>
       </c>
       <c r="B86" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11422,10 +11418,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546244</v>
+        <v>546404</v>
       </c>
       <c r="R86" t="n">
-        <v>6999418</v>
+        <v>6999205</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11510,10 +11506,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131276483</v>
+        <v>131275205</v>
       </c>
       <c r="B87" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11548,10 +11544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546404</v>
+        <v>546149</v>
       </c>
       <c r="R87" t="n">
-        <v>6999205</v>
+        <v>6999093</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11636,10 +11632,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131275205</v>
+        <v>131273388</v>
       </c>
       <c r="B88" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11666,7 +11662,11 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546149</v>
+        <v>546370</v>
       </c>
       <c r="R88" t="n">
-        <v>6999093</v>
+        <v>6999140</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11712,6 +11712,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11744,7 +11749,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11762,10 +11767,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131273388</v>
+        <v>131275188</v>
       </c>
       <c r="B89" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11792,11 +11797,7 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11804,10 +11805,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546370</v>
+        <v>546149</v>
       </c>
       <c r="R89" t="n">
-        <v>6999140</v>
+        <v>6999276</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11844,7 +11845,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11864,22 +11865,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11897,10 +11893,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275188</v>
+        <v>131275161</v>
       </c>
       <c r="B90" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11908,26 +11904,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11935,7 +11936,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546149</v>
+        <v>546100</v>
       </c>
       <c r="R90" t="n">
         <v>6999276</v>
@@ -11975,7 +11976,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11984,7 +11985,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11995,17 +11995,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12023,7 +12023,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131275161</v>
+        <v>131275165</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -12066,10 +12066,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546100</v>
+        <v>546098</v>
       </c>
       <c r="R91" t="n">
-        <v>6999276</v>
+        <v>6999296</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12153,7 +12153,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275165</v>
+        <v>131275164</v>
       </c>
       <c r="B92" t="n">
         <v>57884</v>
@@ -12196,10 +12196,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546098</v>
+        <v>546097</v>
       </c>
       <c r="R92" t="n">
-        <v>6999296</v>
+        <v>6999287</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131273362</v>
+        <v>131273424</v>
       </c>
       <c r="B93" t="n">
-        <v>91813</v>
+        <v>79246</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12294,30 +12294,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12325,10 +12321,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546302</v>
+        <v>546090</v>
       </c>
       <c r="R93" t="n">
-        <v>6999463</v>
+        <v>6999323</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12365,7 +12361,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12393,14 +12389,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12418,7 +12409,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131275135</v>
+        <v>131276477</v>
       </c>
       <c r="B94" t="n">
         <v>57884</v>
@@ -12461,10 +12452,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546142</v>
+        <v>546062</v>
       </c>
       <c r="R94" t="n">
-        <v>6999047</v>
+        <v>6999442</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12548,7 +12539,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275158</v>
+        <v>131275135</v>
       </c>
       <c r="B95" t="n">
         <v>57884</v>
@@ -12591,10 +12582,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546100</v>
+        <v>546142</v>
       </c>
       <c r="R95" t="n">
-        <v>6999268</v>
+        <v>6999047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12678,7 +12669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131273366</v>
+        <v>131275158</v>
       </c>
       <c r="B96" t="n">
         <v>57884</v>
@@ -12724,7 +12715,7 @@
         <v>546100</v>
       </c>
       <c r="R96" t="n">
-        <v>6999258</v>
+        <v>6999268</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12761,7 +12752,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12788,14 +12779,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12813,37 +12799,41 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131275209</v>
+        <v>131273362</v>
       </c>
       <c r="B97" t="n">
-        <v>80310</v>
+        <v>91814</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12851,10 +12841,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546171</v>
+        <v>546302</v>
       </c>
       <c r="R97" t="n">
-        <v>6999219</v>
+        <v>6999463</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12889,6 +12879,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12906,22 +12901,22 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12939,10 +12934,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131273424</v>
+        <v>131273366</v>
       </c>
       <c r="B98" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12950,26 +12945,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -12977,10 +12977,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546090</v>
+        <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999323</v>
+        <v>6999258</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13026,7 +13026,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13045,9 +13044,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13068,7 +13072,7 @@
         <v>131275217</v>
       </c>
       <c r="B99" t="n">
-        <v>83212</v>
+        <v>83213</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13218,42 +13222,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131276477</v>
+        <v>131275209</v>
       </c>
       <c r="B100" t="n">
-        <v>57884</v>
+        <v>80311</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13261,10 +13260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546062</v>
+        <v>546171</v>
       </c>
       <c r="R100" t="n">
-        <v>6999442</v>
+        <v>6999219</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13299,17 +13298,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13320,17 +13315,22 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273419</v>
+        <v>131273409</v>
       </c>
       <c r="B101" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,26 +13359,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546230</v>
+        <v>546299</v>
       </c>
       <c r="R101" t="n">
-        <v>6999267</v>
+        <v>6999454</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13454,19 +13454,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13484,10 +13479,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273395</v>
+        <v>131273377</v>
       </c>
       <c r="B102" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13495,26 +13490,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13522,10 +13522,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546313</v>
+        <v>546077</v>
       </c>
       <c r="R102" t="n">
-        <v>6999066</v>
+        <v>6999352</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13571,7 +13571,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13592,12 +13591,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13615,10 +13614,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131275137</v>
+        <v>131273419</v>
       </c>
       <c r="B103" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13626,31 +13625,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13658,10 +13652,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546139</v>
+        <v>546230</v>
       </c>
       <c r="R103" t="n">
-        <v>6999047</v>
+        <v>6999267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13698,7 +13692,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13707,12 +13701,13 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -13725,9 +13720,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13745,10 +13750,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131273377</v>
+        <v>131273395</v>
       </c>
       <c r="B104" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13756,31 +13761,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13788,10 +13788,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546077</v>
+        <v>546313</v>
       </c>
       <c r="R104" t="n">
-        <v>6999352</v>
+        <v>6999066</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13837,6 +13837,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13857,12 +13858,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13880,10 +13881,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131273409</v>
+        <v>131275137</v>
       </c>
       <c r="B105" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13891,24 +13892,29 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -13918,10 +13924,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546299</v>
+        <v>546139</v>
       </c>
       <c r="R105" t="n">
-        <v>6999454</v>
+        <v>6999047</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13958,7 +13964,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13967,7 +13973,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13986,14 +13991,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14149,7 +14149,7 @@
         <v>131275207</v>
       </c>
       <c r="B107" t="n">
-        <v>78257</v>
+        <v>78258</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>131275172</v>
       </c>
       <c r="B108" t="n">
-        <v>80254</v>
+        <v>80255</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>131275190</v>
       </c>
       <c r="B109" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14519,27 +14519,27 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131273379</v>
+        <v>131273382</v>
       </c>
       <c r="B110" t="n">
-        <v>57884</v>
+        <v>57725</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14547,25 +14547,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>546099</v>
+        <v>546360</v>
       </c>
       <c r="R110" t="n">
-        <v>6999326</v>
+        <v>6999087</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14602,7 +14614,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14619,24 +14631,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14654,7 +14651,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131275143</v>
+        <v>131273376</v>
       </c>
       <c r="B111" t="n">
         <v>57884</v>
@@ -14687,7 +14684,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -14697,10 +14694,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>546149</v>
+        <v>546086</v>
       </c>
       <c r="R111" t="n">
-        <v>6999065</v>
+        <v>6999336</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14737,7 +14734,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14764,9 +14761,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14784,7 +14786,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131273376</v>
+        <v>131275143</v>
       </c>
       <c r="B112" t="n">
         <v>57884</v>
@@ -14817,7 +14819,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -14827,10 +14829,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>546086</v>
+        <v>546149</v>
       </c>
       <c r="R112" t="n">
-        <v>6999336</v>
+        <v>6999065</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14867,7 +14869,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14894,14 +14896,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14919,27 +14916,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131273382</v>
+        <v>131273379</v>
       </c>
       <c r="B113" t="n">
-        <v>57725</v>
+        <v>57884</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -14947,37 +14944,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546360</v>
+        <v>546099</v>
       </c>
       <c r="R113" t="n">
-        <v>6999087</v>
+        <v>6999326</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15014,7 +14999,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15031,9 +15016,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15051,10 +15051,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131275212</v>
+        <v>131275167</v>
       </c>
       <c r="B114" t="n">
-        <v>91833</v>
+        <v>80217</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15062,26 +15062,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15089,10 +15089,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546213</v>
+        <v>546468</v>
       </c>
       <c r="R114" t="n">
-        <v>6999022</v>
+        <v>6999037</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15144,17 +15144,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15175,7 +15175,7 @@
         <v>131273363</v>
       </c>
       <c r="B115" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273418</v>
+        <v>131275212</v>
       </c>
       <c r="B116" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15318,26 +15318,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546329</v>
+        <v>546213</v>
       </c>
       <c r="R116" t="n">
-        <v>6999224</v>
+        <v>6999022</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15381,11 +15381,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15436,7 +15431,7 @@
         <v>131273387</v>
       </c>
       <c r="B117" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15568,37 +15563,42 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131275174</v>
+        <v>131275166</v>
       </c>
       <c r="B118" t="n">
-        <v>75223</v>
+        <v>57884</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15606,10 +15606,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546222</v>
+        <v>546208</v>
       </c>
       <c r="R118" t="n">
-        <v>6999408</v>
+        <v>6999393</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15655,7 +15655,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -15666,22 +15665,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15699,10 +15693,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131275167</v>
+        <v>131273418</v>
       </c>
       <c r="B119" t="n">
-        <v>80216</v>
+        <v>79246</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15710,21 +15704,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15737,10 +15731,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546468</v>
+        <v>546329</v>
       </c>
       <c r="R119" t="n">
-        <v>6999037</v>
+        <v>6999224</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15775,6 +15769,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -15792,17 +15791,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15820,42 +15819,37 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275166</v>
+        <v>131275174</v>
       </c>
       <c r="B120" t="n">
-        <v>57884</v>
+        <v>75224</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15863,10 +15857,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546208</v>
+        <v>546222</v>
       </c>
       <c r="R120" t="n">
-        <v>6999393</v>
+        <v>6999408</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15903,7 +15897,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15912,6 +15906,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -15922,17 +15917,22 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15950,10 +15950,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131273385</v>
+        <v>131275148</v>
       </c>
       <c r="B121" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15961,28 +15961,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -15992,10 +15993,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>546261</v>
+        <v>546118</v>
       </c>
       <c r="R121" t="n">
-        <v>6999479</v>
+        <v>6999179</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16032,7 +16033,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16041,7 +16042,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16052,22 +16052,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16085,10 +16080,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131275216</v>
+        <v>131275133</v>
       </c>
       <c r="B122" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16096,26 +16091,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -16123,10 +16123,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>546240</v>
+        <v>546213</v>
       </c>
       <c r="R122" t="n">
-        <v>6999411</v>
+        <v>6999200</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16172,7 +16172,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16211,10 +16210,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131275148</v>
+        <v>131275216</v>
       </c>
       <c r="B123" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16222,31 +16221,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -16254,10 +16248,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>546118</v>
+        <v>546240</v>
       </c>
       <c r="R123" t="n">
-        <v>6999179</v>
+        <v>6999411</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16294,7 +16288,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16303,6 +16297,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -16341,10 +16336,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131275133</v>
+        <v>131273385</v>
       </c>
       <c r="B124" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16352,29 +16347,28 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -16384,10 +16378,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>546213</v>
+        <v>546261</v>
       </c>
       <c r="R124" t="n">
-        <v>6999200</v>
+        <v>6999479</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16424,7 +16418,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16433,6 +16427,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -16443,17 +16438,22 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -16471,10 +16471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131275199</v>
+        <v>131273383</v>
       </c>
       <c r="B125" t="n">
-        <v>80350</v>
+        <v>80352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16482,21 +16482,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546147</v>
+        <v>546292</v>
       </c>
       <c r="R125" t="n">
-        <v>6999326</v>
+        <v>6999247</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16547,6 +16547,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Växer här på en lutande sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -16564,22 +16569,22 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16597,37 +16602,42 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131275171</v>
+        <v>131273364</v>
       </c>
       <c r="B126" t="n">
-        <v>80254</v>
+        <v>57884</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -16635,10 +16645,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546230</v>
+        <v>546403</v>
       </c>
       <c r="R126" t="n">
-        <v>6999202</v>
+        <v>6998994</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16673,13 +16683,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -16690,17 +16704,22 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16718,10 +16737,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275197</v>
+        <v>131275134</v>
       </c>
       <c r="B127" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16729,26 +16748,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -16756,10 +16780,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546130</v>
+        <v>546141</v>
       </c>
       <c r="R127" t="n">
-        <v>6999313</v>
+        <v>6999039</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16794,13 +16818,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -16811,22 +16839,17 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16844,32 +16867,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275173</v>
+        <v>131275199</v>
       </c>
       <c r="B128" t="n">
-        <v>80254</v>
+        <v>80351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -16882,10 +16905,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546165</v>
+        <v>546147</v>
       </c>
       <c r="R128" t="n">
-        <v>6999228</v>
+        <v>6999326</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16937,17 +16960,22 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -16965,32 +16993,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131273383</v>
+        <v>131275171</v>
       </c>
       <c r="B129" t="n">
-        <v>80351</v>
+        <v>80255</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -17003,10 +17031,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546292</v>
+        <v>546230</v>
       </c>
       <c r="R129" t="n">
-        <v>6999247</v>
+        <v>6999202</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17041,11 +17069,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Växer här på en lutande sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -17063,22 +17086,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -17096,10 +17114,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131273364</v>
+        <v>131275197</v>
       </c>
       <c r="B130" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17107,31 +17125,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -17139,10 +17152,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>546403</v>
+        <v>546130</v>
       </c>
       <c r="R130" t="n">
-        <v>6998994</v>
+        <v>6999313</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17177,17 +17190,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -17198,22 +17207,22 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -17231,42 +17240,37 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131275134</v>
+        <v>131275173</v>
       </c>
       <c r="B131" t="n">
-        <v>57884</v>
+        <v>80255</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -17274,10 +17278,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>546141</v>
+        <v>546165</v>
       </c>
       <c r="R131" t="n">
-        <v>6999039</v>
+        <v>6999228</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17312,17 +17316,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -17333,17 +17333,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -17361,10 +17361,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131273398</v>
+        <v>131273411</v>
       </c>
       <c r="B132" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17372,30 +17372,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -17403,10 +17399,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>546299</v>
+        <v>546421</v>
       </c>
       <c r="R132" t="n">
-        <v>6999243</v>
+        <v>6999063</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17443,7 +17439,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17463,22 +17459,17 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -17496,10 +17487,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131275125</v>
+        <v>131273425</v>
       </c>
       <c r="B133" t="n">
-        <v>83225</v>
+        <v>79246</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17507,21 +17498,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -17534,10 +17525,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>546375</v>
+        <v>546106</v>
       </c>
       <c r="R133" t="n">
-        <v>6998987</v>
+        <v>6999416</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17572,6 +17563,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -17597,9 +17593,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -17617,10 +17618,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131273411</v>
+        <v>131275149</v>
       </c>
       <c r="B134" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17628,26 +17629,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -17655,10 +17661,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>546421</v>
+        <v>546120</v>
       </c>
       <c r="R134" t="n">
-        <v>6999063</v>
+        <v>6999185</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17695,7 +17701,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17704,7 +17710,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -17743,10 +17748,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131275149</v>
+        <v>131273398</v>
       </c>
       <c r="B135" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17754,29 +17759,28 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -17786,10 +17790,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>546120</v>
+        <v>546299</v>
       </c>
       <c r="R135" t="n">
-        <v>6999185</v>
+        <v>6999243</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17826,7 +17830,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en flerstammig gammal sälg.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17835,6 +17839,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -17845,17 +17850,22 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -17873,10 +17883,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131273425</v>
+        <v>131275125</v>
       </c>
       <c r="B136" t="n">
-        <v>79245</v>
+        <v>83226</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17884,21 +17894,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -17911,10 +17921,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>546106</v>
+        <v>546375</v>
       </c>
       <c r="R136" t="n">
-        <v>6999416</v>
+        <v>6998987</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17949,11 +17959,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -17979,14 +17984,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131275138</v>
+        <v>131275136</v>
       </c>
       <c r="B138" t="n">
         <v>57884</v>
@@ -18177,10 +18177,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>546145</v>
+        <v>546148</v>
       </c>
       <c r="R138" t="n">
-        <v>6999053</v>
+        <v>6999041</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18264,7 +18264,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131275136</v>
+        <v>131275138</v>
       </c>
       <c r="B139" t="n">
         <v>57884</v>
@@ -18307,10 +18307,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>546148</v>
+        <v>546145</v>
       </c>
       <c r="R139" t="n">
-        <v>6999041</v>
+        <v>6999053</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18397,7 +18397,7 @@
         <v>131275208</v>
       </c>
       <c r="B140" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>131273408</v>
       </c>
       <c r="B141" t="n">
-        <v>80386</v>
+        <v>80387</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>131273390</v>
       </c>
       <c r="B142" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>131275203</v>
       </c>
       <c r="B143" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>131275186</v>
       </c>
       <c r="B144" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>131276485</v>
       </c>
       <c r="B145" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>131275183</v>
       </c>
       <c r="B146" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19279,10 +19279,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275214</v>
+        <v>131273367</v>
       </c>
       <c r="B147" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19290,26 +19290,31 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -19317,10 +19322,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546193</v>
+        <v>546103</v>
       </c>
       <c r="R147" t="n">
-        <v>6999241</v>
+        <v>6999266</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19355,13 +19360,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -19380,9 +19389,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19400,37 +19414,42 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131275210</v>
+        <v>131276480</v>
       </c>
       <c r="B148" t="n">
-        <v>80310</v>
+        <v>57884</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -19438,10 +19457,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546168</v>
+        <v>546066</v>
       </c>
       <c r="R148" t="n">
-        <v>6999217</v>
+        <v>6999401</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19476,13 +19495,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -19493,22 +19516,17 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19526,7 +19544,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131273367</v>
+        <v>131276479</v>
       </c>
       <c r="B149" t="n">
         <v>57884</v>
@@ -19569,10 +19587,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546103</v>
+        <v>546062</v>
       </c>
       <c r="R149" t="n">
-        <v>6999266</v>
+        <v>6999415</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19609,7 +19627,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -19636,14 +19654,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19661,10 +19674,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131276480</v>
+        <v>131275214</v>
       </c>
       <c r="B150" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19672,31 +19685,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -19704,10 +19712,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546066</v>
+        <v>546193</v>
       </c>
       <c r="R150" t="n">
-        <v>6999401</v>
+        <v>6999241</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19742,17 +19750,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -19791,42 +19795,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131276479</v>
+        <v>131275210</v>
       </c>
       <c r="B151" t="n">
-        <v>57884</v>
+        <v>80311</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -19834,10 +19833,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546062</v>
+        <v>546168</v>
       </c>
       <c r="R151" t="n">
-        <v>6999415</v>
+        <v>6999217</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19872,17 +19871,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -19893,17 +19888,22 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -19921,10 +19921,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131275130</v>
+        <v>131275177</v>
       </c>
       <c r="B152" t="n">
-        <v>57884</v>
+        <v>83221</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19932,31 +19932,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -19964,10 +19959,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546460</v>
+        <v>546303</v>
       </c>
       <c r="R152" t="n">
-        <v>6999069</v>
+        <v>6999065</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -20004,7 +19999,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20013,6 +20008,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -20021,19 +20017,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20051,10 +20057,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275177</v>
+        <v>131275189</v>
       </c>
       <c r="B153" t="n">
-        <v>83220</v>
+        <v>80351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20062,21 +20068,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -20089,10 +20095,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546303</v>
+        <v>546224</v>
       </c>
       <c r="R153" t="n">
-        <v>6999065</v>
+        <v>6999013</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20129,7 +20135,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20147,29 +20153,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -20187,10 +20188,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131275189</v>
+        <v>131273405</v>
       </c>
       <c r="B154" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20225,10 +20226,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>546224</v>
+        <v>546169</v>
       </c>
       <c r="R154" t="n">
-        <v>6999013</v>
+        <v>6999410</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -20265,7 +20266,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20285,12 +20286,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -20300,7 +20301,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -20318,10 +20319,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131273405</v>
+        <v>131275196</v>
       </c>
       <c r="B155" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20356,10 +20357,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>546169</v>
+        <v>546124</v>
       </c>
       <c r="R155" t="n">
-        <v>6999410</v>
+        <v>6999220</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -20392,11 +20393,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20449,10 +20445,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131275196</v>
+        <v>131275130</v>
       </c>
       <c r="B156" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20460,26 +20456,31 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -20487,10 +20488,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>546124</v>
+        <v>546460</v>
       </c>
       <c r="R156" t="n">
-        <v>6999220</v>
+        <v>6999069</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20525,13 +20526,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -20542,22 +20547,17 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -20578,7 +20578,7 @@
         <v>131275168</v>
       </c>
       <c r="B157" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>131273403</v>
       </c>
       <c r="B158" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>131273400</v>
       </c>
       <c r="B159" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>131273417</v>
       </c>
       <c r="B160" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131273412</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
-        <v>79246</v>
+        <v>80351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,21 +7696,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546441</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999013</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7778,17 +7778,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7806,7 +7811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131275195</v>
+        <v>131273394</v>
       </c>
       <c r="B58" t="n">
         <v>80351</v>
@@ -7836,7 +7841,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7844,10 +7853,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546150</v>
+        <v>546346</v>
       </c>
       <c r="R58" t="n">
-        <v>6999197</v>
+        <v>6999078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7882,6 +7891,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7899,12 +7913,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7914,7 +7928,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7932,7 +7946,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273394</v>
+        <v>131276488</v>
       </c>
       <c r="B59" t="n">
         <v>80351</v>
@@ -7962,11 +7976,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7974,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546346</v>
+        <v>546062</v>
       </c>
       <c r="R59" t="n">
-        <v>6999078</v>
+        <v>6999441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8010,11 +8020,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8067,7 +8072,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276488</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
         <v>80351</v>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546062</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999441</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8193,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131276491</v>
+        <v>131275129</v>
       </c>
       <c r="B61" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8204,26 +8209,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8231,10 +8241,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546074</v>
+        <v>546338</v>
       </c>
       <c r="R61" t="n">
-        <v>6999366</v>
+        <v>6999380</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8269,13 +8279,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8286,22 +8300,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8319,7 +8328,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131275129</v>
+        <v>131273373</v>
       </c>
       <c r="B62" t="n">
         <v>57884</v>
@@ -8362,10 +8371,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>546338</v>
+        <v>546097</v>
       </c>
       <c r="R62" t="n">
-        <v>6999380</v>
+        <v>6999307</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8402,7 +8411,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8429,9 +8438,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131273373</v>
+        <v>131276475</v>
       </c>
       <c r="B63" t="n">
         <v>57884</v>
@@ -8482,7 +8496,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8492,10 +8506,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546097</v>
+        <v>546338</v>
       </c>
       <c r="R63" t="n">
-        <v>6999307</v>
+        <v>6999168</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8532,7 +8546,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8559,14 +8573,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8584,10 +8593,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276475</v>
+        <v>131273412</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8595,31 +8604,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8627,10 +8631,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546338</v>
+        <v>546441</v>
       </c>
       <c r="R64" t="n">
-        <v>6999168</v>
+        <v>6999013</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8665,17 +8669,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131273414</v>
+        <v>131275211</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546430</v>
+        <v>546185</v>
       </c>
       <c r="R65" t="n">
-        <v>6998969</v>
+        <v>6999135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8835,7 +8835,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273420</v>
+        <v>131273414</v>
       </c>
       <c r="B66" t="n">
         <v>79246</v>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546204</v>
+        <v>546430</v>
       </c>
       <c r="R66" t="n">
-        <v>6999267</v>
+        <v>6998969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8909,11 +8909,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8961,7 +8956,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273416</v>
+        <v>131273420</v>
       </c>
       <c r="B67" t="n">
         <v>79246</v>
@@ -8999,10 +8994,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546387</v>
+        <v>546204</v>
       </c>
       <c r="R67" t="n">
-        <v>6999068</v>
+        <v>6999267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9039,7 +9034,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9087,10 +9082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131275200</v>
+        <v>131273416</v>
       </c>
       <c r="B68" t="n">
-        <v>80351</v>
+        <v>79246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9098,21 +9093,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9125,10 +9120,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546174</v>
+        <v>546387</v>
       </c>
       <c r="R68" t="n">
-        <v>6999354</v>
+        <v>6999068</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9163,6 +9158,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9180,22 +9180,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9213,7 +9208,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273384</v>
+        <v>131275200</v>
       </c>
       <c r="B69" t="n">
         <v>80351</v>
@@ -9242,16 +9237,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546286</v>
+        <v>546174</v>
       </c>
       <c r="R69" t="n">
-        <v>6999257</v>
+        <v>6999354</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9286,19 +9284,40 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Fertil med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9315,7 +9334,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273386</v>
+        <v>131273384</v>
       </c>
       <c r="B70" t="n">
         <v>80351</v>
@@ -9344,23 +9363,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546294</v>
+        <v>546286</v>
       </c>
       <c r="R70" t="n">
-        <v>6999434</v>
+        <v>6999257</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9397,7 +9409,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9406,34 +9418,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9450,10 +9436,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273371</v>
+        <v>131273386</v>
       </c>
       <c r="B71" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9461,29 +9447,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9493,10 +9478,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546089</v>
+        <v>546294</v>
       </c>
       <c r="R71" t="n">
-        <v>6999267</v>
+        <v>6999434</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9533,7 +9518,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9542,6 +9527,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9552,17 +9538,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9580,7 +9571,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131276481</v>
+        <v>131273371</v>
       </c>
       <c r="B72" t="n">
         <v>57884</v>
@@ -9613,7 +9604,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9623,10 +9614,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546070</v>
+        <v>546089</v>
       </c>
       <c r="R72" t="n">
-        <v>6999374</v>
+        <v>6999267</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9663,7 +9654,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9710,7 +9701,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273372</v>
+        <v>131276481</v>
       </c>
       <c r="B73" t="n">
         <v>57884</v>
@@ -9753,10 +9744,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546089</v>
+        <v>546070</v>
       </c>
       <c r="R73" t="n">
-        <v>6999297</v>
+        <v>6999374</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9793,7 +9784,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9820,14 +9811,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9845,10 +9831,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131275211</v>
+        <v>131273372</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9856,24 +9842,29 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9883,10 +9874,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546185</v>
+        <v>546089</v>
       </c>
       <c r="R74" t="n">
-        <v>6999135</v>
+        <v>6999297</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9921,13 +9912,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9946,9 +9941,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -11128,37 +11128,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131275170</v>
+        <v>131275165</v>
       </c>
       <c r="B84" t="n">
-        <v>83217</v>
+        <v>57884</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11166,10 +11171,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>546401</v>
+        <v>546098</v>
       </c>
       <c r="R84" t="n">
-        <v>6999141</v>
+        <v>6999296</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11204,13 +11209,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11221,22 +11230,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11254,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131275204</v>
+        <v>131275164</v>
       </c>
       <c r="B85" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11265,26 +11269,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11292,10 +11301,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546244</v>
+        <v>546097</v>
       </c>
       <c r="R85" t="n">
-        <v>6999418</v>
+        <v>6999287</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11330,13 +11339,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11347,22 +11360,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11380,7 +11388,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131276483</v>
+        <v>131275204</v>
       </c>
       <c r="B86" t="n">
         <v>80351</v>
@@ -11418,10 +11426,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546404</v>
+        <v>546244</v>
       </c>
       <c r="R86" t="n">
-        <v>6999205</v>
+        <v>6999418</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11506,7 +11514,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131275205</v>
+        <v>131276483</v>
       </c>
       <c r="B87" t="n">
         <v>80351</v>
@@ -11544,10 +11552,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546149</v>
+        <v>546404</v>
       </c>
       <c r="R87" t="n">
-        <v>6999093</v>
+        <v>6999205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11632,7 +11640,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131273388</v>
+        <v>131275205</v>
       </c>
       <c r="B88" t="n">
         <v>80351</v>
@@ -11662,11 +11670,7 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11674,10 +11678,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546370</v>
+        <v>546149</v>
       </c>
       <c r="R88" t="n">
-        <v>6999140</v>
+        <v>6999093</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11712,11 +11716,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11749,7 +11748,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11767,7 +11766,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131275188</v>
+        <v>131273388</v>
       </c>
       <c r="B89" t="n">
         <v>80351</v>
@@ -11797,7 +11796,11 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11805,10 +11808,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546149</v>
+        <v>546370</v>
       </c>
       <c r="R89" t="n">
-        <v>6999276</v>
+        <v>6999140</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11845,7 +11848,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11865,17 +11868,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11893,10 +11901,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275161</v>
+        <v>131275188</v>
       </c>
       <c r="B90" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11904,31 +11912,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11936,7 +11939,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546100</v>
+        <v>546149</v>
       </c>
       <c r="R90" t="n">
         <v>6999276</v>
@@ -11976,7 +11979,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11985,6 +11988,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11995,17 +11999,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12023,7 +12027,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131275165</v>
+        <v>131275161</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -12066,10 +12070,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546098</v>
+        <v>546100</v>
       </c>
       <c r="R91" t="n">
-        <v>6999296</v>
+        <v>6999276</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12106,7 +12110,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12153,42 +12157,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275164</v>
+        <v>131275170</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>83217</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12196,10 +12195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546097</v>
+        <v>546401</v>
       </c>
       <c r="R92" t="n">
-        <v>6999287</v>
+        <v>6999141</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12234,17 +12233,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12255,17 +12250,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131273424</v>
+        <v>131273362</v>
       </c>
       <c r="B93" t="n">
-        <v>79246</v>
+        <v>91814</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12294,26 +12294,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12321,10 +12325,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546090</v>
+        <v>546302</v>
       </c>
       <c r="R93" t="n">
-        <v>6999323</v>
+        <v>6999463</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12361,7 +12365,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12389,9 +12393,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12409,10 +12418,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131276477</v>
+        <v>131273424</v>
       </c>
       <c r="B94" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12420,31 +12429,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12452,10 +12456,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546062</v>
+        <v>546090</v>
       </c>
       <c r="R94" t="n">
-        <v>6999442</v>
+        <v>6999323</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12492,7 +12496,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12501,6 +12505,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12539,42 +12544,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275135</v>
+        <v>131275209</v>
       </c>
       <c r="B95" t="n">
-        <v>57884</v>
+        <v>80311</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546142</v>
+        <v>546171</v>
       </c>
       <c r="R95" t="n">
-        <v>6999047</v>
+        <v>6999219</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12620,17 +12620,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12641,17 +12637,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12669,7 +12670,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131275158</v>
+        <v>131276477</v>
       </c>
       <c r="B96" t="n">
         <v>57884</v>
@@ -12712,10 +12713,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546100</v>
+        <v>546062</v>
       </c>
       <c r="R96" t="n">
-        <v>6999268</v>
+        <v>6999442</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12799,10 +12800,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131273362</v>
+        <v>131275135</v>
       </c>
       <c r="B97" t="n">
-        <v>91814</v>
+        <v>57884</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,28 +12811,29 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -12841,10 +12843,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546302</v>
+        <v>546142</v>
       </c>
       <c r="R97" t="n">
-        <v>6999463</v>
+        <v>6999047</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12881,7 +12883,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12890,7 +12892,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12909,14 +12910,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12934,7 +12930,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131273366</v>
+        <v>131275158</v>
       </c>
       <c r="B98" t="n">
         <v>57884</v>
@@ -12980,7 +12976,7 @@
         <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999258</v>
+        <v>6999268</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13017,7 +13013,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13044,14 +13040,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13069,47 +13060,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131275217</v>
+        <v>131273366</v>
       </c>
       <c r="B99" t="n">
-        <v>83213</v>
+        <v>57884</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -13119,10 +13103,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546307</v>
+        <v>546100</v>
       </c>
       <c r="R99" t="n">
-        <v>6999069</v>
+        <v>6999258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13159,7 +13143,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13168,7 +13152,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13177,34 +13160,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13222,37 +13195,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131275209</v>
+        <v>131275217</v>
       </c>
       <c r="B100" t="n">
-        <v>80311</v>
+        <v>83213</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229497</v>
+        <v>307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13260,10 +13245,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546171</v>
+        <v>546307</v>
       </c>
       <c r="R100" t="n">
-        <v>6999219</v>
+        <v>6999069</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13298,6 +13283,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -13313,6 +13303,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ100" t="inlineStr">
         <is>
           <t>asp</t>
@@ -13323,14 +13318,19 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -15051,37 +15051,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131275167</v>
+        <v>131273363</v>
       </c>
       <c r="B114" t="n">
-        <v>80217</v>
+        <v>92536</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>388</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15089,10 +15093,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546468</v>
+        <v>546304</v>
       </c>
       <c r="R114" t="n">
-        <v>6999037</v>
+        <v>6999379</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15127,6 +15131,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -15144,17 +15153,22 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15172,34 +15186,30 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131273363</v>
+        <v>131275212</v>
       </c>
       <c r="B115" t="n">
-        <v>92536</v>
+        <v>91834</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
@@ -15214,10 +15224,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546304</v>
+        <v>546213</v>
       </c>
       <c r="R115" t="n">
-        <v>6999379</v>
+        <v>6999022</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15252,11 +15262,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15282,14 +15287,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131275212</v>
+        <v>131275167</v>
       </c>
       <c r="B116" t="n">
-        <v>91834</v>
+        <v>80217</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15318,26 +15318,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546213</v>
+        <v>546468</v>
       </c>
       <c r="R116" t="n">
-        <v>6999022</v>
+        <v>6999037</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15400,17 +15400,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131273387</v>
+        <v>131275166</v>
       </c>
       <c r="B117" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15439,28 +15439,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15470,10 +15471,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546286</v>
+        <v>546208</v>
       </c>
       <c r="R117" t="n">
-        <v>6999419</v>
+        <v>6999393</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15510,7 +15511,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15519,7 +15520,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15530,22 +15530,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15563,10 +15558,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131275166</v>
+        <v>131273418</v>
       </c>
       <c r="B118" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15574,31 +15569,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15606,10 +15596,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546208</v>
+        <v>546329</v>
       </c>
       <c r="R118" t="n">
-        <v>6999393</v>
+        <v>6999224</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15646,7 +15636,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15655,6 +15645,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -15693,32 +15684,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131273418</v>
+        <v>131275174</v>
       </c>
       <c r="B119" t="n">
-        <v>79246</v>
+        <v>75224</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15731,10 +15722,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546329</v>
+        <v>546222</v>
       </c>
       <c r="R119" t="n">
-        <v>6999224</v>
+        <v>6999408</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15771,7 +15762,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15791,17 +15782,22 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15819,37 +15815,41 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275174</v>
+        <v>131273387</v>
       </c>
       <c r="B120" t="n">
-        <v>75224</v>
+        <v>80351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15857,10 +15857,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546222</v>
+        <v>546286</v>
       </c>
       <c r="R120" t="n">
-        <v>6999408</v>
+        <v>6999419</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -20696,10 +20696,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131273403</v>
+        <v>131273417</v>
       </c>
       <c r="B158" t="n">
-        <v>80351</v>
+        <v>79246</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20707,21 +20707,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -20734,10 +20734,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>546109</v>
+        <v>546334</v>
       </c>
       <c r="R158" t="n">
-        <v>6999309</v>
+        <v>6999084</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20827,7 +20827,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131273400</v>
+        <v>131273403</v>
       </c>
       <c r="B159" t="n">
         <v>80351</v>
@@ -20865,10 +20865,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>546297</v>
+        <v>546109</v>
       </c>
       <c r="R159" t="n">
-        <v>6999244</v>
+        <v>6999309</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20905,7 +20905,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Lunglav på en liten gran.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20925,22 +20925,22 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -20958,10 +20958,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131273417</v>
+        <v>131273400</v>
       </c>
       <c r="B160" t="n">
-        <v>79246</v>
+        <v>80351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20969,21 +20969,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>546334</v>
+        <v>546297</v>
       </c>
       <c r="R160" t="n">
-        <v>6999084</v>
+        <v>6999244</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -21056,22 +21056,22 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131273413</v>
+        <v>131273397</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546491</v>
+        <v>546296</v>
       </c>
       <c r="R2" t="n">
-        <v>6998962</v>
+        <v>6999259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131273422</v>
+        <v>131275180</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546111</v>
+        <v>546406</v>
       </c>
       <c r="R3" t="n">
-        <v>6999297</v>
+        <v>6999201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,17 +904,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275215</v>
+        <v>131275187</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546164</v>
+        <v>546202</v>
       </c>
       <c r="R4" t="n">
-        <v>6999199</v>
+        <v>6999223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,17 +1030,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131273397</v>
+        <v>131273413</v>
       </c>
       <c r="B5" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1069,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546296</v>
+        <v>546491</v>
       </c>
       <c r="R5" t="n">
-        <v>6999259</v>
+        <v>6998962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,11 +1134,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1146,22 +1151,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275180</v>
+        <v>131275215</v>
       </c>
       <c r="B6" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546406</v>
+        <v>546164</v>
       </c>
       <c r="R6" t="n">
-        <v>6999201</v>
+        <v>6999199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131275187</v>
+        <v>131275160</v>
       </c>
       <c r="B7" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1316,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546202</v>
+        <v>546104</v>
       </c>
       <c r="R7" t="n">
-        <v>6999223</v>
+        <v>6999263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1388,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1397,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,17 +1407,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273378</v>
+        <v>131273422</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,31 +1446,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1474,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546094</v>
+        <v>546111</v>
       </c>
       <c r="R8" t="n">
-        <v>6999329</v>
+        <v>6999297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1513,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,6 +1522,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,14 +1541,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1569,7 +1564,7 @@
         <v>131275145</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1696,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275160</v>
+        <v>131273378</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1724,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1739,10 +1734,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546104</v>
+        <v>546094</v>
       </c>
       <c r="R10" t="n">
-        <v>6999263</v>
+        <v>6999329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,9 +1801,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
         <v>131276476</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273391</v>
+        <v>131273421</v>
       </c>
       <c r="B12" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,30 +1967,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1998,10 +1994,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546459</v>
+        <v>546167</v>
       </c>
       <c r="R12" t="n">
-        <v>6998921</v>
+        <v>6999264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2053,22 +2049,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2086,10 +2077,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131275185</v>
+        <v>131273391</v>
       </c>
       <c r="B13" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2116,7 +2107,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2124,10 +2119,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546230</v>
+        <v>546459</v>
       </c>
       <c r="R13" t="n">
-        <v>6999202</v>
+        <v>6998921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2162,11 +2157,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2184,12 +2174,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2199,7 +2189,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2217,10 +2207,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131273407</v>
+        <v>131275185</v>
       </c>
       <c r="B14" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,11 +2237,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2259,10 +2245,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546227</v>
+        <v>546230</v>
       </c>
       <c r="R14" t="n">
-        <v>6999437</v>
+        <v>6999202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2299,7 +2285,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,12 +2305,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2334,7 +2320,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2352,10 +2338,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131276484</v>
+        <v>131273407</v>
       </c>
       <c r="B15" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2382,7 +2368,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2390,10 +2380,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546500</v>
+        <v>546227</v>
       </c>
       <c r="R15" t="n">
-        <v>6998983</v>
+        <v>6999437</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2426,6 +2416,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2478,10 +2473,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131275184</v>
+        <v>131276484</v>
       </c>
       <c r="B16" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546300</v>
+        <v>546500</v>
       </c>
       <c r="R16" t="n">
-        <v>6999066</v>
+        <v>6998983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,6 +2562,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,10 +2599,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131273421</v>
+        <v>131275184</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,21 +2610,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2622,10 +2637,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546167</v>
+        <v>546300</v>
       </c>
       <c r="R17" t="n">
-        <v>6999264</v>
+        <v>6999066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,21 +2688,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
         <v>131275192</v>
       </c>
       <c r="B18" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131273396</v>
       </c>
       <c r="B19" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131273375</v>
+        <v>131275156</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546088</v>
+        <v>546115</v>
       </c>
       <c r="R20" t="n">
-        <v>6999337</v>
+        <v>6999245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3081,14 +3081,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3106,10 +3101,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131275142</v>
+        <v>131273375</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3149,10 +3144,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546139</v>
+        <v>546088</v>
       </c>
       <c r="R21" t="n">
-        <v>6999063</v>
+        <v>6999337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3189,7 +3184,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3216,9 +3211,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131275131</v>
+        <v>131273368</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546445</v>
+        <v>546097</v>
       </c>
       <c r="R22" t="n">
-        <v>6998989</v>
+        <v>6999266</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3366,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131275156</v>
+        <v>131275142</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546115</v>
+        <v>546139</v>
       </c>
       <c r="R23" t="n">
-        <v>6999245</v>
+        <v>6999063</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131273368</v>
+        <v>131275153</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546097</v>
+        <v>546126</v>
       </c>
       <c r="R24" t="n">
-        <v>6999266</v>
+        <v>6999216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131275150</v>
+        <v>131275131</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3669,10 +3669,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546123</v>
+        <v>546445</v>
       </c>
       <c r="R25" t="n">
-        <v>6999192</v>
+        <v>6998989</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3756,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131275153</v>
+        <v>131275150</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546126</v>
+        <v>546123</v>
       </c>
       <c r="R26" t="n">
-        <v>6999216</v>
+        <v>6999192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3889,7 +3889,7 @@
         <v>131275163</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131275191</v>
+        <v>131275176</v>
       </c>
       <c r="B28" t="n">
-        <v>80353</v>
+        <v>75339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546174</v>
+        <v>546399</v>
       </c>
       <c r="R28" t="n">
-        <v>6999215</v>
+        <v>6998994</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4092,11 +4092,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4114,12 +4109,12 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -4129,7 +4124,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4147,10 +4142,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275201</v>
+        <v>131275175</v>
       </c>
       <c r="B29" t="n">
-        <v>80353</v>
+        <v>75339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4158,21 +4153,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4185,10 +4180,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546222</v>
+        <v>546372</v>
       </c>
       <c r="R29" t="n">
-        <v>6999418</v>
+        <v>6998999</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4223,6 +4218,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark av gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275178</v>
+        <v>131275191</v>
       </c>
       <c r="B30" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546403</v>
+        <v>546174</v>
       </c>
       <c r="R30" t="n">
-        <v>6999213</v>
+        <v>6999215</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4349,6 +4349,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4362,6 +4367,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4379,10 +4404,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275176</v>
+        <v>131275201</v>
       </c>
       <c r="B31" t="n">
-        <v>75338</v>
+        <v>80354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4390,21 +4415,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4417,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546399</v>
+        <v>546222</v>
       </c>
       <c r="R31" t="n">
-        <v>6998994</v>
+        <v>6999418</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4472,12 +4497,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4487,7 +4512,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4505,10 +4530,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275175</v>
+        <v>131275178</v>
       </c>
       <c r="B32" t="n">
-        <v>75338</v>
+        <v>80354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4516,21 +4541,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4543,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546372</v>
+        <v>546403</v>
       </c>
       <c r="R32" t="n">
-        <v>6998999</v>
+        <v>6999213</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4581,11 +4606,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På bark av gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4599,26 +4619,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
         <v>131275206</v>
       </c>
       <c r="B33" t="n">
-        <v>78260</v>
+        <v>78261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>131276490</v>
       </c>
       <c r="B34" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>131276489</v>
       </c>
       <c r="B35" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>131275193</v>
       </c>
       <c r="B36" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>131273389</v>
       </c>
       <c r="B37" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>131276492</v>
       </c>
       <c r="B38" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131273365</v>
+        <v>131275155</v>
       </c>
       <c r="B39" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546239</v>
+        <v>546116</v>
       </c>
       <c r="R39" t="n">
-        <v>6999263</v>
+        <v>6999243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5483,14 +5483,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5508,10 +5503,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131275146</v>
+        <v>131275152</v>
       </c>
       <c r="B40" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5551,10 +5546,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546130</v>
+        <v>546122</v>
       </c>
       <c r="R40" t="n">
-        <v>6999093</v>
+        <v>6999205</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5638,10 +5633,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131275152</v>
+        <v>131275146</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5681,10 +5676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546122</v>
+        <v>546130</v>
       </c>
       <c r="R41" t="n">
-        <v>6999205</v>
+        <v>6999093</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5768,10 +5763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131275155</v>
+        <v>131273365</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5801,7 +5796,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5811,10 +5806,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546116</v>
+        <v>546239</v>
       </c>
       <c r="R42" t="n">
-        <v>6999243</v>
+        <v>6999263</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5851,7 +5846,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5878,9 +5873,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131275182</v>
+        <v>131275159</v>
       </c>
       <c r="B43" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5909,26 +5909,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5936,10 +5941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546357</v>
+        <v>546099</v>
       </c>
       <c r="R43" t="n">
-        <v>6999022</v>
+        <v>6999277</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5974,19 +5979,38 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6004,10 +6028,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131276487</v>
+        <v>131275151</v>
       </c>
       <c r="B44" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6015,26 +6039,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6042,10 +6071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546313</v>
+        <v>546124</v>
       </c>
       <c r="R44" t="n">
-        <v>6999060</v>
+        <v>6999206</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6080,13 +6109,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6097,22 +6130,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6130,39 +6158,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131273381</v>
+        <v>131276478</v>
       </c>
       <c r="B45" t="n">
-        <v>80382</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6172,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546353</v>
+        <v>546058</v>
       </c>
       <c r="R45" t="n">
-        <v>6999084</v>
+        <v>6999435</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6212,7 +6241,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6221,7 +6250,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6232,22 +6260,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6265,10 +6288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131275194</v>
+        <v>131273410</v>
       </c>
       <c r="B46" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6276,21 +6299,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6303,10 +6326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546153</v>
+        <v>546342</v>
       </c>
       <c r="R46" t="n">
-        <v>6999210</v>
+        <v>6999195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6341,11 +6364,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6363,22 +6381,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6396,10 +6409,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131273410</v>
+        <v>131273426</v>
       </c>
       <c r="B47" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6434,10 +6447,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546342</v>
+        <v>546172</v>
       </c>
       <c r="R47" t="n">
-        <v>6999195</v>
+        <v>6999385</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6470,6 +6483,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6517,10 +6535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131273426</v>
+        <v>131275213</v>
       </c>
       <c r="B48" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6555,10 +6573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546172</v>
+        <v>546481</v>
       </c>
       <c r="R48" t="n">
-        <v>6999385</v>
+        <v>6998980</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6591,11 +6609,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6643,10 +6656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131273401</v>
+        <v>131275182</v>
       </c>
       <c r="B49" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6673,11 +6686,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6685,10 +6694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546279</v>
+        <v>546357</v>
       </c>
       <c r="R49" t="n">
-        <v>6999244</v>
+        <v>6999022</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6723,11 +6732,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6741,26 +6745,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6778,10 +6762,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131273406</v>
+        <v>131276487</v>
       </c>
       <c r="B50" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6816,10 +6800,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546223</v>
+        <v>546313</v>
       </c>
       <c r="R50" t="n">
-        <v>6999436</v>
+        <v>6999060</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6854,11 +6838,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6876,22 +6855,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6909,37 +6888,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131275213</v>
+        <v>131273381</v>
       </c>
       <c r="B51" t="n">
-        <v>79248</v>
+        <v>80383</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6947,10 +6930,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546481</v>
+        <v>546353</v>
       </c>
       <c r="R51" t="n">
-        <v>6998980</v>
+        <v>6999084</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6985,6 +6968,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7002,17 +6990,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7030,10 +7023,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131273374</v>
+        <v>131275194</v>
       </c>
       <c r="B52" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7041,31 +7034,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7073,10 +7061,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546094</v>
+        <v>546153</v>
       </c>
       <c r="R52" t="n">
-        <v>6999322</v>
+        <v>6999210</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7113,7 +7101,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7122,6 +7110,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7132,22 +7121,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7165,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131275151</v>
+        <v>131273401</v>
       </c>
       <c r="B53" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7176,29 +7165,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7208,10 +7196,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546124</v>
+        <v>546279</v>
       </c>
       <c r="R53" t="n">
-        <v>6999206</v>
+        <v>6999244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7248,7 +7236,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7257,6 +7245,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7267,17 +7256,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7295,10 +7289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131276478</v>
+        <v>131273406</v>
       </c>
       <c r="B54" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7306,31 +7300,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7338,10 +7327,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546058</v>
+        <v>546223</v>
       </c>
       <c r="R54" t="n">
-        <v>6999435</v>
+        <v>6999436</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7378,7 +7367,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7387,6 +7376,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7405,9 +7395,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7425,10 +7420,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131275159</v>
+        <v>131273374</v>
       </c>
       <c r="B55" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7458,7 +7453,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7468,10 +7463,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546099</v>
+        <v>546094</v>
       </c>
       <c r="R55" t="n">
-        <v>6999277</v>
+        <v>6999322</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7508,7 +7503,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7535,9 +7530,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7558,7 +7558,7 @@
         <v>131275139</v>
       </c>
       <c r="B56" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131275195</v>
+        <v>131273412</v>
       </c>
       <c r="B57" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,21 +7696,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546150</v>
+        <v>546441</v>
       </c>
       <c r="R57" t="n">
-        <v>6999197</v>
+        <v>6999013</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7778,22 +7778,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7811,10 +7806,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131273394</v>
+        <v>131275195</v>
       </c>
       <c r="B58" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7841,11 +7836,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7853,10 +7844,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546346</v>
+        <v>546150</v>
       </c>
       <c r="R58" t="n">
-        <v>6999078</v>
+        <v>6999197</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7891,11 +7882,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7913,12 +7899,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7928,7 +7914,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7946,10 +7932,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131276488</v>
+        <v>131273394</v>
       </c>
       <c r="B59" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7976,7 +7962,11 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7984,10 +7974,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546062</v>
+        <v>546346</v>
       </c>
       <c r="R59" t="n">
-        <v>6999441</v>
+        <v>6999078</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8020,6 +8010,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8072,10 +8067,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276491</v>
+        <v>131276488</v>
       </c>
       <c r="B60" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546074</v>
+        <v>546062</v>
       </c>
       <c r="R60" t="n">
-        <v>6999366</v>
+        <v>6999441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8198,10 +8193,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131273412</v>
+        <v>131276491</v>
       </c>
       <c r="B61" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8209,21 +8204,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8236,10 +8231,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546441</v>
+        <v>546074</v>
       </c>
       <c r="R61" t="n">
-        <v>6999013</v>
+        <v>6999366</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8291,17 +8286,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8319,10 +8319,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131275129</v>
+        <v>131276475</v>
       </c>
       <c r="B62" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
         <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999380</v>
+        <v>6999168</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8449,10 +8449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131273373</v>
+        <v>131275129</v>
       </c>
       <c r="B63" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546097</v>
+        <v>546338</v>
       </c>
       <c r="R63" t="n">
-        <v>6999307</v>
+        <v>6999380</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8559,14 +8559,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8584,10 +8579,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276475</v>
+        <v>131273373</v>
       </c>
       <c r="B64" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8617,7 +8612,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8627,10 +8622,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546338</v>
+        <v>546097</v>
       </c>
       <c r="R64" t="n">
-        <v>6999168</v>
+        <v>6999307</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8667,7 +8662,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8694,9 +8689,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131275211</v>
+        <v>131275200</v>
       </c>
       <c r="B65" t="n">
-        <v>91836</v>
+        <v>80354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546185</v>
+        <v>546174</v>
       </c>
       <c r="R65" t="n">
-        <v>6999135</v>
+        <v>6999354</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8807,17 +8807,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8835,10 +8840,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273414</v>
+        <v>131273384</v>
       </c>
       <c r="B66" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8846,37 +8851,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546430</v>
+        <v>546286</v>
       </c>
       <c r="R66" t="n">
-        <v>6998969</v>
+        <v>6999257</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8911,35 +8913,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fertil med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8956,10 +8942,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131276481</v>
+        <v>131273386</v>
       </c>
       <c r="B67" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8967,29 +8953,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8999,10 +8984,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546070</v>
+        <v>546294</v>
       </c>
       <c r="R67" t="n">
-        <v>6999374</v>
+        <v>6999434</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9039,7 +9024,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9048,6 +9033,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9058,17 +9044,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9086,10 +9077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131275200</v>
+        <v>131273414</v>
       </c>
       <c r="B68" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9097,21 +9088,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9124,10 +9115,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546174</v>
+        <v>546430</v>
       </c>
       <c r="R68" t="n">
-        <v>6999354</v>
+        <v>6998969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9179,22 +9170,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9212,10 +9198,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273384</v>
+        <v>131273420</v>
       </c>
       <c r="B69" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9223,34 +9209,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546286</v>
+        <v>546204</v>
       </c>
       <c r="R69" t="n">
-        <v>6999257</v>
+        <v>6999267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9287,7 +9276,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9296,8 +9285,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9314,10 +9324,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273420</v>
+        <v>131273416</v>
       </c>
       <c r="B70" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9352,10 +9362,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546204</v>
+        <v>546387</v>
       </c>
       <c r="R70" t="n">
-        <v>6999267</v>
+        <v>6999068</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9392,7 +9402,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9440,10 +9450,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273386</v>
+        <v>131276481</v>
       </c>
       <c r="B71" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9451,28 +9461,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9482,10 +9493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546294</v>
+        <v>546070</v>
       </c>
       <c r="R71" t="n">
-        <v>6999434</v>
+        <v>6999374</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9522,7 +9533,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9531,7 +9542,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9542,22 +9552,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9575,10 +9580,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273416</v>
+        <v>131275211</v>
       </c>
       <c r="B72" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,26 +9591,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9613,10 +9618,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546387</v>
+        <v>546185</v>
       </c>
       <c r="R72" t="n">
-        <v>6999068</v>
+        <v>6999135</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9649,11 +9654,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9704,7 +9704,7 @@
         <v>131273371</v>
       </c>
       <c r="B73" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>131273372</v>
       </c>
       <c r="B74" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>131276486</v>
       </c>
       <c r="B75" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>131275181</v>
       </c>
       <c r="B76" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>131273393</v>
       </c>
       <c r="B77" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>131275202</v>
       </c>
       <c r="B78" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>131273402</v>
       </c>
       <c r="B79" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>131273392</v>
       </c>
       <c r="B80" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>131276482</v>
       </c>
       <c r="B81" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10866,10 +10866,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131275132</v>
+        <v>131275144</v>
       </c>
       <c r="B82" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10894,37 +10894,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>546295</v>
+        <v>546124</v>
       </c>
       <c r="R82" t="n">
-        <v>6999077</v>
+        <v>6999127</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10961,7 +10949,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10978,9 +10966,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Äldre granskog med höga naturvärden.</t>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10998,10 +10996,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131275144</v>
+        <v>131275132</v>
       </c>
       <c r="B83" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11026,25 +11024,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>546124</v>
+        <v>546295</v>
       </c>
       <c r="R83" t="n">
-        <v>6999127</v>
+        <v>6999077</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11081,7 +11091,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11098,19 +11108,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11131,7 +11131,7 @@
         <v>131275170</v>
       </c>
       <c r="B84" t="n">
-        <v>83219</v>
+        <v>83220</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>131275204</v>
       </c>
       <c r="B85" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>131276483</v>
       </c>
       <c r="B86" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>131275205</v>
       </c>
       <c r="B87" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>131273388</v>
       </c>
       <c r="B88" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>131275188</v>
       </c>
       <c r="B89" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>131275161</v>
       </c>
       <c r="B90" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>131275165</v>
       </c>
       <c r="B91" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>131275164</v>
       </c>
       <c r="B92" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>131273362</v>
       </c>
       <c r="B93" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12418,10 +12418,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131276477</v>
+        <v>131275135</v>
       </c>
       <c r="B94" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12461,10 +12461,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546062</v>
+        <v>546142</v>
       </c>
       <c r="R94" t="n">
-        <v>6999442</v>
+        <v>6999047</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12548,10 +12548,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275135</v>
+        <v>131273366</v>
       </c>
       <c r="B95" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546142</v>
+        <v>546100</v>
       </c>
       <c r="R95" t="n">
-        <v>6999047</v>
+        <v>6999258</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12658,9 +12658,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12678,40 +12683,47 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131275158</v>
+        <v>131275217</v>
       </c>
       <c r="B96" t="n">
-        <v>57886</v>
+        <v>83216</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -12721,10 +12733,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546100</v>
+        <v>546307</v>
       </c>
       <c r="R96" t="n">
-        <v>6999268</v>
+        <v>6999069</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12761,7 +12773,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12770,6 +12782,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12778,19 +12791,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12808,10 +12836,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131273366</v>
+        <v>131273424</v>
       </c>
       <c r="B97" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12819,31 +12847,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12851,10 +12874,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546100</v>
+        <v>546090</v>
       </c>
       <c r="R97" t="n">
-        <v>6999258</v>
+        <v>6999323</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12891,7 +12914,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12900,6 +12923,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12918,14 +12942,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12943,37 +12962,42 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131275209</v>
+        <v>131275158</v>
       </c>
       <c r="B98" t="n">
-        <v>80313</v>
+        <v>57887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -12981,10 +13005,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546171</v>
+        <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999219</v>
+        <v>6999268</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13019,13 +13043,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13036,22 +13064,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13069,47 +13092,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131275217</v>
+        <v>131276477</v>
       </c>
       <c r="B99" t="n">
-        <v>83215</v>
+        <v>57887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -13119,10 +13135,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546307</v>
+        <v>546062</v>
       </c>
       <c r="R99" t="n">
-        <v>6999069</v>
+        <v>6999442</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13159,7 +13175,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13168,7 +13184,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13177,34 +13192,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13222,32 +13222,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131273424</v>
+        <v>131275209</v>
       </c>
       <c r="B100" t="n">
-        <v>79248</v>
+        <v>80314</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13260,10 +13260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546090</v>
+        <v>546171</v>
       </c>
       <c r="R100" t="n">
-        <v>6999323</v>
+        <v>6999219</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13298,11 +13298,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -13320,17 +13315,22 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131275207</v>
+        <v>131273409</v>
       </c>
       <c r="B101" t="n">
-        <v>78260</v>
+        <v>91837</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,26 +13359,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546365</v>
+        <v>546299</v>
       </c>
       <c r="R101" t="n">
-        <v>6998993</v>
+        <v>6999454</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13424,6 +13424,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -13449,9 +13454,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13469,10 +13479,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273419</v>
+        <v>131273380</v>
       </c>
       <c r="B102" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13480,26 +13490,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13507,10 +13522,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546230</v>
+        <v>546091</v>
       </c>
       <c r="R102" t="n">
-        <v>6999267</v>
+        <v>6999334</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13547,7 +13562,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13556,13 +13571,12 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13575,19 +13589,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13605,10 +13614,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131273395</v>
+        <v>131273419</v>
       </c>
       <c r="B103" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13616,21 +13625,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13643,10 +13652,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546313</v>
+        <v>546230</v>
       </c>
       <c r="R103" t="n">
-        <v>6999066</v>
+        <v>6999267</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13683,7 +13692,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13698,7 +13707,7 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -13711,6 +13720,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
       <c r="AM103" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -13718,7 +13732,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13736,10 +13750,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131273409</v>
+        <v>131273395</v>
       </c>
       <c r="B104" t="n">
-        <v>91836</v>
+        <v>80354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13747,26 +13761,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13774,10 +13788,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546299</v>
+        <v>546313</v>
       </c>
       <c r="R104" t="n">
-        <v>6999454</v>
+        <v>6999066</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13814,7 +13828,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13844,12 +13858,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13870,7 +13884,7 @@
         <v>131275137</v>
       </c>
       <c r="B105" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13997,10 +14011,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131273380</v>
+        <v>131273377</v>
       </c>
       <c r="B106" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,10 +14054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546091</v>
+        <v>546077</v>
       </c>
       <c r="R106" t="n">
-        <v>6999334</v>
+        <v>6999352</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14080,7 +14094,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14132,10 +14146,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131273377</v>
+        <v>131275207</v>
       </c>
       <c r="B107" t="n">
-        <v>57886</v>
+        <v>78261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14143,31 +14157,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14175,10 +14184,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546077</v>
+        <v>546365</v>
       </c>
       <c r="R107" t="n">
-        <v>6999352</v>
+        <v>6998993</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14213,17 +14222,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -14242,14 +14247,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14270,7 +14270,7 @@
         <v>131275172</v>
       </c>
       <c r="B108" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>131275190</v>
       </c>
       <c r="B109" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14519,27 +14519,27 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131273382</v>
+        <v>131273379</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14547,37 +14547,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>546360</v>
+        <v>546099</v>
       </c>
       <c r="R110" t="n">
-        <v>6999087</v>
+        <v>6999326</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14614,7 +14602,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14631,9 +14619,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14654,7 +14657,7 @@
         <v>131275143</v>
       </c>
       <c r="B111" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14781,27 +14784,27 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131273379</v>
+        <v>131273382</v>
       </c>
       <c r="B112" t="n">
-        <v>57886</v>
+        <v>57728</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -14809,25 +14812,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>546099</v>
+        <v>546360</v>
       </c>
       <c r="R112" t="n">
-        <v>6999326</v>
+        <v>6999087</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14864,7 +14879,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14881,24 +14896,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14919,7 +14919,7 @@
         <v>131273376</v>
       </c>
       <c r="B113" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15051,10 +15051,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131275166</v>
+        <v>131273418</v>
       </c>
       <c r="B114" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15062,31 +15062,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15094,10 +15089,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546208</v>
+        <v>546329</v>
       </c>
       <c r="R114" t="n">
-        <v>6999393</v>
+        <v>6999224</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15134,7 +15129,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15143,6 +15138,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -15181,32 +15177,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275167</v>
+        <v>131275174</v>
       </c>
       <c r="B115" t="n">
-        <v>80219</v>
+        <v>75227</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>388</v>
+        <v>6428</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15219,10 +15215,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546468</v>
+        <v>546222</v>
       </c>
       <c r="R115" t="n">
-        <v>6999037</v>
+        <v>6999408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15257,6 +15253,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15274,17 +15275,22 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15302,41 +15308,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273363</v>
+        <v>131275167</v>
       </c>
       <c r="B116" t="n">
-        <v>92538</v>
+        <v>80220</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>388</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15344,10 +15346,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546304</v>
+        <v>546468</v>
       </c>
       <c r="R116" t="n">
-        <v>6999379</v>
+        <v>6999037</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15382,11 +15384,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -15404,22 +15401,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15437,30 +15429,34 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275212</v>
+        <v>131273363</v>
       </c>
       <c r="B117" t="n">
-        <v>91836</v>
+        <v>92539</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
@@ -15475,10 +15471,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546213</v>
+        <v>546304</v>
       </c>
       <c r="R117" t="n">
-        <v>6999022</v>
+        <v>6999379</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15513,6 +15509,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -15538,9 +15539,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15558,10 +15564,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131273418</v>
+        <v>131273387</v>
       </c>
       <c r="B118" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15569,26 +15575,30 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15596,10 +15606,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546329</v>
+        <v>546286</v>
       </c>
       <c r="R118" t="n">
-        <v>6999224</v>
+        <v>6999419</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15636,7 +15646,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15656,17 +15666,22 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15684,10 +15699,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131273387</v>
+        <v>131275212</v>
       </c>
       <c r="B119" t="n">
-        <v>80353</v>
+        <v>91837</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15695,28 +15710,24 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -15726,10 +15737,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546286</v>
+        <v>546213</v>
       </c>
       <c r="R119" t="n">
-        <v>6999419</v>
+        <v>6999022</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15764,11 +15775,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -15786,22 +15792,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15819,37 +15820,42 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275174</v>
+        <v>131275166</v>
       </c>
       <c r="B120" t="n">
-        <v>75226</v>
+        <v>57887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15857,10 +15863,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546222</v>
+        <v>546208</v>
       </c>
       <c r="R120" t="n">
-        <v>6999408</v>
+        <v>6999393</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15897,7 +15903,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15906,7 +15912,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -15917,22 +15922,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15953,7 +15953,7 @@
         <v>131273385</v>
       </c>
       <c r="B121" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>131275216</v>
       </c>
       <c r="B122" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>131275148</v>
       </c>
       <c r="B123" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>131275133</v>
       </c>
       <c r="B124" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16471,10 +16471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131275134</v>
+        <v>131275199</v>
       </c>
       <c r="B125" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16482,31 +16482,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -16514,10 +16509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546141</v>
+        <v>546147</v>
       </c>
       <c r="R125" t="n">
-        <v>6999039</v>
+        <v>6999326</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16552,17 +16547,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -16581,9 +16572,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16601,32 +16597,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131273383</v>
+        <v>131275171</v>
       </c>
       <c r="B126" t="n">
-        <v>80354</v>
+        <v>80258</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16639,10 +16635,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546292</v>
+        <v>546230</v>
       </c>
       <c r="R126" t="n">
-        <v>6999247</v>
+        <v>6999202</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16677,11 +16673,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Växer här på en lutande sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -16699,22 +16690,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16732,10 +16718,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275199</v>
+        <v>131275197</v>
       </c>
       <c r="B127" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16770,10 +16756,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546147</v>
+        <v>546130</v>
       </c>
       <c r="R127" t="n">
-        <v>6999326</v>
+        <v>6999313</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16825,22 +16811,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16858,10 +16844,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275171</v>
+        <v>131275173</v>
       </c>
       <c r="B128" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16896,10 +16882,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546230</v>
+        <v>546165</v>
       </c>
       <c r="R128" t="n">
-        <v>6999202</v>
+        <v>6999228</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16979,10 +16965,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131275197</v>
+        <v>131273383</v>
       </c>
       <c r="B129" t="n">
-        <v>80353</v>
+        <v>80355</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16990,21 +16976,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -17017,10 +17003,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546130</v>
+        <v>546292</v>
       </c>
       <c r="R129" t="n">
-        <v>6999313</v>
+        <v>6999247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17053,6 +17039,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Växer här på en lutande sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -17105,37 +17096,42 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131275173</v>
+        <v>131273364</v>
       </c>
       <c r="B130" t="n">
-        <v>80257</v>
+        <v>57887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -17143,10 +17139,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>546165</v>
+        <v>546403</v>
       </c>
       <c r="R130" t="n">
-        <v>6999228</v>
+        <v>6998994</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17181,13 +17177,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -17198,17 +17198,22 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -17226,10 +17231,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131273364</v>
+        <v>131275134</v>
       </c>
       <c r="B131" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17259,7 +17264,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -17269,10 +17274,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>546403</v>
+        <v>546141</v>
       </c>
       <c r="R131" t="n">
-        <v>6998994</v>
+        <v>6999039</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17309,7 +17314,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17336,14 +17341,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -17364,7 +17364,7 @@
         <v>131273398</v>
       </c>
       <c r="B132" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>131275125</v>
       </c>
       <c r="B133" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>131273411</v>
       </c>
       <c r="B134" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>131273425</v>
       </c>
       <c r="B135" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>131275149</v>
       </c>
       <c r="B136" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>131273408</v>
       </c>
       <c r="B137" t="n">
-        <v>80389</v>
+        <v>80390</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>131273390</v>
       </c>
       <c r="B138" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>131275203</v>
       </c>
       <c r="B139" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18400,37 +18400,42 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131275208</v>
+        <v>131275136</v>
       </c>
       <c r="B140" t="n">
-        <v>80313</v>
+        <v>57887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -18438,10 +18443,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546460</v>
+        <v>546148</v>
       </c>
       <c r="R140" t="n">
-        <v>6999073</v>
+        <v>6999041</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18476,13 +18481,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -18493,22 +18502,17 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -18526,10 +18530,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131275147</v>
+        <v>131275138</v>
       </c>
       <c r="B141" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18569,10 +18573,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546137</v>
+        <v>546145</v>
       </c>
       <c r="R141" t="n">
-        <v>6999148</v>
+        <v>6999053</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18656,10 +18660,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275136</v>
+        <v>131275147</v>
       </c>
       <c r="B142" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18699,10 +18703,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546148</v>
+        <v>546137</v>
       </c>
       <c r="R142" t="n">
-        <v>6999041</v>
+        <v>6999148</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18786,42 +18790,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131275138</v>
+        <v>131275208</v>
       </c>
       <c r="B143" t="n">
-        <v>57886</v>
+        <v>80314</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -18829,10 +18828,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>546145</v>
+        <v>546460</v>
       </c>
       <c r="R143" t="n">
-        <v>6999053</v>
+        <v>6999073</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18867,17 +18866,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -18888,17 +18883,22 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -18916,10 +18916,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131275186</v>
+        <v>131275214</v>
       </c>
       <c r="B144" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18927,21 +18927,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -18954,10 +18954,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>546206</v>
+        <v>546193</v>
       </c>
       <c r="R144" t="n">
-        <v>6999203</v>
+        <v>6999241</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18992,11 +18992,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -19014,22 +19009,17 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -19047,10 +19037,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131276485</v>
+        <v>131275186</v>
       </c>
       <c r="B145" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19085,10 +19075,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>546409</v>
+        <v>546206</v>
       </c>
       <c r="R145" t="n">
-        <v>6999005</v>
+        <v>6999203</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -19121,6 +19111,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -19173,10 +19168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131275183</v>
+        <v>131276485</v>
       </c>
       <c r="B146" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19211,10 +19206,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>546345</v>
+        <v>546409</v>
       </c>
       <c r="R146" t="n">
-        <v>6999035</v>
+        <v>6999005</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19262,6 +19257,26 @@
       <c r="AH146" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -19279,10 +19294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275214</v>
+        <v>131275183</v>
       </c>
       <c r="B147" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19290,21 +19305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19317,10 +19332,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546193</v>
+        <v>546345</v>
       </c>
       <c r="R147" t="n">
-        <v>6999241</v>
+        <v>6999035</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19368,21 +19383,6 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19400,37 +19400,42 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131275210</v>
+        <v>131273367</v>
       </c>
       <c r="B148" t="n">
-        <v>80313</v>
+        <v>57887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -19438,10 +19443,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546168</v>
+        <v>546103</v>
       </c>
       <c r="R148" t="n">
-        <v>6999217</v>
+        <v>6999266</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19476,13 +19481,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -19493,22 +19502,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19526,42 +19535,37 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131276480</v>
+        <v>131275210</v>
       </c>
       <c r="B149" t="n">
-        <v>57886</v>
+        <v>80314</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -19569,10 +19573,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546066</v>
+        <v>546168</v>
       </c>
       <c r="R149" t="n">
-        <v>6999401</v>
+        <v>6999217</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19607,17 +19611,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -19628,17 +19628,22 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19656,10 +19661,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131273367</v>
+        <v>131276479</v>
       </c>
       <c r="B150" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19699,10 +19704,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546103</v>
+        <v>546062</v>
       </c>
       <c r="R150" t="n">
-        <v>6999266</v>
+        <v>6999415</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19739,7 +19744,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -19766,14 +19771,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -19791,10 +19791,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131276479</v>
+        <v>131276480</v>
       </c>
       <c r="B151" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19834,10 +19834,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546062</v>
+        <v>546066</v>
       </c>
       <c r="R151" t="n">
-        <v>6999415</v>
+        <v>6999401</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19921,10 +19921,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131275130</v>
+        <v>131275177</v>
       </c>
       <c r="B152" t="n">
-        <v>57886</v>
+        <v>83224</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19932,31 +19932,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -19964,10 +19959,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546460</v>
+        <v>546303</v>
       </c>
       <c r="R152" t="n">
-        <v>6999069</v>
+        <v>6999065</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -20004,7 +19999,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20013,6 +20008,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -20021,19 +20017,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20051,10 +20057,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275177</v>
+        <v>131275189</v>
       </c>
       <c r="B153" t="n">
-        <v>83223</v>
+        <v>80354</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20062,21 +20068,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -20089,10 +20095,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546303</v>
+        <v>546224</v>
       </c>
       <c r="R153" t="n">
-        <v>6999065</v>
+        <v>6999013</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20129,7 +20135,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20147,29 +20153,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -20187,10 +20188,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131275189</v>
+        <v>131273405</v>
       </c>
       <c r="B154" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20225,10 +20226,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>546224</v>
+        <v>546169</v>
       </c>
       <c r="R154" t="n">
-        <v>6999013</v>
+        <v>6999410</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -20265,7 +20266,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20285,12 +20286,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -20300,7 +20301,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -20318,10 +20319,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131273405</v>
+        <v>131275196</v>
       </c>
       <c r="B155" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20356,10 +20357,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>546169</v>
+        <v>546124</v>
       </c>
       <c r="R155" t="n">
-        <v>6999410</v>
+        <v>6999220</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -20392,11 +20393,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20449,10 +20445,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131275196</v>
+        <v>131275130</v>
       </c>
       <c r="B156" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20460,26 +20456,31 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -20487,10 +20488,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>546124</v>
+        <v>546460</v>
       </c>
       <c r="R156" t="n">
-        <v>6999220</v>
+        <v>6999069</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20525,13 +20526,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -20542,22 +20547,17 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -20575,10 +20575,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131273403</v>
+        <v>131275157</v>
       </c>
       <c r="B157" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20586,26 +20586,31 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -20613,10 +20618,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>546109</v>
+        <v>546111</v>
       </c>
       <c r="R157" t="n">
-        <v>6999309</v>
+        <v>6999255</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -20653,7 +20658,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -20662,7 +20667,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -20681,14 +20685,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -20706,10 +20705,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131273417</v>
+        <v>131275154</v>
       </c>
       <c r="B158" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20717,26 +20716,31 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -20744,10 +20748,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>546334</v>
+        <v>546118</v>
       </c>
       <c r="R158" t="n">
-        <v>6999084</v>
+        <v>6999237</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -20784,7 +20788,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20793,7 +20797,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -20812,14 +20815,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -20837,10 +20835,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131275141</v>
+        <v>131273403</v>
       </c>
       <c r="B159" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20848,31 +20846,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -20880,10 +20873,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>546148</v>
+        <v>546109</v>
       </c>
       <c r="R159" t="n">
-        <v>6999053</v>
+        <v>6999309</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20920,7 +20913,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Lunglav på en liten gran.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20929,6 +20922,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -20947,9 +20941,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -20967,10 +20966,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131275162</v>
+        <v>131273400</v>
       </c>
       <c r="B160" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20978,31 +20977,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -21010,10 +21004,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>546103</v>
+        <v>546297</v>
       </c>
       <c r="R160" t="n">
-        <v>6999294</v>
+        <v>6999244</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -21050,7 +21044,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -21059,6 +21053,7 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -21069,17 +21064,22 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -21097,10 +21097,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131275154</v>
+        <v>131275141</v>
       </c>
       <c r="B161" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21140,10 +21140,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>546118</v>
+        <v>546148</v>
       </c>
       <c r="R161" t="n">
-        <v>6999237</v>
+        <v>6999053</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -21227,10 +21227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131275157</v>
+        <v>131275162</v>
       </c>
       <c r="B162" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21270,10 +21270,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>546111</v>
+        <v>546103</v>
       </c>
       <c r="R162" t="n">
-        <v>6999255</v>
+        <v>6999294</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21360,7 +21360,7 @@
         <v>131275168</v>
       </c>
       <c r="B163" t="n">
-        <v>80219</v>
+        <v>80220</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21478,10 +21478,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131273400</v>
+        <v>131273417</v>
       </c>
       <c r="B164" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -21489,21 +21489,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>546297</v>
+        <v>546334</v>
       </c>
       <c r="R164" t="n">
-        <v>6999244</v>
+        <v>6999084</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -21556,7 +21556,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21576,22 +21576,22 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131273397</v>
+        <v>131273413</v>
       </c>
       <c r="B2" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546296</v>
+        <v>546491</v>
       </c>
       <c r="R2" t="n">
-        <v>6999259</v>
+        <v>6998962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131275180</v>
+        <v>131273422</v>
       </c>
       <c r="B3" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546406</v>
+        <v>546111</v>
       </c>
       <c r="R3" t="n">
-        <v>6999201</v>
+        <v>6999297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,17 +894,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275187</v>
+        <v>131275215</v>
       </c>
       <c r="B4" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546202</v>
+        <v>546164</v>
       </c>
       <c r="R4" t="n">
-        <v>6999223</v>
+        <v>6999199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,17 +1020,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131273413</v>
+        <v>131273397</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,21 +1059,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546491</v>
+        <v>546296</v>
       </c>
       <c r="R5" t="n">
-        <v>6998962</v>
+        <v>6999259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,6 +1124,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1151,17 +1146,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275215</v>
+        <v>131275180</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546164</v>
+        <v>546406</v>
       </c>
       <c r="R6" t="n">
-        <v>6999199</v>
+        <v>6999201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131275160</v>
+        <v>131275187</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1348,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546104</v>
+        <v>546202</v>
       </c>
       <c r="R7" t="n">
-        <v>6999263</v>
+        <v>6999223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1407,17 +1403,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1435,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273422</v>
+        <v>131273378</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,26 +1442,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1473,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546111</v>
+        <v>546094</v>
       </c>
       <c r="R8" t="n">
-        <v>6999297</v>
+        <v>6999329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1523,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,9 +1541,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1691,7 +1696,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131273378</v>
+        <v>131275160</v>
       </c>
       <c r="B10" t="n">
         <v>57887</v>
@@ -1724,7 +1729,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1734,10 +1739,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546094</v>
+        <v>546104</v>
       </c>
       <c r="R10" t="n">
-        <v>6999329</v>
+        <v>6999263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1774,7 +1779,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,14 +1806,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273421</v>
+        <v>131273375</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,26 +1967,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546167</v>
+        <v>546088</v>
       </c>
       <c r="R12" t="n">
-        <v>6999264</v>
+        <v>6999337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,13 +2037,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2057,9 +2066,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2077,10 +2091,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131273391</v>
+        <v>131275142</v>
       </c>
       <c r="B13" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,28 +2102,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2119,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546139</v>
       </c>
       <c r="R13" t="n">
-        <v>6998921</v>
+        <v>6999063</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,13 +2172,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2174,22 +2193,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,10 +2221,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131275185</v>
+        <v>131275131</v>
       </c>
       <c r="B14" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2218,26 +2232,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2245,10 +2264,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546230</v>
+        <v>546445</v>
       </c>
       <c r="R14" t="n">
-        <v>6999202</v>
+        <v>6998989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,7 +2304,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,7 +2313,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2305,22 +2323,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2338,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131273407</v>
+        <v>131275156</v>
       </c>
       <c r="B15" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,28 +2362,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2380,10 +2394,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546227</v>
+        <v>546115</v>
       </c>
       <c r="R15" t="n">
-        <v>6999437</v>
+        <v>6999245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2420,7 +2434,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,7 +2443,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2440,22 +2453,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2473,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131276484</v>
+        <v>131273368</v>
       </c>
       <c r="B16" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,26 +2492,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2511,10 +2524,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546500</v>
+        <v>546097</v>
       </c>
       <c r="R16" t="n">
-        <v>6998983</v>
+        <v>6999266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2549,13 +2562,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2566,22 +2583,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2599,10 +2611,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131275184</v>
+        <v>131275150</v>
       </c>
       <c r="B17" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,26 +2622,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2637,10 +2654,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546300</v>
+        <v>546123</v>
       </c>
       <c r="R17" t="n">
-        <v>6999066</v>
+        <v>6999192</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2675,19 +2692,38 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2705,10 +2741,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131275192</v>
+        <v>131275153</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2716,26 +2752,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2743,10 +2784,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546168</v>
+        <v>546126</v>
       </c>
       <c r="R18" t="n">
-        <v>6999218</v>
+        <v>6999216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2781,13 +2822,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2798,22 +2843,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2831,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131273396</v>
+        <v>131275163</v>
       </c>
       <c r="B19" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2842,28 +2882,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2873,10 +2914,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546277</v>
+        <v>546096</v>
       </c>
       <c r="R19" t="n">
-        <v>6999264</v>
+        <v>6999292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2913,7 +2954,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2922,7 +2963,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2933,27 +2973,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2971,10 +3001,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131275156</v>
+        <v>131273391</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,29 +3012,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3014,10 +3043,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546115</v>
+        <v>546459</v>
       </c>
       <c r="R20" t="n">
-        <v>6999245</v>
+        <v>6998921</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3052,17 +3081,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3073,17 +3098,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3101,10 +3131,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131273375</v>
+        <v>131275185</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3112,31 +3142,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3144,10 +3169,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546088</v>
+        <v>546230</v>
       </c>
       <c r="R21" t="n">
-        <v>6999337</v>
+        <v>6999202</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3184,7 +3209,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3193,6 +3218,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3203,22 +3229,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3236,10 +3262,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131273368</v>
+        <v>131273407</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3247,29 +3273,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3279,10 +3304,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546097</v>
+        <v>546227</v>
       </c>
       <c r="R22" t="n">
-        <v>6999266</v>
+        <v>6999437</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,7 +3344,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3328,6 +3353,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3338,17 +3364,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3366,10 +3397,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131275142</v>
+        <v>131276484</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3377,31 +3408,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3409,10 +3435,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546139</v>
+        <v>546500</v>
       </c>
       <c r="R23" t="n">
-        <v>6999063</v>
+        <v>6998983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3447,17 +3473,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3468,17 +3490,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3496,10 +3523,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131275153</v>
+        <v>131275184</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3507,31 +3534,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3539,10 +3561,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546126</v>
+        <v>546300</v>
       </c>
       <c r="R24" t="n">
-        <v>6999216</v>
+        <v>6999066</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3577,38 +3599,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3626,10 +3629,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131275131</v>
+        <v>131273421</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3637,31 +3640,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3669,10 +3667,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546445</v>
+        <v>546167</v>
       </c>
       <c r="R25" t="n">
-        <v>6998989</v>
+        <v>6999264</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3707,17 +3705,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3756,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131275150</v>
+        <v>131275192</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3767,31 +3761,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3799,10 +3788,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546123</v>
+        <v>546168</v>
       </c>
       <c r="R26" t="n">
-        <v>6999192</v>
+        <v>6999218</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3837,17 +3826,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3858,17 +3843,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3886,10 +3876,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131275163</v>
+        <v>131273396</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3897,29 +3887,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3929,10 +3918,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546096</v>
+        <v>546277</v>
       </c>
       <c r="R27" t="n">
-        <v>6999292</v>
+        <v>6999264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3969,7 +3958,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3978,6 +3967,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3988,17 +3978,27 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275178</v>
+        <v>131275206</v>
       </c>
       <c r="B32" t="n">
-        <v>80354</v>
+        <v>78261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4541,21 +4541,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546403</v>
+        <v>546408</v>
       </c>
       <c r="R32" t="n">
-        <v>6999213</v>
+        <v>6999129</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4619,6 +4619,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4636,10 +4656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275206</v>
+        <v>131275178</v>
       </c>
       <c r="B33" t="n">
-        <v>78261</v>
+        <v>80354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,21 +4667,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4674,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546408</v>
+        <v>546403</v>
       </c>
       <c r="R33" t="n">
-        <v>6999129</v>
+        <v>6999213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,26 +4745,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131276490</v>
+        <v>131273365</v>
       </c>
       <c r="B34" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4773,26 +4773,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4800,10 +4805,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546070</v>
+        <v>546239</v>
       </c>
       <c r="R34" t="n">
-        <v>6999377</v>
+        <v>6999263</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4838,13 +4843,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4855,22 +4864,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4888,10 +4897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131276489</v>
+        <v>131275146</v>
       </c>
       <c r="B35" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,26 +4908,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4926,10 +4940,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546065</v>
+        <v>546130</v>
       </c>
       <c r="R35" t="n">
-        <v>6999434</v>
+        <v>6999093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4964,13 +4978,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4981,22 +4999,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5014,10 +5027,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131275193</v>
+        <v>131275152</v>
       </c>
       <c r="B36" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5025,26 +5038,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5052,10 +5070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546158</v>
+        <v>546122</v>
       </c>
       <c r="R36" t="n">
-        <v>6999223</v>
+        <v>6999205</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5092,7 +5110,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5101,7 +5119,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5112,22 +5129,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5145,10 +5157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131273389</v>
+        <v>131275155</v>
       </c>
       <c r="B37" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5156,34 +5168,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546366</v>
+        <v>546116</v>
       </c>
       <c r="R37" t="n">
-        <v>6999149</v>
+        <v>6999243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5220,7 +5240,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på en sälg. Fertil!</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5231,6 +5251,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5247,7 +5287,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131276492</v>
+        <v>131276490</v>
       </c>
       <c r="B38" t="n">
         <v>80354</v>
@@ -5285,10 +5325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546097</v>
+        <v>546070</v>
       </c>
       <c r="R38" t="n">
-        <v>6999346</v>
+        <v>6999377</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5373,10 +5413,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131275155</v>
+        <v>131276489</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5384,31 +5424,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5416,10 +5451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546116</v>
+        <v>546065</v>
       </c>
       <c r="R39" t="n">
-        <v>6999243</v>
+        <v>6999434</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5454,17 +5489,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5475,17 +5506,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5503,10 +5539,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131275152</v>
+        <v>131275193</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5514,31 +5550,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5546,10 +5577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546122</v>
+        <v>546158</v>
       </c>
       <c r="R40" t="n">
-        <v>6999205</v>
+        <v>6999223</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5586,7 +5617,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5595,6 +5626,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5605,17 +5637,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5633,10 +5670,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131275146</v>
+        <v>131273389</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5644,42 +5681,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546130</v>
+        <v>546366</v>
       </c>
       <c r="R41" t="n">
-        <v>6999093</v>
+        <v>6999149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5716,7 +5745,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt på en sälg. Fertil!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5727,26 +5756,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5763,10 +5772,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131273365</v>
+        <v>131276492</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5774,31 +5783,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5806,10 +5810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546239</v>
+        <v>546097</v>
       </c>
       <c r="R42" t="n">
-        <v>6999263</v>
+        <v>6999346</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5844,17 +5848,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5865,22 +5865,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131275159</v>
+        <v>131273374</v>
       </c>
       <c r="B43" t="n">
         <v>57887</v>
@@ -5931,7 +5931,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546099</v>
+        <v>546094</v>
       </c>
       <c r="R43" t="n">
-        <v>6999277</v>
+        <v>6999322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6008,9 +6008,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6158,7 +6163,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131276478</v>
+        <v>131275159</v>
       </c>
       <c r="B45" t="n">
         <v>57887</v>
@@ -6191,7 +6196,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6201,10 +6206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546058</v>
+        <v>546099</v>
       </c>
       <c r="R45" t="n">
-        <v>6999435</v>
+        <v>6999277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6241,7 +6246,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6288,10 +6293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131273410</v>
+        <v>131276478</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6299,26 +6304,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6326,10 +6336,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546342</v>
+        <v>546058</v>
       </c>
       <c r="R46" t="n">
-        <v>6999195</v>
+        <v>6999435</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6364,13 +6374,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6409,10 +6423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131273426</v>
+        <v>131275139</v>
       </c>
       <c r="B47" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6420,26 +6434,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6447,10 +6466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546172</v>
+        <v>546151</v>
       </c>
       <c r="R47" t="n">
-        <v>6999385</v>
+        <v>6999044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6487,7 +6506,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6496,7 +6515,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7154,10 +7172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131273401</v>
+        <v>131273410</v>
       </c>
       <c r="B53" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,30 +7183,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7196,10 +7210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546279</v>
+        <v>546342</v>
       </c>
       <c r="R53" t="n">
-        <v>6999244</v>
+        <v>6999195</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7234,11 +7248,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7256,22 +7265,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7289,10 +7293,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131273406</v>
+        <v>131273426</v>
       </c>
       <c r="B54" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7300,21 +7304,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7327,10 +7331,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546223</v>
+        <v>546172</v>
       </c>
       <c r="R54" t="n">
-        <v>6999436</v>
+        <v>6999385</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7367,7 +7371,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7395,14 +7399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7420,10 +7419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131273374</v>
+        <v>131273401</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7431,29 +7430,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7463,10 +7461,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546094</v>
+        <v>546279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999322</v>
+        <v>6999244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7503,7 +7501,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7512,6 +7510,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7522,22 +7521,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7555,10 +7554,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131275139</v>
+        <v>131273406</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7566,31 +7565,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7598,10 +7592,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546151</v>
+        <v>546223</v>
       </c>
       <c r="R56" t="n">
-        <v>6999044</v>
+        <v>6999436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7638,7 +7632,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7647,6 +7641,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7665,9 +7660,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131273412</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,21 +7696,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546441</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999013</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7778,17 +7778,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7806,7 +7811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131275195</v>
+        <v>131273394</v>
       </c>
       <c r="B58" t="n">
         <v>80354</v>
@@ -7836,7 +7841,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7844,10 +7853,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546150</v>
+        <v>546346</v>
       </c>
       <c r="R58" t="n">
-        <v>6999197</v>
+        <v>6999078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7882,6 +7891,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7899,12 +7913,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7914,7 +7928,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7932,7 +7946,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273394</v>
+        <v>131276488</v>
       </c>
       <c r="B59" t="n">
         <v>80354</v>
@@ -7962,11 +7976,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7974,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546346</v>
+        <v>546062</v>
       </c>
       <c r="R59" t="n">
-        <v>6999078</v>
+        <v>6999441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8010,11 +8020,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8067,7 +8072,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276488</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
         <v>80354</v>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546062</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999441</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8193,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131276491</v>
+        <v>131273412</v>
       </c>
       <c r="B61" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8204,21 +8209,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8231,10 +8236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546074</v>
+        <v>546441</v>
       </c>
       <c r="R61" t="n">
-        <v>6999366</v>
+        <v>6999013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8286,22 +8291,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131276475</v>
+        <v>131275129</v>
       </c>
       <c r="B62" t="n">
         <v>57887</v>
@@ -8352,7 +8352,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
         <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999168</v>
+        <v>6999380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8449,7 +8449,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131275129</v>
+        <v>131273373</v>
       </c>
       <c r="B63" t="n">
         <v>57887</v>
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546338</v>
+        <v>546097</v>
       </c>
       <c r="R63" t="n">
-        <v>6999380</v>
+        <v>6999307</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8559,9 +8559,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8579,7 +8584,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131273373</v>
+        <v>131276475</v>
       </c>
       <c r="B64" t="n">
         <v>57887</v>
@@ -8612,7 +8617,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8622,10 +8627,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546097</v>
+        <v>546338</v>
       </c>
       <c r="R64" t="n">
-        <v>6999307</v>
+        <v>6999168</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8662,7 +8667,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8689,14 +8694,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131275200</v>
+        <v>131275211</v>
       </c>
       <c r="B65" t="n">
-        <v>80354</v>
+        <v>91837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546174</v>
+        <v>546185</v>
       </c>
       <c r="R65" t="n">
-        <v>6999354</v>
+        <v>6999135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8807,22 +8807,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8840,10 +8835,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273384</v>
+        <v>131273414</v>
       </c>
       <c r="B66" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8851,34 +8846,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546286</v>
+        <v>546430</v>
       </c>
       <c r="R66" t="n">
-        <v>6999257</v>
+        <v>6998969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8913,19 +8911,35 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fertil med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8942,10 +8956,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273386</v>
+        <v>131273416</v>
       </c>
       <c r="B67" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8953,30 +8967,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8984,10 +8994,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546294</v>
+        <v>546387</v>
       </c>
       <c r="R67" t="n">
-        <v>6999434</v>
+        <v>6999068</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9024,7 +9034,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9044,22 +9054,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9077,10 +9082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131273414</v>
+        <v>131276481</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9088,26 +9093,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9115,10 +9125,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546430</v>
+        <v>546070</v>
       </c>
       <c r="R68" t="n">
-        <v>6998969</v>
+        <v>6999374</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9153,13 +9163,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9198,10 +9212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273420</v>
+        <v>131273372</v>
       </c>
       <c r="B69" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9209,26 +9223,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9236,10 +9255,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546204</v>
+        <v>546089</v>
       </c>
       <c r="R69" t="n">
-        <v>6999267</v>
+        <v>6999297</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9276,7 +9295,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9285,7 +9304,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9304,9 +9322,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9324,10 +9347,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273416</v>
+        <v>131275200</v>
       </c>
       <c r="B70" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9335,21 +9358,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9362,10 +9385,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546387</v>
+        <v>546174</v>
       </c>
       <c r="R70" t="n">
-        <v>6999068</v>
+        <v>6999354</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9400,11 +9423,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9422,17 +9440,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9450,10 +9473,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131276481</v>
+        <v>131273384</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9461,42 +9484,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546070</v>
+        <v>546286</v>
       </c>
       <c r="R71" t="n">
-        <v>6999374</v>
+        <v>6999257</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9533,7 +9548,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9544,26 +9559,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9580,10 +9575,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131275211</v>
+        <v>131273420</v>
       </c>
       <c r="B72" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9591,26 +9586,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9618,10 +9613,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546185</v>
+        <v>546204</v>
       </c>
       <c r="R72" t="n">
-        <v>6999135</v>
+        <v>6999267</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9654,6 +9649,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9701,10 +9701,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273371</v>
+        <v>131273386</v>
       </c>
       <c r="B73" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9712,29 +9712,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9744,10 +9743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546089</v>
+        <v>546294</v>
       </c>
       <c r="R73" t="n">
-        <v>6999267</v>
+        <v>6999434</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9784,7 +9783,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9793,6 +9792,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9803,17 +9803,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9831,7 +9836,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273372</v>
+        <v>131273371</v>
       </c>
       <c r="B74" t="n">
         <v>57887</v>
@@ -9864,7 +9869,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9877,7 +9882,7 @@
         <v>546089</v>
       </c>
       <c r="R74" t="n">
-        <v>6999297</v>
+        <v>6999267</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9914,7 +9919,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9941,14 +9946,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131275144</v>
+        <v>131275132</v>
       </c>
       <c r="B82" t="n">
         <v>57887</v>
@@ -10894,25 +10894,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>546124</v>
+        <v>546295</v>
       </c>
       <c r="R82" t="n">
-        <v>6999127</v>
+        <v>6999077</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10949,7 +10961,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10966,19 +10978,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10996,7 +10998,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131275132</v>
+        <v>131275144</v>
       </c>
       <c r="B83" t="n">
         <v>57887</v>
@@ -11024,37 +11026,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>546295</v>
+        <v>546124</v>
       </c>
       <c r="R83" t="n">
-        <v>6999077</v>
+        <v>6999127</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11091,7 +11081,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11108,9 +11098,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>Äldre granskog med höga naturvärden.</t>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12283,39 +12283,47 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131273362</v>
+        <v>131275217</v>
       </c>
       <c r="B93" t="n">
-        <v>91817</v>
+        <v>83216</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -12325,10 +12333,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546302</v>
+        <v>546307</v>
       </c>
       <c r="R93" t="n">
-        <v>6999463</v>
+        <v>6999069</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12365,7 +12373,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12383,24 +12391,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12418,10 +12436,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131275135</v>
+        <v>131273362</v>
       </c>
       <c r="B94" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12429,29 +12447,28 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -12461,10 +12478,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546142</v>
+        <v>546302</v>
       </c>
       <c r="R94" t="n">
-        <v>6999047</v>
+        <v>6999463</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12501,7 +12518,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12510,6 +12527,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12528,9 +12546,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12548,10 +12571,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131273366</v>
+        <v>131273424</v>
       </c>
       <c r="B95" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12559,31 +12582,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12591,10 +12609,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546100</v>
+        <v>546090</v>
       </c>
       <c r="R95" t="n">
-        <v>6999258</v>
+        <v>6999323</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12631,7 +12649,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12640,6 +12658,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12658,14 +12677,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12683,47 +12697,40 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131275217</v>
+        <v>131276477</v>
       </c>
       <c r="B96" t="n">
-        <v>83216</v>
+        <v>57887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -12733,10 +12740,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546307</v>
+        <v>546062</v>
       </c>
       <c r="R96" t="n">
-        <v>6999069</v>
+        <v>6999442</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12773,7 +12780,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12782,7 +12789,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12791,34 +12797,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12836,10 +12827,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131273424</v>
+        <v>131275135</v>
       </c>
       <c r="B97" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12847,26 +12838,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12874,10 +12870,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546090</v>
+        <v>546142</v>
       </c>
       <c r="R97" t="n">
-        <v>6999323</v>
+        <v>6999047</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12914,7 +12910,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12923,7 +12919,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -13092,7 +13087,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131276477</v>
+        <v>131273366</v>
       </c>
       <c r="B99" t="n">
         <v>57887</v>
@@ -13135,10 +13130,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546062</v>
+        <v>546100</v>
       </c>
       <c r="R99" t="n">
-        <v>6999442</v>
+        <v>6999258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13175,7 +13170,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13202,9 +13197,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273409</v>
+        <v>131273380</v>
       </c>
       <c r="B101" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,24 +13359,29 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -13386,10 +13391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546299</v>
+        <v>546091</v>
       </c>
       <c r="R101" t="n">
-        <v>6999454</v>
+        <v>6999334</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13426,7 +13431,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13435,7 +13440,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13456,12 +13460,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13479,10 +13483,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273380</v>
+        <v>131273409</v>
       </c>
       <c r="B102" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13490,29 +13494,24 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -13522,10 +13521,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546091</v>
+        <v>546299</v>
       </c>
       <c r="R102" t="n">
-        <v>6999334</v>
+        <v>6999454</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13562,7 +13561,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13571,6 +13570,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13591,12 +13591,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -14267,10 +14267,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131275172</v>
+        <v>131273382</v>
       </c>
       <c r="B108" t="n">
-        <v>80258</v>
+        <v>57728</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14278,37 +14278,54 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>102621</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>546223</v>
+        <v>546360</v>
       </c>
       <c r="R108" t="n">
-        <v>6999048</v>
+        <v>6999087</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14343,13 +14360,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -14358,19 +14379,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14388,32 +14399,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131275190</v>
+        <v>131275172</v>
       </c>
       <c r="B109" t="n">
-        <v>80354</v>
+        <v>80258</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14426,10 +14437,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>546145</v>
+        <v>546223</v>
       </c>
       <c r="R109" t="n">
-        <v>6999134</v>
+        <v>6999048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14464,11 +14475,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -14494,14 +14500,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14519,7 +14520,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131273379</v>
+        <v>131275143</v>
       </c>
       <c r="B110" t="n">
         <v>57887</v>
@@ -14562,10 +14563,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>546099</v>
+        <v>546149</v>
       </c>
       <c r="R110" t="n">
-        <v>6999326</v>
+        <v>6999065</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14602,7 +14603,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14629,14 +14630,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14654,7 +14650,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131275143</v>
+        <v>131273379</v>
       </c>
       <c r="B111" t="n">
         <v>57887</v>
@@ -14697,10 +14693,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>546149</v>
+        <v>546099</v>
       </c>
       <c r="R111" t="n">
-        <v>6999065</v>
+        <v>6999326</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14737,7 +14733,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14764,9 +14760,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14784,27 +14785,27 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131273382</v>
+        <v>131273376</v>
       </c>
       <c r="B112" t="n">
-        <v>57728</v>
+        <v>57887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -14812,37 +14813,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>546360</v>
+        <v>546086</v>
       </c>
       <c r="R112" t="n">
-        <v>6999087</v>
+        <v>6999336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14879,7 +14868,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14896,9 +14885,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14916,10 +14920,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131273376</v>
+        <v>131275190</v>
       </c>
       <c r="B113" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14927,31 +14931,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14959,10 +14958,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546086</v>
+        <v>546145</v>
       </c>
       <c r="R113" t="n">
-        <v>6999336</v>
+        <v>6999134</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14999,7 +14998,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15008,6 +15007,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -15018,22 +15018,22 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15051,37 +15051,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131273418</v>
+        <v>131273363</v>
       </c>
       <c r="B114" t="n">
-        <v>79249</v>
+        <v>92539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15089,10 +15093,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546329</v>
+        <v>546304</v>
       </c>
       <c r="R114" t="n">
-        <v>6999224</v>
+        <v>6999379</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15129,7 +15133,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15157,9 +15161,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15177,37 +15186,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275174</v>
+        <v>131275212</v>
       </c>
       <c r="B115" t="n">
-        <v>75227</v>
+        <v>91837</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Leight.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15215,10 +15224,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546222</v>
+        <v>546213</v>
       </c>
       <c r="R115" t="n">
-        <v>6999408</v>
+        <v>6999022</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15253,11 +15262,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15275,22 +15279,17 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15429,39 +15428,40 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131273363</v>
+        <v>131275166</v>
       </c>
       <c r="B117" t="n">
-        <v>92539</v>
+        <v>57887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15471,10 +15471,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546304</v>
+        <v>546208</v>
       </c>
       <c r="R117" t="n">
-        <v>6999379</v>
+        <v>6999393</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15520,7 +15520,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15539,14 +15538,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15564,10 +15558,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131273387</v>
+        <v>131273418</v>
       </c>
       <c r="B118" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15575,30 +15569,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15606,10 +15596,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546286</v>
+        <v>546329</v>
       </c>
       <c r="R118" t="n">
-        <v>6999419</v>
+        <v>6999224</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15646,7 +15636,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15666,22 +15656,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15699,10 +15684,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131275212</v>
+        <v>131273387</v>
       </c>
       <c r="B119" t="n">
-        <v>91837</v>
+        <v>80354</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15710,24 +15695,28 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -15737,10 +15726,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546213</v>
+        <v>546286</v>
       </c>
       <c r="R119" t="n">
-        <v>6999022</v>
+        <v>6999419</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15775,6 +15764,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -15792,17 +15786,22 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15820,42 +15819,37 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275166</v>
+        <v>131275174</v>
       </c>
       <c r="B120" t="n">
-        <v>57887</v>
+        <v>75227</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15863,10 +15857,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546208</v>
+        <v>546222</v>
       </c>
       <c r="R120" t="n">
-        <v>6999393</v>
+        <v>6999408</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15903,7 +15897,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15912,6 +15906,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -15922,17 +15917,22 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16471,10 +16471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131275199</v>
+        <v>131273364</v>
       </c>
       <c r="B125" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16482,26 +16482,31 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -16509,10 +16514,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546147</v>
+        <v>546403</v>
       </c>
       <c r="R125" t="n">
-        <v>6999326</v>
+        <v>6998994</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16547,13 +16552,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -16574,12 +16583,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16597,32 +16606,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131275171</v>
+        <v>131273383</v>
       </c>
       <c r="B126" t="n">
-        <v>80258</v>
+        <v>80355</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16635,10 +16644,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546230</v>
+        <v>546292</v>
       </c>
       <c r="R126" t="n">
-        <v>6999202</v>
+        <v>6999247</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16673,6 +16682,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Växer här på en lutande sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -16690,17 +16704,22 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16718,7 +16737,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275197</v>
+        <v>131275199</v>
       </c>
       <c r="B127" t="n">
         <v>80354</v>
@@ -16756,10 +16775,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546130</v>
+        <v>546147</v>
       </c>
       <c r="R127" t="n">
-        <v>6999313</v>
+        <v>6999326</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16811,22 +16830,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16844,7 +16863,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275173</v>
+        <v>131275171</v>
       </c>
       <c r="B128" t="n">
         <v>80258</v>
@@ -16882,10 +16901,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546165</v>
+        <v>546230</v>
       </c>
       <c r="R128" t="n">
-        <v>6999228</v>
+        <v>6999202</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16965,10 +16984,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131273383</v>
+        <v>131275197</v>
       </c>
       <c r="B129" t="n">
-        <v>80355</v>
+        <v>80354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16976,21 +16995,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -17003,10 +17022,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546292</v>
+        <v>546130</v>
       </c>
       <c r="R129" t="n">
-        <v>6999247</v>
+        <v>6999313</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17039,11 +17058,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Växer här på en lutande sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -17096,42 +17110,37 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131273364</v>
+        <v>131275173</v>
       </c>
       <c r="B130" t="n">
-        <v>57887</v>
+        <v>80258</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -17139,10 +17148,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>546403</v>
+        <v>546165</v>
       </c>
       <c r="R130" t="n">
-        <v>6998994</v>
+        <v>6999228</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17177,17 +17186,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -17198,22 +17203,17 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -18004,39 +18004,40 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131273408</v>
+        <v>131275147</v>
       </c>
       <c r="B137" t="n">
-        <v>80390</v>
+        <v>57887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -18046,10 +18047,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>546110</v>
+        <v>546137</v>
       </c>
       <c r="R137" t="n">
-        <v>6999309</v>
+        <v>6999148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -18086,7 +18087,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -18095,7 +18096,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -18106,22 +18106,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -18139,10 +18134,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131273390</v>
+        <v>131275136</v>
       </c>
       <c r="B138" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18150,28 +18145,29 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -18181,10 +18177,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>546420</v>
+        <v>546148</v>
       </c>
       <c r="R138" t="n">
-        <v>6999089</v>
+        <v>6999041</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18221,7 +18217,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18230,7 +18226,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -18241,22 +18236,17 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18274,10 +18264,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131275203</v>
+        <v>131275138</v>
       </c>
       <c r="B139" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18285,26 +18275,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -18312,10 +18307,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>546227</v>
+        <v>546145</v>
       </c>
       <c r="R139" t="n">
-        <v>6999420</v>
+        <v>6999053</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18350,13 +18345,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -18367,22 +18366,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18400,40 +18394,39 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131275136</v>
+        <v>131273408</v>
       </c>
       <c r="B140" t="n">
-        <v>57887</v>
+        <v>80390</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -18443,10 +18436,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546148</v>
+        <v>546110</v>
       </c>
       <c r="R140" t="n">
-        <v>6999041</v>
+        <v>6999309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18483,7 +18476,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en flerstammig gammal sälg.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18492,6 +18485,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -18502,17 +18496,22 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -18530,10 +18529,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131275138</v>
+        <v>131273390</v>
       </c>
       <c r="B141" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18541,29 +18540,28 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -18573,10 +18571,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546145</v>
+        <v>546420</v>
       </c>
       <c r="R141" t="n">
-        <v>6999053</v>
+        <v>6999089</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18613,7 +18611,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18622,6 +18620,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -18632,17 +18631,22 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -18660,10 +18664,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275147</v>
+        <v>131275203</v>
       </c>
       <c r="B142" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18671,31 +18675,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -18703,10 +18702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546137</v>
+        <v>546227</v>
       </c>
       <c r="R142" t="n">
-        <v>6999148</v>
+        <v>6999420</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18741,17 +18740,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -18762,17 +18757,22 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -18916,10 +18916,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131275214</v>
+        <v>131273367</v>
       </c>
       <c r="B144" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18927,26 +18927,31 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -18954,10 +18959,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>546193</v>
+        <v>546103</v>
       </c>
       <c r="R144" t="n">
-        <v>6999241</v>
+        <v>6999266</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18992,13 +18997,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -19017,9 +19026,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -19400,10 +19414,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131273367</v>
+        <v>131275214</v>
       </c>
       <c r="B148" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19411,31 +19425,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -19443,10 +19452,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546103</v>
+        <v>546193</v>
       </c>
       <c r="R148" t="n">
-        <v>6999266</v>
+        <v>6999241</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19481,17 +19490,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -19510,14 +19515,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19535,37 +19535,42 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131275210</v>
+        <v>131276480</v>
       </c>
       <c r="B149" t="n">
-        <v>80314</v>
+        <v>57887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -19573,10 +19578,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546168</v>
+        <v>546066</v>
       </c>
       <c r="R149" t="n">
-        <v>6999217</v>
+        <v>6999401</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19611,13 +19616,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -19628,22 +19637,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19791,42 +19795,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131276480</v>
+        <v>131275210</v>
       </c>
       <c r="B151" t="n">
-        <v>57887</v>
+        <v>80314</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -19834,10 +19833,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546066</v>
+        <v>546168</v>
       </c>
       <c r="R151" t="n">
-        <v>6999401</v>
+        <v>6999217</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19872,17 +19871,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -19893,17 +19888,22 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -19921,10 +19921,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131275177</v>
+        <v>131275130</v>
       </c>
       <c r="B152" t="n">
-        <v>83224</v>
+        <v>57887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19932,26 +19932,31 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -19959,10 +19964,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546303</v>
+        <v>546460</v>
       </c>
       <c r="R152" t="n">
-        <v>6999065</v>
+        <v>6999069</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19999,7 +20004,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20008,7 +20013,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -20017,29 +20021,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20057,10 +20051,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275189</v>
+        <v>131275177</v>
       </c>
       <c r="B153" t="n">
-        <v>80354</v>
+        <v>83224</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20068,21 +20062,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -20095,10 +20089,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546224</v>
+        <v>546303</v>
       </c>
       <c r="R153" t="n">
-        <v>6999013</v>
+        <v>6999065</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20135,7 +20129,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20153,24 +20147,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -20188,7 +20187,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131273405</v>
+        <v>131275189</v>
       </c>
       <c r="B154" t="n">
         <v>80354</v>
@@ -20226,10 +20225,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>546169</v>
+        <v>546224</v>
       </c>
       <c r="R154" t="n">
-        <v>6999410</v>
+        <v>6999013</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -20266,7 +20265,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Enstaka bålar på asp.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20286,12 +20285,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -20301,7 +20300,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -20319,7 +20318,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131275196</v>
+        <v>131273405</v>
       </c>
       <c r="B155" t="n">
         <v>80354</v>
@@ -20357,10 +20356,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>546124</v>
+        <v>546169</v>
       </c>
       <c r="R155" t="n">
-        <v>6999220</v>
+        <v>6999410</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -20393,6 +20392,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20445,10 +20449,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131275130</v>
+        <v>131275196</v>
       </c>
       <c r="B156" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20456,31 +20460,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -20488,10 +20487,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>546460</v>
+        <v>546124</v>
       </c>
       <c r="R156" t="n">
-        <v>6999069</v>
+        <v>6999220</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20526,17 +20525,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -20547,17 +20542,22 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -20575,10 +20575,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131275157</v>
+        <v>131275168</v>
       </c>
       <c r="B157" t="n">
-        <v>57887</v>
+        <v>80220</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20586,31 +20586,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -20618,10 +20613,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>546111</v>
+        <v>546465</v>
       </c>
       <c r="R157" t="n">
-        <v>6999255</v>
+        <v>6999031</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -20656,17 +20651,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -20677,17 +20668,17 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -20705,10 +20696,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131275154</v>
+        <v>131273403</v>
       </c>
       <c r="B158" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20716,31 +20707,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -20748,10 +20734,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>546118</v>
+        <v>546109</v>
       </c>
       <c r="R158" t="n">
-        <v>6999237</v>
+        <v>6999309</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -20788,7 +20774,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Lunglav på en liten gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20797,6 +20783,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -20815,9 +20802,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -20835,7 +20827,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131273403</v>
+        <v>131273400</v>
       </c>
       <c r="B159" t="n">
         <v>80354</v>
@@ -20873,10 +20865,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>546109</v>
+        <v>546297</v>
       </c>
       <c r="R159" t="n">
-        <v>6999309</v>
+        <v>6999244</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20913,7 +20905,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20933,22 +20925,22 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -20966,10 +20958,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131273400</v>
+        <v>131273417</v>
       </c>
       <c r="B160" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20977,21 +20969,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -21004,10 +20996,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>546297</v>
+        <v>546334</v>
       </c>
       <c r="R160" t="n">
-        <v>6999244</v>
+        <v>6999084</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -21044,7 +21036,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -21064,22 +21056,22 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr"/>
@@ -21357,10 +21349,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131275168</v>
+        <v>131275154</v>
       </c>
       <c r="B163" t="n">
-        <v>80220</v>
+        <v>57887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21368,26 +21360,31 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -21395,10 +21392,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>546465</v>
+        <v>546118</v>
       </c>
       <c r="R163" t="n">
-        <v>6999031</v>
+        <v>6999237</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -21433,13 +21430,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -21450,17 +21451,17 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>
@@ -21478,10 +21479,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131273417</v>
+        <v>131275157</v>
       </c>
       <c r="B164" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -21489,26 +21490,31 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -21516,10 +21522,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>546334</v>
+        <v>546111</v>
       </c>
       <c r="R164" t="n">
-        <v>6999084</v>
+        <v>6999255</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -21556,7 +21562,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21565,7 +21571,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -21584,14 +21589,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -1431,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273378</v>
+        <v>131275145</v>
       </c>
       <c r="B8" t="n">
         <v>57887</v>
@@ -1464,7 +1464,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546094</v>
+        <v>546148</v>
       </c>
       <c r="R8" t="n">
-        <v>6999329</v>
+        <v>6999078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,14 +1541,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,7 +1561,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131275145</v>
+        <v>131273378</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -1599,7 +1594,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546148</v>
+        <v>546094</v>
       </c>
       <c r="R9" t="n">
-        <v>6999078</v>
+        <v>6999329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,9 +1671,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273375</v>
+        <v>131273391</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,29 +1967,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1999,10 +1998,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546088</v>
+        <v>546459</v>
       </c>
       <c r="R12" t="n">
-        <v>6999337</v>
+        <v>6998921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2037,17 +2036,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2058,22 +2053,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2091,10 +2086,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131275142</v>
+        <v>131275185</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2102,31 +2097,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2134,10 +2124,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546139</v>
+        <v>546230</v>
       </c>
       <c r="R13" t="n">
-        <v>6999063</v>
+        <v>6999202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2174,7 +2164,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,6 +2173,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2193,17 +2184,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2221,10 +2217,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131275131</v>
+        <v>131273407</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2232,29 +2228,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2264,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546445</v>
+        <v>546227</v>
       </c>
       <c r="R14" t="n">
-        <v>6998989</v>
+        <v>6999437</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2304,7 +2299,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,6 +2308,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2323,17 +2319,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2351,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131275156</v>
+        <v>131276484</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,31 +2363,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2394,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546115</v>
+        <v>546500</v>
       </c>
       <c r="R15" t="n">
-        <v>6999245</v>
+        <v>6998983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2432,17 +2428,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2453,17 +2445,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2481,10 +2478,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131273368</v>
+        <v>131275184</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,31 +2489,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2524,10 +2516,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546097</v>
+        <v>546300</v>
       </c>
       <c r="R16" t="n">
-        <v>6999266</v>
+        <v>6999066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,38 +2554,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2611,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131275150</v>
+        <v>131273421</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2622,31 +2595,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2654,10 +2622,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546123</v>
+        <v>546167</v>
       </c>
       <c r="R17" t="n">
-        <v>6999192</v>
+        <v>6999264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2692,17 +2660,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2741,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131275153</v>
+        <v>131275192</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2752,31 +2716,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2784,10 +2743,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546126</v>
+        <v>546168</v>
       </c>
       <c r="R18" t="n">
-        <v>6999216</v>
+        <v>6999218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2822,17 +2781,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2843,17 +2798,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2871,10 +2831,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131275163</v>
+        <v>131273396</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2882,29 +2842,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2914,10 +2873,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546096</v>
+        <v>546277</v>
       </c>
       <c r="R19" t="n">
-        <v>6999292</v>
+        <v>6999264</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2954,7 +2913,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2963,6 +2922,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2973,17 +2933,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3001,10 +2971,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131273391</v>
+        <v>131275163</v>
       </c>
       <c r="B20" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3012,28 +2982,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3043,10 +3014,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546459</v>
+        <v>546096</v>
       </c>
       <c r="R20" t="n">
-        <v>6998921</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3081,13 +3052,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3098,22 +3073,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3131,10 +3101,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131275185</v>
+        <v>131273368</v>
       </c>
       <c r="B21" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,26 +3112,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3169,10 +3144,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546230</v>
+        <v>546097</v>
       </c>
       <c r="R21" t="n">
-        <v>6999202</v>
+        <v>6999266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3209,7 +3184,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, äldre, på en gran med rikt kådaflöde  vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3218,7 +3193,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3229,22 +3203,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3262,10 +3231,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131273407</v>
+        <v>131275156</v>
       </c>
       <c r="B22" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,28 +3242,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3304,10 +3274,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546227</v>
+        <v>546115</v>
       </c>
       <c r="R22" t="n">
-        <v>6999437</v>
+        <v>6999245</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3344,7 +3314,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3353,7 +3323,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3364,22 +3333,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3397,10 +3361,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131276484</v>
+        <v>131273375</v>
       </c>
       <c r="B23" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3408,26 +3372,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3435,10 +3404,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546500</v>
+        <v>546088</v>
       </c>
       <c r="R23" t="n">
-        <v>6998983</v>
+        <v>6999337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3473,13 +3442,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran nära en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3490,22 +3463,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3523,10 +3496,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131275184</v>
+        <v>131275142</v>
       </c>
       <c r="B24" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3534,26 +3507,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3561,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546300</v>
+        <v>546139</v>
       </c>
       <c r="R24" t="n">
-        <v>6999066</v>
+        <v>6999063</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3599,19 +3577,38 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3629,10 +3626,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131273421</v>
+        <v>131275153</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,26 +3637,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3667,10 +3669,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546167</v>
+        <v>546126</v>
       </c>
       <c r="R25" t="n">
-        <v>6999264</v>
+        <v>6999216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3705,13 +3707,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3750,10 +3756,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131275192</v>
+        <v>131275150</v>
       </c>
       <c r="B26" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,26 +3767,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3788,10 +3799,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546168</v>
+        <v>546123</v>
       </c>
       <c r="R26" t="n">
-        <v>6999218</v>
+        <v>6999192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3826,13 +3837,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3843,22 +3858,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3876,10 +3886,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131273396</v>
+        <v>131275131</v>
       </c>
       <c r="B27" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3887,28 +3897,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3918,10 +3929,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546277</v>
+        <v>546445</v>
       </c>
       <c r="R27" t="n">
-        <v>6999264</v>
+        <v>6998989</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3958,7 +3969,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en särskilt grov gammal sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3967,7 +3978,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3978,27 +3988,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Mycket grov bark. # Salix caprea # En grovbarkad sälg med 75 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131275176</v>
+        <v>131275191</v>
       </c>
       <c r="B28" t="n">
-        <v>75339</v>
+        <v>80354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546399</v>
+        <v>546174</v>
       </c>
       <c r="R28" t="n">
-        <v>6998994</v>
+        <v>6999215</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4092,6 +4092,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4109,12 +4114,12 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -4124,7 +4129,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4142,10 +4147,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275175</v>
+        <v>131275201</v>
       </c>
       <c r="B29" t="n">
-        <v>75339</v>
+        <v>80354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4153,21 +4158,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546372</v>
+        <v>546222</v>
       </c>
       <c r="R29" t="n">
-        <v>6998999</v>
+        <v>6999418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4218,11 +4223,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark av gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275191</v>
+        <v>131275178</v>
       </c>
       <c r="B30" t="n">
         <v>80354</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546174</v>
+        <v>546403</v>
       </c>
       <c r="R30" t="n">
-        <v>6999215</v>
+        <v>6999213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4349,11 +4349,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4367,26 +4362,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4404,10 +4379,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275201</v>
+        <v>131275176</v>
       </c>
       <c r="B31" t="n">
-        <v>80354</v>
+        <v>75339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4415,21 +4390,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4442,10 +4417,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546222</v>
+        <v>546399</v>
       </c>
       <c r="R31" t="n">
-        <v>6999418</v>
+        <v>6998994</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4497,12 +4472,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4512,7 +4487,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4530,10 +4505,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275206</v>
+        <v>131275175</v>
       </c>
       <c r="B32" t="n">
-        <v>78261</v>
+        <v>75339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4541,21 +4516,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>1460</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4568,10 +4543,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546408</v>
+        <v>546372</v>
       </c>
       <c r="R32" t="n">
-        <v>6999129</v>
+        <v>6998999</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4604,6 +4579,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På bark av gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4656,10 +4636,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275178</v>
+        <v>131275206</v>
       </c>
       <c r="B33" t="n">
-        <v>80354</v>
+        <v>78261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,21 +4647,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4694,10 +4674,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546403</v>
+        <v>546408</v>
       </c>
       <c r="R33" t="n">
-        <v>6999213</v>
+        <v>6999129</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4745,6 +4725,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131273365</v>
+        <v>131275155</v>
       </c>
       <c r="B34" t="n">
         <v>57887</v>
@@ -4795,7 +4795,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546239</v>
+        <v>546116</v>
       </c>
       <c r="R34" t="n">
-        <v>6999263</v>
+        <v>6999243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4872,14 +4872,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4897,7 +4892,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131275146</v>
+        <v>131275152</v>
       </c>
       <c r="B35" t="n">
         <v>57887</v>
@@ -4940,10 +4935,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546130</v>
+        <v>546122</v>
       </c>
       <c r="R35" t="n">
-        <v>6999093</v>
+        <v>6999205</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5027,7 +5022,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131275152</v>
+        <v>131275146</v>
       </c>
       <c r="B36" t="n">
         <v>57887</v>
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546122</v>
+        <v>546130</v>
       </c>
       <c r="R36" t="n">
-        <v>6999205</v>
+        <v>6999093</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5157,7 +5152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131275155</v>
+        <v>131273365</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5190,7 +5185,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546116</v>
+        <v>546239</v>
       </c>
       <c r="R37" t="n">
-        <v>6999243</v>
+        <v>6999263</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5240,7 +5235,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5267,9 +5262,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273374</v>
+        <v>131275182</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5909,31 +5909,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5941,10 +5936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546094</v>
+        <v>546357</v>
       </c>
       <c r="R43" t="n">
-        <v>6999322</v>
+        <v>6999022</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5979,43 +5974,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6033,10 +6004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131275151</v>
+        <v>131276487</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6044,31 +6015,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6076,10 +6042,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546124</v>
+        <v>546313</v>
       </c>
       <c r="R44" t="n">
-        <v>6999206</v>
+        <v>6999060</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6114,17 +6080,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6135,17 +6097,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6163,40 +6130,39 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131275159</v>
+        <v>131273381</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>80383</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6206,10 +6172,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546099</v>
+        <v>546353</v>
       </c>
       <c r="R45" t="n">
-        <v>6999277</v>
+        <v>6999084</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6246,7 +6212,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6255,6 +6221,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6265,17 +6232,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6293,10 +6265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131276478</v>
+        <v>131275194</v>
       </c>
       <c r="B46" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6304,31 +6276,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6336,10 +6303,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546058</v>
+        <v>546153</v>
       </c>
       <c r="R46" t="n">
-        <v>6999435</v>
+        <v>6999210</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6376,7 +6343,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6385,6 +6352,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6395,17 +6363,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6423,10 +6396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131275139</v>
+        <v>131273410</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6434,31 +6407,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6466,10 +6434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546151</v>
+        <v>546342</v>
       </c>
       <c r="R47" t="n">
-        <v>6999044</v>
+        <v>6999195</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6504,17 +6472,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6553,7 +6517,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131275213</v>
+        <v>131273426</v>
       </c>
       <c r="B48" t="n">
         <v>79249</v>
@@ -6591,10 +6555,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546481</v>
+        <v>546172</v>
       </c>
       <c r="R48" t="n">
-        <v>6998980</v>
+        <v>6999385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6627,6 +6591,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6674,7 +6643,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131275182</v>
+        <v>131273401</v>
       </c>
       <c r="B49" t="n">
         <v>80354</v>
@@ -6704,7 +6673,11 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6712,10 +6685,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546357</v>
+        <v>546279</v>
       </c>
       <c r="R49" t="n">
-        <v>6999022</v>
+        <v>6999244</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6750,6 +6723,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6763,6 +6741,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6780,7 +6778,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131276487</v>
+        <v>131273406</v>
       </c>
       <c r="B50" t="n">
         <v>80354</v>
@@ -6818,10 +6816,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546313</v>
+        <v>546223</v>
       </c>
       <c r="R50" t="n">
-        <v>6999060</v>
+        <v>6999436</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6856,6 +6854,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6873,22 +6876,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6906,41 +6909,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131273381</v>
+        <v>131275213</v>
       </c>
       <c r="B51" t="n">
-        <v>80383</v>
+        <v>79249</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6948,10 +6947,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546353</v>
+        <v>546481</v>
       </c>
       <c r="R51" t="n">
-        <v>6999084</v>
+        <v>6998980</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6986,11 +6985,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7008,22 +7002,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7041,10 +7030,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131275194</v>
+        <v>131275159</v>
       </c>
       <c r="B52" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7052,26 +7041,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7079,10 +7073,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546153</v>
+        <v>546099</v>
       </c>
       <c r="R52" t="n">
-        <v>6999210</v>
+        <v>6999277</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7119,7 +7113,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7128,7 +7122,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7139,22 +7132,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7172,10 +7160,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131273410</v>
+        <v>131275151</v>
       </c>
       <c r="B53" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7183,26 +7171,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7210,10 +7203,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546342</v>
+        <v>546124</v>
       </c>
       <c r="R53" t="n">
-        <v>6999195</v>
+        <v>6999206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7248,13 +7241,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7293,10 +7290,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131273426</v>
+        <v>131273374</v>
       </c>
       <c r="B54" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7304,26 +7301,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7331,10 +7333,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546172</v>
+        <v>546094</v>
       </c>
       <c r="R54" t="n">
-        <v>6999385</v>
+        <v>6999322</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7371,7 +7373,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7380,7 +7382,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7399,9 +7400,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7419,10 +7425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131273401</v>
+        <v>131275139</v>
       </c>
       <c r="B55" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7430,28 +7436,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7461,10 +7468,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546279</v>
+        <v>546151</v>
       </c>
       <c r="R55" t="n">
-        <v>6999244</v>
+        <v>6999044</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7501,7 +7508,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7510,7 +7517,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7521,22 +7527,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7554,10 +7555,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131273406</v>
+        <v>131276478</v>
       </c>
       <c r="B56" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7565,26 +7566,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7592,10 +7598,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546223</v>
+        <v>546058</v>
       </c>
       <c r="R56" t="n">
-        <v>6999436</v>
+        <v>6999435</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7632,7 +7638,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7641,7 +7647,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7660,14 +7665,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131275129</v>
+        <v>131276475</v>
       </c>
       <c r="B62" t="n">
         <v>57887</v>
@@ -8352,7 +8352,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8365,7 +8365,7 @@
         <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999380</v>
+        <v>6999168</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8584,7 +8584,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276475</v>
+        <v>131275129</v>
       </c>
       <c r="B64" t="n">
         <v>57887</v>
@@ -8617,7 +8617,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
         <v>546338</v>
       </c>
       <c r="R64" t="n">
-        <v>6999168</v>
+        <v>6999380</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273414</v>
+        <v>131275200</v>
       </c>
       <c r="B66" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546430</v>
+        <v>546174</v>
       </c>
       <c r="R66" t="n">
-        <v>6998969</v>
+        <v>6999354</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8928,17 +8928,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8956,10 +8961,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273416</v>
+        <v>131273384</v>
       </c>
       <c r="B67" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8967,37 +8972,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546387</v>
+        <v>546286</v>
       </c>
       <c r="R67" t="n">
-        <v>6999068</v>
+        <v>6999257</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9034,7 +9036,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9043,29 +9045,8 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9082,10 +9063,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131276481</v>
+        <v>131273414</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9093,31 +9074,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9125,10 +9101,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546070</v>
+        <v>546430</v>
       </c>
       <c r="R68" t="n">
-        <v>6999374</v>
+        <v>6998969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9163,17 +9139,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9212,10 +9184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273372</v>
+        <v>131273420</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9223,31 +9195,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9255,10 +9222,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546089</v>
+        <v>546204</v>
       </c>
       <c r="R69" t="n">
-        <v>6999297</v>
+        <v>6999267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9295,7 +9262,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9304,6 +9271,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9322,14 +9290,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9347,7 +9310,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131275200</v>
+        <v>131273386</v>
       </c>
       <c r="B70" t="n">
         <v>80354</v>
@@ -9377,7 +9340,11 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9385,10 +9352,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546174</v>
+        <v>546294</v>
       </c>
       <c r="R70" t="n">
-        <v>6999354</v>
+        <v>6999434</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9423,6 +9390,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9440,12 +9412,12 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -9455,7 +9427,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9473,10 +9445,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273384</v>
+        <v>131273416</v>
       </c>
       <c r="B71" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9484,34 +9456,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546286</v>
+        <v>546387</v>
       </c>
       <c r="R71" t="n">
-        <v>6999257</v>
+        <v>6999068</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9548,7 +9523,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9557,8 +9532,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9575,10 +9571,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273420</v>
+        <v>131273371</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,26 +9582,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9613,7 +9614,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546204</v>
+        <v>546089</v>
       </c>
       <c r="R72" t="n">
         <v>6999267</v>
@@ -9653,7 +9654,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9662,7 +9663,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9701,10 +9701,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273386</v>
+        <v>131276481</v>
       </c>
       <c r="B73" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9712,28 +9712,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9743,10 +9744,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546294</v>
+        <v>546070</v>
       </c>
       <c r="R73" t="n">
-        <v>6999434</v>
+        <v>6999374</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9783,7 +9784,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9792,7 +9793,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9803,22 +9803,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9836,7 +9831,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273371</v>
+        <v>131273372</v>
       </c>
       <c r="B74" t="n">
         <v>57887</v>
@@ -9869,7 +9864,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9882,7 +9877,7 @@
         <v>546089</v>
       </c>
       <c r="R74" t="n">
-        <v>6999267</v>
+        <v>6999297</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9919,7 +9914,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9946,9 +9941,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131276486</v>
+        <v>131276482</v>
       </c>
       <c r="B75" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9977,26 +9977,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>546356</v>
+        <v>546075</v>
       </c>
       <c r="R75" t="n">
-        <v>6999034</v>
+        <v>6999369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10042,13 +10047,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10059,22 +10068,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10092,10 +10096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131275181</v>
+        <v>131275144</v>
       </c>
       <c r="B76" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10103,26 +10107,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10130,10 +10139,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>546435</v>
+        <v>546124</v>
       </c>
       <c r="R76" t="n">
-        <v>6999096</v>
+        <v>6999127</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10170,7 +10179,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10179,7 +10188,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10190,22 +10198,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10223,10 +10226,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131273393</v>
+        <v>131275132</v>
       </c>
       <c r="B77" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10234,41 +10237,54 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>546394</v>
+        <v>546295</v>
       </c>
       <c r="R77" t="n">
-        <v>6999043</v>
+        <v>6999077</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10303,13 +10319,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10318,24 +10338,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10353,7 +10358,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131275202</v>
+        <v>131276486</v>
       </c>
       <c r="B78" t="n">
         <v>80354</v>
@@ -10391,10 +10396,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>546230</v>
+        <v>546356</v>
       </c>
       <c r="R78" t="n">
-        <v>6999398</v>
+        <v>6999034</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10479,7 +10484,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131273402</v>
+        <v>131275181</v>
       </c>
       <c r="B79" t="n">
         <v>80354</v>
@@ -10517,10 +10522,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>546159</v>
+        <v>546435</v>
       </c>
       <c r="R79" t="n">
-        <v>6999249</v>
+        <v>6999096</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10557,7 +10562,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10577,22 +10582,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10610,7 +10615,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131273392</v>
+        <v>131273393</v>
       </c>
       <c r="B80" t="n">
         <v>80354</v>
@@ -10640,7 +10645,11 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10648,10 +10657,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>546398</v>
+        <v>546394</v>
       </c>
       <c r="R80" t="n">
-        <v>6998976</v>
+        <v>6999043</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10736,10 +10745,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131276482</v>
+        <v>131275202</v>
       </c>
       <c r="B81" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10747,31 +10756,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10779,10 +10783,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>546075</v>
+        <v>546230</v>
       </c>
       <c r="R81" t="n">
-        <v>6999369</v>
+        <v>6999398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10817,17 +10821,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10838,17 +10838,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10866,10 +10871,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131275132</v>
+        <v>131273402</v>
       </c>
       <c r="B82" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10877,54 +10882,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>546295</v>
+        <v>546159</v>
       </c>
       <c r="R82" t="n">
-        <v>6999077</v>
+        <v>6999249</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10961,7 +10949,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10970,6 +10958,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10978,9 +10967,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Äldre granskog med höga naturvärden.</t>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10998,10 +11002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131275144</v>
+        <v>131273392</v>
       </c>
       <c r="B83" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11009,31 +11013,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11041,10 +11040,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>546124</v>
+        <v>546398</v>
       </c>
       <c r="R83" t="n">
-        <v>6999127</v>
+        <v>6998976</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11079,17 +11078,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11100,17 +11095,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11893,7 +11893,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275161</v>
+        <v>131275164</v>
       </c>
       <c r="B90" t="n">
         <v>57887</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546100</v>
+        <v>546097</v>
       </c>
       <c r="R90" t="n">
-        <v>6999276</v>
+        <v>6999287</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12153,7 +12153,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275164</v>
+        <v>131275161</v>
       </c>
       <c r="B92" t="n">
         <v>57887</v>
@@ -12196,10 +12196,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546097</v>
+        <v>546100</v>
       </c>
       <c r="R92" t="n">
-        <v>6999287</v>
+        <v>6999276</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12436,10 +12436,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131273362</v>
+        <v>131273424</v>
       </c>
       <c r="B94" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12447,30 +12447,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12478,10 +12474,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546302</v>
+        <v>546090</v>
       </c>
       <c r="R94" t="n">
-        <v>6999463</v>
+        <v>6999323</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12518,7 +12514,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12546,14 +12542,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12571,10 +12562,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131273424</v>
+        <v>131273362</v>
       </c>
       <c r="B95" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12582,26 +12573,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12609,10 +12604,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546090</v>
+        <v>546302</v>
       </c>
       <c r="R95" t="n">
-        <v>6999323</v>
+        <v>6999463</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12649,7 +12644,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12677,9 +12672,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131276477</v>
+        <v>131275135</v>
       </c>
       <c r="B96" t="n">
         <v>57887</v>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546062</v>
+        <v>546142</v>
       </c>
       <c r="R96" t="n">
-        <v>6999442</v>
+        <v>6999047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12827,7 +12827,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131275135</v>
+        <v>131273366</v>
       </c>
       <c r="B97" t="n">
         <v>57887</v>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546142</v>
+        <v>546100</v>
       </c>
       <c r="R97" t="n">
-        <v>6999047</v>
+        <v>6999258</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12937,9 +12937,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13087,7 +13092,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131273366</v>
+        <v>131276477</v>
       </c>
       <c r="B99" t="n">
         <v>57887</v>
@@ -13130,10 +13135,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546100</v>
+        <v>546062</v>
       </c>
       <c r="R99" t="n">
-        <v>6999258</v>
+        <v>6999442</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13170,7 +13175,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13197,14 +13202,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13348,7 +13348,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273380</v>
+        <v>131275137</v>
       </c>
       <c r="B101" t="n">
         <v>57887</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546091</v>
+        <v>546139</v>
       </c>
       <c r="R101" t="n">
-        <v>6999334</v>
+        <v>6999047</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13458,14 +13458,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13483,10 +13478,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273409</v>
+        <v>131273377</v>
       </c>
       <c r="B102" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13494,24 +13489,29 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -13521,10 +13521,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546299</v>
+        <v>546077</v>
       </c>
       <c r="R102" t="n">
-        <v>6999454</v>
+        <v>6999352</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13570,7 +13570,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13591,12 +13590,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13614,10 +13613,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131273419</v>
+        <v>131273380</v>
       </c>
       <c r="B103" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13625,26 +13624,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13652,10 +13656,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546230</v>
+        <v>546091</v>
       </c>
       <c r="R103" t="n">
-        <v>6999267</v>
+        <v>6999334</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13692,7 +13696,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13701,13 +13705,12 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -13720,19 +13723,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13750,10 +13748,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131273395</v>
+        <v>131275207</v>
       </c>
       <c r="B104" t="n">
-        <v>80354</v>
+        <v>78261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13761,21 +13759,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13788,10 +13786,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546313</v>
+        <v>546365</v>
       </c>
       <c r="R104" t="n">
-        <v>6999066</v>
+        <v>6998993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13826,11 +13824,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -13856,14 +13849,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13881,10 +13869,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131275137</v>
+        <v>131273409</v>
       </c>
       <c r="B105" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13892,29 +13880,24 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -13924,10 +13907,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546139</v>
+        <v>546299</v>
       </c>
       <c r="R105" t="n">
-        <v>6999047</v>
+        <v>6999454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13964,7 +13947,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13973,6 +13956,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13991,9 +13975,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14011,10 +14000,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131273377</v>
+        <v>131273419</v>
       </c>
       <c r="B106" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14022,31 +14011,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14054,10 +14038,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546077</v>
+        <v>546230</v>
       </c>
       <c r="R106" t="n">
-        <v>6999352</v>
+        <v>6999267</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14094,7 +14078,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14103,12 +14087,13 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -14121,14 +14106,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14146,10 +14136,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131275207</v>
+        <v>131273395</v>
       </c>
       <c r="B107" t="n">
-        <v>78261</v>
+        <v>80354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14157,21 +14147,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14184,10 +14174,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546365</v>
+        <v>546313</v>
       </c>
       <c r="R107" t="n">
-        <v>6998993</v>
+        <v>6999066</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14222,6 +14212,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -14247,9 +14242,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14267,27 +14267,27 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131273382</v>
+        <v>131273379</v>
       </c>
       <c r="B108" t="n">
-        <v>57728</v>
+        <v>57887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -14295,37 +14295,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>546360</v>
+        <v>546099</v>
       </c>
       <c r="R108" t="n">
-        <v>6999087</v>
+        <v>6999326</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14362,7 +14350,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14379,9 +14367,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14399,37 +14402,42 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131275172</v>
+        <v>131275143</v>
       </c>
       <c r="B109" t="n">
-        <v>80258</v>
+        <v>57887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -14437,10 +14445,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>546223</v>
+        <v>546149</v>
       </c>
       <c r="R109" t="n">
-        <v>6999048</v>
+        <v>6999065</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14475,13 +14483,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -14492,17 +14504,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14520,7 +14532,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131275143</v>
+        <v>131273376</v>
       </c>
       <c r="B110" t="n">
         <v>57887</v>
@@ -14553,7 +14565,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -14563,10 +14575,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>546149</v>
+        <v>546086</v>
       </c>
       <c r="R110" t="n">
-        <v>6999065</v>
+        <v>6999336</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14603,7 +14615,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14630,9 +14642,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14650,42 +14667,37 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131273379</v>
+        <v>131275172</v>
       </c>
       <c r="B111" t="n">
-        <v>57887</v>
+        <v>80258</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -14693,10 +14705,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>546099</v>
+        <v>546223</v>
       </c>
       <c r="R111" t="n">
-        <v>6999326</v>
+        <v>6999048</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14731,17 +14743,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -14752,22 +14760,17 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14785,10 +14788,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131273376</v>
+        <v>131275190</v>
       </c>
       <c r="B112" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14796,31 +14799,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -14828,10 +14826,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>546086</v>
+        <v>546145</v>
       </c>
       <c r="R112" t="n">
-        <v>6999336</v>
+        <v>6999134</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14868,7 +14866,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14877,6 +14875,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -14887,22 +14886,22 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14920,48 +14919,65 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131275190</v>
+        <v>131273382</v>
       </c>
       <c r="B113" t="n">
-        <v>80354</v>
+        <v>57728</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546145</v>
+        <v>546360</v>
       </c>
       <c r="R113" t="n">
-        <v>6999134</v>
+        <v>6999087</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14998,7 +15014,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15007,7 +15023,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -15016,24 +15031,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15307,10 +15307,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131275167</v>
+        <v>131273418</v>
       </c>
       <c r="B116" t="n">
-        <v>80220</v>
+        <v>79249</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15318,21 +15318,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546468</v>
+        <v>546329</v>
       </c>
       <c r="R116" t="n">
-        <v>6999037</v>
+        <v>6999224</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15383,6 +15383,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -15400,17 +15405,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15428,10 +15433,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275166</v>
+        <v>131273387</v>
       </c>
       <c r="B117" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15439,29 +15444,28 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15471,10 +15475,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546208</v>
+        <v>546286</v>
       </c>
       <c r="R117" t="n">
-        <v>6999393</v>
+        <v>6999419</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15511,7 +15515,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15520,6 +15524,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15530,17 +15535,22 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15558,32 +15568,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131273418</v>
+        <v>131275174</v>
       </c>
       <c r="B118" t="n">
-        <v>79249</v>
+        <v>75227</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15596,10 +15606,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546329</v>
+        <v>546222</v>
       </c>
       <c r="R118" t="n">
-        <v>6999224</v>
+        <v>6999408</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15636,7 +15646,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15656,17 +15666,22 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15684,10 +15699,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131273387</v>
+        <v>131275166</v>
       </c>
       <c r="B119" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15695,28 +15710,29 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -15726,10 +15742,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546286</v>
+        <v>546208</v>
       </c>
       <c r="R119" t="n">
-        <v>6999419</v>
+        <v>6999393</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15766,7 +15782,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15775,7 +15791,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -15786,22 +15801,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15819,32 +15829,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275174</v>
+        <v>131275167</v>
       </c>
       <c r="B120" t="n">
-        <v>75227</v>
+        <v>80220</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6428</v>
+        <v>388</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -15857,10 +15867,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546222</v>
+        <v>546468</v>
       </c>
       <c r="R120" t="n">
-        <v>6999408</v>
+        <v>6999037</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15895,11 +15905,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -15917,22 +15922,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16211,7 +16211,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131275148</v>
+        <v>131275133</v>
       </c>
       <c r="B123" t="n">
         <v>57887</v>
@@ -16244,7 +16244,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -16254,10 +16254,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>546118</v>
+        <v>546213</v>
       </c>
       <c r="R123" t="n">
-        <v>6999179</v>
+        <v>6999200</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16341,7 +16341,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131275133</v>
+        <v>131275148</v>
       </c>
       <c r="B124" t="n">
         <v>57887</v>
@@ -16374,7 +16374,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -16384,10 +16384,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>546213</v>
+        <v>546118</v>
       </c>
       <c r="R124" t="n">
-        <v>6999200</v>
+        <v>6999179</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16471,10 +16471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131273364</v>
+        <v>131275199</v>
       </c>
       <c r="B125" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16482,31 +16482,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -16514,10 +16509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546403</v>
+        <v>546147</v>
       </c>
       <c r="R125" t="n">
-        <v>6998994</v>
+        <v>6999326</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16552,17 +16547,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -16583,12 +16574,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16606,32 +16597,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131273383</v>
+        <v>131275171</v>
       </c>
       <c r="B126" t="n">
-        <v>80355</v>
+        <v>80258</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16644,10 +16635,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546292</v>
+        <v>546230</v>
       </c>
       <c r="R126" t="n">
-        <v>6999247</v>
+        <v>6999202</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16682,11 +16673,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Växer här på en lutande sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -16704,22 +16690,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16737,7 +16718,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275199</v>
+        <v>131275197</v>
       </c>
       <c r="B127" t="n">
         <v>80354</v>
@@ -16775,10 +16756,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546147</v>
+        <v>546130</v>
       </c>
       <c r="R127" t="n">
-        <v>6999326</v>
+        <v>6999313</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16830,22 +16811,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16863,7 +16844,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275171</v>
+        <v>131275173</v>
       </c>
       <c r="B128" t="n">
         <v>80258</v>
@@ -16901,10 +16882,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546230</v>
+        <v>546165</v>
       </c>
       <c r="R128" t="n">
-        <v>6999202</v>
+        <v>6999228</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16984,10 +16965,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131275197</v>
+        <v>131273383</v>
       </c>
       <c r="B129" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16995,21 +16976,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -17022,10 +17003,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546130</v>
+        <v>546292</v>
       </c>
       <c r="R129" t="n">
-        <v>6999313</v>
+        <v>6999247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17058,6 +17039,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Växer här på en lutande sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -17110,37 +17096,42 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131275173</v>
+        <v>131273364</v>
       </c>
       <c r="B130" t="n">
-        <v>80258</v>
+        <v>57887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -17148,10 +17139,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>546165</v>
+        <v>546403</v>
       </c>
       <c r="R130" t="n">
-        <v>6999228</v>
+        <v>6998994</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17186,13 +17177,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -17203,17 +17198,22 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -17361,10 +17361,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131273398</v>
+        <v>131273425</v>
       </c>
       <c r="B132" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17372,30 +17372,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -17403,10 +17399,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>546299</v>
+        <v>546106</v>
       </c>
       <c r="R132" t="n">
-        <v>6999243</v>
+        <v>6999416</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17443,7 +17439,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17463,22 +17459,22 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -17496,10 +17492,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131275125</v>
+        <v>131273398</v>
       </c>
       <c r="B133" t="n">
-        <v>83229</v>
+        <v>80354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17507,26 +17503,30 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -17534,10 +17534,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>546375</v>
+        <v>546299</v>
       </c>
       <c r="R133" t="n">
-        <v>6998987</v>
+        <v>6999243</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17572,6 +17572,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På en flerstammig gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -17589,17 +17594,22 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -17617,10 +17627,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131273411</v>
+        <v>131275125</v>
       </c>
       <c r="B134" t="n">
-        <v>79249</v>
+        <v>83229</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17628,21 +17638,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -17655,10 +17665,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>546421</v>
+        <v>546375</v>
       </c>
       <c r="R134" t="n">
-        <v>6999063</v>
+        <v>6998987</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17691,11 +17701,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17743,7 +17748,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131273425</v>
+        <v>131273411</v>
       </c>
       <c r="B135" t="n">
         <v>79249</v>
@@ -17781,10 +17786,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>546106</v>
+        <v>546421</v>
       </c>
       <c r="R135" t="n">
-        <v>6999416</v>
+        <v>6999063</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17821,7 +17826,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17849,14 +17854,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -18004,40 +18004,39 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131275147</v>
+        <v>131273408</v>
       </c>
       <c r="B137" t="n">
-        <v>57887</v>
+        <v>80390</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -18047,10 +18046,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>546137</v>
+        <v>546110</v>
       </c>
       <c r="R137" t="n">
-        <v>6999148</v>
+        <v>6999309</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -18087,7 +18086,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en flerstammig gammal sälg.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -18096,6 +18095,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -18106,17 +18106,22 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -18134,10 +18139,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131275136</v>
+        <v>131273390</v>
       </c>
       <c r="B138" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18145,29 +18150,28 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
@@ -18177,10 +18181,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>546148</v>
+        <v>546420</v>
       </c>
       <c r="R138" t="n">
-        <v>6999041</v>
+        <v>6999089</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18217,7 +18221,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18226,6 +18230,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -18236,17 +18241,22 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18264,10 +18274,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131275138</v>
+        <v>131275203</v>
       </c>
       <c r="B139" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18275,31 +18285,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -18307,10 +18312,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>546145</v>
+        <v>546227</v>
       </c>
       <c r="R139" t="n">
-        <v>6999053</v>
+        <v>6999420</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18345,17 +18350,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -18366,17 +18367,22 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18394,39 +18400,40 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131273408</v>
+        <v>131275138</v>
       </c>
       <c r="B140" t="n">
-        <v>80390</v>
+        <v>57887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -18436,10 +18443,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546110</v>
+        <v>546145</v>
       </c>
       <c r="R140" t="n">
-        <v>6999309</v>
+        <v>6999053</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18476,7 +18483,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18485,7 +18492,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -18496,22 +18502,17 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -18529,10 +18530,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131273390</v>
+        <v>131275147</v>
       </c>
       <c r="B141" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18540,28 +18541,29 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -18571,10 +18573,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546420</v>
+        <v>546137</v>
       </c>
       <c r="R141" t="n">
-        <v>6999089</v>
+        <v>6999148</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18611,7 +18613,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18620,7 +18622,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -18631,22 +18632,17 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -18664,10 +18660,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275203</v>
+        <v>131275136</v>
       </c>
       <c r="B142" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18675,26 +18671,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -18702,10 +18703,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546227</v>
+        <v>546148</v>
       </c>
       <c r="R142" t="n">
-        <v>6999420</v>
+        <v>6999041</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18740,13 +18741,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -18757,22 +18762,17 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -19051,10 +19051,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131275186</v>
+        <v>131276479</v>
       </c>
       <c r="B145" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19062,26 +19062,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -19089,10 +19094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>546206</v>
+        <v>546062</v>
       </c>
       <c r="R145" t="n">
-        <v>6999203</v>
+        <v>6999415</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -19129,7 +19134,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -19138,7 +19143,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -19149,22 +19153,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -19182,10 +19181,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131276485</v>
+        <v>131276480</v>
       </c>
       <c r="B146" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19193,26 +19192,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -19220,10 +19224,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>546409</v>
+        <v>546066</v>
       </c>
       <c r="R146" t="n">
-        <v>6999005</v>
+        <v>6999401</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19258,13 +19262,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -19275,22 +19283,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -19308,32 +19311,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275183</v>
+        <v>131275210</v>
       </c>
       <c r="B147" t="n">
-        <v>80354</v>
+        <v>80314</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19346,10 +19349,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546345</v>
+        <v>546168</v>
       </c>
       <c r="R147" t="n">
-        <v>6999035</v>
+        <v>6999217</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19397,6 +19400,26 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19414,10 +19437,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131275214</v>
+        <v>131275186</v>
       </c>
       <c r="B148" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19425,21 +19448,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -19452,10 +19475,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546193</v>
+        <v>546206</v>
       </c>
       <c r="R148" t="n">
-        <v>6999241</v>
+        <v>6999203</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19490,6 +19513,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -19507,17 +19535,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19535,10 +19568,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131276480</v>
+        <v>131276485</v>
       </c>
       <c r="B149" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -19546,31 +19579,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -19578,10 +19606,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546066</v>
+        <v>546409</v>
       </c>
       <c r="R149" t="n">
-        <v>6999401</v>
+        <v>6999005</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19616,17 +19644,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -19637,17 +19661,22 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19665,10 +19694,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131276479</v>
+        <v>131275183</v>
       </c>
       <c r="B150" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19676,31 +19705,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -19708,10 +19732,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546062</v>
+        <v>546345</v>
       </c>
       <c r="R150" t="n">
-        <v>6999415</v>
+        <v>6999035</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19746,38 +19770,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -19795,32 +19800,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131275210</v>
+        <v>131275214</v>
       </c>
       <c r="B151" t="n">
-        <v>80314</v>
+        <v>79249</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -19833,10 +19838,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546168</v>
+        <v>546193</v>
       </c>
       <c r="R151" t="n">
-        <v>6999217</v>
+        <v>6999241</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19888,22 +19893,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -19921,10 +19921,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131275130</v>
+        <v>131275177</v>
       </c>
       <c r="B152" t="n">
-        <v>57887</v>
+        <v>83224</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19932,31 +19932,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -19964,10 +19959,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546460</v>
+        <v>546303</v>
       </c>
       <c r="R152" t="n">
-        <v>6999069</v>
+        <v>6999065</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -20004,7 +19999,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20013,6 +20008,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -20021,19 +20017,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20051,10 +20057,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275177</v>
+        <v>131275130</v>
       </c>
       <c r="B153" t="n">
-        <v>83224</v>
+        <v>57887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20062,26 +20068,31 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -20089,10 +20100,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546303</v>
+        <v>546460</v>
       </c>
       <c r="R153" t="n">
-        <v>6999065</v>
+        <v>6999069</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20129,7 +20140,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20138,7 +20149,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -20147,29 +20157,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -21219,7 +21219,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131275162</v>
+        <v>131275157</v>
       </c>
       <c r="B162" t="n">
         <v>57887</v>
@@ -21262,10 +21262,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>546103</v>
+        <v>546111</v>
       </c>
       <c r="R162" t="n">
-        <v>6999294</v>
+        <v>6999255</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21479,7 +21479,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>131275157</v>
+        <v>131275162</v>
       </c>
       <c r="B164" t="n">
         <v>57887</v>
@@ -21522,10 +21522,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>546111</v>
+        <v>546103</v>
       </c>
       <c r="R164" t="n">
-        <v>6999255</v>
+        <v>6999294</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -21562,7 +21562,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131275215</v>
+        <v>131273397</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546164</v>
+        <v>546296</v>
       </c>
       <c r="R3" t="n">
-        <v>6999199</v>
+        <v>6999259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,17 +899,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131273397</v>
+        <v>131275187</v>
       </c>
       <c r="B4" t="n">
         <v>80355</v>
@@ -965,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546296</v>
+        <v>546202</v>
       </c>
       <c r="R4" t="n">
-        <v>6999259</v>
+        <v>6999223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,22 +1030,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131275180</v>
+        <v>131273378</v>
       </c>
       <c r="B5" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,26 +1069,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546406</v>
+        <v>546094</v>
       </c>
       <c r="R5" t="n">
-        <v>6999201</v>
+        <v>6999329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1141,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1150,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,17 +1160,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275187</v>
+        <v>131275145</v>
       </c>
       <c r="B6" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,26 +1204,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1222,10 +1236,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546202</v>
+        <v>546148</v>
       </c>
       <c r="R6" t="n">
-        <v>6999223</v>
+        <v>6999078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1276,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1285,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1282,17 +1295,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131273413</v>
+        <v>131275160</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,26 +1334,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1348,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546491</v>
+        <v>546104</v>
       </c>
       <c r="R7" t="n">
-        <v>6998962</v>
+        <v>6999263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,13 +1404,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1431,7 +1453,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273378</v>
+        <v>131276476</v>
       </c>
       <c r="B8" t="n">
         <v>57888</v>
@@ -1464,7 +1486,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1474,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546094</v>
+        <v>546050</v>
       </c>
       <c r="R8" t="n">
-        <v>6999329</v>
+        <v>6999453</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,14 +1563,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,10 +1583,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131275145</v>
+        <v>131273413</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,31 +1594,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1609,10 +1621,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546148</v>
+        <v>546491</v>
       </c>
       <c r="R9" t="n">
-        <v>6999078</v>
+        <v>6998962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1647,17 +1659,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1696,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275160</v>
+        <v>131275215</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,31 +1715,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1739,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546104</v>
+        <v>546164</v>
       </c>
       <c r="R10" t="n">
-        <v>6999263</v>
+        <v>6999199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,7 +1782,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,6 +1791,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1826,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131276476</v>
+        <v>131275180</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,31 +1841,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1869,10 +1868,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546050</v>
+        <v>546406</v>
       </c>
       <c r="R11" t="n">
-        <v>6999453</v>
+        <v>6999201</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1909,7 +1908,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,6 +1917,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131275176</v>
+        <v>131275206</v>
       </c>
       <c r="B28" t="n">
-        <v>75340</v>
+        <v>78262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1460</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546399</v>
+        <v>546408</v>
       </c>
       <c r="R28" t="n">
-        <v>6998994</v>
+        <v>6999129</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275175</v>
+        <v>131275176</v>
       </c>
       <c r="B29" t="n">
         <v>75340</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546372</v>
+        <v>546399</v>
       </c>
       <c r="R29" t="n">
-        <v>6998999</v>
+        <v>6998994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark av gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4273,10 +4268,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275191</v>
+        <v>131275175</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>75340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4284,21 +4279,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4311,10 +4306,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546174</v>
+        <v>546372</v>
       </c>
       <c r="R30" t="n">
-        <v>6999215</v>
+        <v>6998999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4351,7 +4346,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På bark av gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,12 +4366,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4386,7 +4381,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4404,7 +4399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275201</v>
+        <v>131275191</v>
       </c>
       <c r="B31" t="n">
         <v>80355</v>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546222</v>
+        <v>546174</v>
       </c>
       <c r="R31" t="n">
-        <v>6999418</v>
+        <v>6999215</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4480,6 +4475,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275178</v>
+        <v>131275201</v>
       </c>
       <c r="B32" t="n">
         <v>80355</v>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546403</v>
+        <v>546222</v>
       </c>
       <c r="R32" t="n">
-        <v>6999213</v>
+        <v>6999418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4619,6 +4619,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4636,10 +4656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275206</v>
+        <v>131275178</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>80355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,21 +4667,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4674,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546408</v>
+        <v>546403</v>
       </c>
       <c r="R33" t="n">
-        <v>6999129</v>
+        <v>6999213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,26 +4745,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -12283,47 +12283,39 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131275217</v>
+        <v>131273362</v>
       </c>
       <c r="B93" t="n">
-        <v>83217</v>
+        <v>91818</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>307</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -12333,10 +12325,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546307</v>
+        <v>546302</v>
       </c>
       <c r="R93" t="n">
-        <v>6999069</v>
+        <v>6999463</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12373,7 +12365,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12391,34 +12383,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12436,32 +12418,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131275209</v>
+        <v>131273424</v>
       </c>
       <c r="B94" t="n">
-        <v>80315</v>
+        <v>79250</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12474,10 +12456,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546171</v>
+        <v>546090</v>
       </c>
       <c r="R94" t="n">
-        <v>6999219</v>
+        <v>6999323</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12512,6 +12494,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12529,22 +12516,17 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12562,10 +12544,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131273362</v>
+        <v>131276477</v>
       </c>
       <c r="B95" t="n">
-        <v>91818</v>
+        <v>57888</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12573,28 +12555,29 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -12604,10 +12587,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546302</v>
+        <v>546062</v>
       </c>
       <c r="R95" t="n">
-        <v>6999463</v>
+        <v>6999442</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12644,7 +12627,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12653,7 +12636,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12672,14 +12654,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12697,10 +12674,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131273424</v>
+        <v>131275135</v>
       </c>
       <c r="B96" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12708,26 +12685,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -12735,10 +12717,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546090</v>
+        <v>546142</v>
       </c>
       <c r="R96" t="n">
-        <v>6999323</v>
+        <v>6999047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12775,7 +12757,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12784,7 +12766,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12823,7 +12804,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131276477</v>
+        <v>131275158</v>
       </c>
       <c r="B97" t="n">
         <v>57888</v>
@@ -12866,10 +12847,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546062</v>
+        <v>546100</v>
       </c>
       <c r="R97" t="n">
-        <v>6999442</v>
+        <v>6999268</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12953,7 +12934,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131275135</v>
+        <v>131273366</v>
       </c>
       <c r="B98" t="n">
         <v>57888</v>
@@ -12996,10 +12977,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546142</v>
+        <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999047</v>
+        <v>6999258</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13036,7 +13017,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13063,9 +13044,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13083,42 +13069,37 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131275158</v>
+        <v>131275209</v>
       </c>
       <c r="B99" t="n">
-        <v>57888</v>
+        <v>80315</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13126,10 +13107,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546100</v>
+        <v>546171</v>
       </c>
       <c r="R99" t="n">
-        <v>6999268</v>
+        <v>6999219</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13164,17 +13145,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13185,17 +13162,22 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13213,40 +13195,47 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131273366</v>
+        <v>131275217</v>
       </c>
       <c r="B100" t="n">
-        <v>57888</v>
+        <v>83217</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -13256,10 +13245,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546100</v>
+        <v>546307</v>
       </c>
       <c r="R100" t="n">
-        <v>6999258</v>
+        <v>6999069</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13296,7 +13285,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13305,6 +13294,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13313,24 +13303,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273409</v>
+        <v>131275207</v>
       </c>
       <c r="B101" t="n">
-        <v>91838</v>
+        <v>78262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,26 +13359,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546299</v>
+        <v>546365</v>
       </c>
       <c r="R101" t="n">
-        <v>6999454</v>
+        <v>6998993</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13424,11 +13424,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -13454,14 +13449,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13479,10 +13469,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273419</v>
+        <v>131275137</v>
       </c>
       <c r="B102" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13490,26 +13480,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13517,10 +13512,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546230</v>
+        <v>546139</v>
       </c>
       <c r="R102" t="n">
-        <v>6999267</v>
+        <v>6999047</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13557,7 +13552,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13566,13 +13561,12 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13585,19 +13579,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13615,10 +13599,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131273395</v>
+        <v>131273377</v>
       </c>
       <c r="B103" t="n">
-        <v>80355</v>
+        <v>57888</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13626,26 +13610,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13653,10 +13642,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546313</v>
+        <v>546077</v>
       </c>
       <c r="R103" t="n">
-        <v>6999066</v>
+        <v>6999352</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13693,7 +13682,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13702,7 +13691,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13723,12 +13711,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13746,10 +13734,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131273380</v>
+        <v>131273409</v>
       </c>
       <c r="B104" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13757,29 +13745,24 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -13789,10 +13772,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546091</v>
+        <v>546299</v>
       </c>
       <c r="R104" t="n">
-        <v>6999334</v>
+        <v>6999454</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13829,7 +13812,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13838,6 +13821,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13858,12 +13842,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13881,10 +13865,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131275137</v>
+        <v>131273419</v>
       </c>
       <c r="B105" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13892,31 +13876,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13924,10 +13903,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546139</v>
+        <v>546230</v>
       </c>
       <c r="R105" t="n">
-        <v>6999047</v>
+        <v>6999267</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13964,7 +13943,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13973,12 +13952,13 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -13991,9 +13971,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14011,10 +14001,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131273377</v>
+        <v>131273395</v>
       </c>
       <c r="B106" t="n">
-        <v>57888</v>
+        <v>80355</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14022,31 +14012,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14054,10 +14039,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546077</v>
+        <v>546313</v>
       </c>
       <c r="R106" t="n">
-        <v>6999352</v>
+        <v>6999066</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14094,7 +14079,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14103,6 +14088,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -14123,12 +14109,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14146,10 +14132,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131275207</v>
+        <v>131273380</v>
       </c>
       <c r="B107" t="n">
-        <v>78262</v>
+        <v>57888</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14157,26 +14143,31 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14184,10 +14175,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546365</v>
+        <v>546091</v>
       </c>
       <c r="R107" t="n">
-        <v>6998993</v>
+        <v>6999334</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14222,13 +14213,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -14247,9 +14242,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -15051,10 +15051,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131273387</v>
+        <v>131275167</v>
       </c>
       <c r="B114" t="n">
-        <v>80355</v>
+        <v>80221</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15062,30 +15062,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15093,10 +15089,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546286</v>
+        <v>546468</v>
       </c>
       <c r="R114" t="n">
-        <v>6999419</v>
+        <v>6999037</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15131,11 +15127,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -15153,22 +15144,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15186,10 +15172,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275174</v>
+        <v>131273363</v>
       </c>
       <c r="B115" t="n">
-        <v>75228</v>
+        <v>92540</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15197,26 +15183,30 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6428</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15224,10 +15214,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546222</v>
+        <v>546304</v>
       </c>
       <c r="R115" t="n">
-        <v>6999408</v>
+        <v>6999379</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15264,7 +15254,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15284,22 +15274,22 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15317,10 +15307,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273418</v>
+        <v>131275166</v>
       </c>
       <c r="B116" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15328,26 +15318,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15355,10 +15350,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546329</v>
+        <v>546208</v>
       </c>
       <c r="R116" t="n">
-        <v>6999224</v>
+        <v>6999393</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15395,7 +15390,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15404,7 +15399,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15443,10 +15437,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275212</v>
+        <v>131273387</v>
       </c>
       <c r="B117" t="n">
-        <v>91838</v>
+        <v>80355</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15454,24 +15448,28 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15481,10 +15479,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546213</v>
+        <v>546286</v>
       </c>
       <c r="R117" t="n">
-        <v>6999022</v>
+        <v>6999419</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15519,6 +15517,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -15536,17 +15539,22 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15564,42 +15572,37 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131275166</v>
+        <v>131275174</v>
       </c>
       <c r="B118" t="n">
-        <v>57888</v>
+        <v>75228</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15607,10 +15610,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546208</v>
+        <v>546222</v>
       </c>
       <c r="R118" t="n">
-        <v>6999393</v>
+        <v>6999408</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15647,7 +15650,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15656,6 +15659,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -15666,17 +15670,22 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15694,10 +15703,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131275167</v>
+        <v>131273418</v>
       </c>
       <c r="B119" t="n">
-        <v>80221</v>
+        <v>79250</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15705,21 +15714,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -15732,10 +15741,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546468</v>
+        <v>546329</v>
       </c>
       <c r="R119" t="n">
-        <v>6999037</v>
+        <v>6999224</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15770,6 +15779,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -15787,17 +15801,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15815,34 +15829,30 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131273363</v>
+        <v>131275212</v>
       </c>
       <c r="B120" t="n">
-        <v>92540</v>
+        <v>91838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -15857,10 +15867,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546304</v>
+        <v>546213</v>
       </c>
       <c r="R120" t="n">
-        <v>6999379</v>
+        <v>6999022</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15895,11 +15905,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -15925,14 +15930,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16471,10 +16471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131273383</v>
+        <v>131275199</v>
       </c>
       <c r="B125" t="n">
-        <v>80356</v>
+        <v>80355</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16482,21 +16482,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546292</v>
+        <v>546147</v>
       </c>
       <c r="R125" t="n">
-        <v>6999247</v>
+        <v>6999326</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16547,11 +16547,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Växer här på en lutande sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -16569,22 +16564,22 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16602,32 +16597,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131275199</v>
+        <v>131275171</v>
       </c>
       <c r="B126" t="n">
-        <v>80355</v>
+        <v>80259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16640,10 +16635,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546147</v>
+        <v>546230</v>
       </c>
       <c r="R126" t="n">
-        <v>6999326</v>
+        <v>6999202</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16695,22 +16690,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16728,32 +16718,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275171</v>
+        <v>131275197</v>
       </c>
       <c r="B127" t="n">
-        <v>80259</v>
+        <v>80355</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -16766,10 +16756,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546230</v>
+        <v>546130</v>
       </c>
       <c r="R127" t="n">
-        <v>6999202</v>
+        <v>6999313</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16821,17 +16811,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16849,32 +16844,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275197</v>
+        <v>131275173</v>
       </c>
       <c r="B128" t="n">
-        <v>80355</v>
+        <v>80259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -16887,10 +16882,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546130</v>
+        <v>546165</v>
       </c>
       <c r="R128" t="n">
-        <v>6999313</v>
+        <v>6999228</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16942,22 +16937,17 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -16975,32 +16965,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131275173</v>
+        <v>131273383</v>
       </c>
       <c r="B129" t="n">
-        <v>80259</v>
+        <v>80356</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -17013,10 +17003,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546165</v>
+        <v>546292</v>
       </c>
       <c r="R129" t="n">
-        <v>6999228</v>
+        <v>6999247</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17051,6 +17041,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Växer här på en lutande sälg intill lunglav.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -17068,17 +17063,22 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -17361,10 +17361,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131273411</v>
+        <v>131273398</v>
       </c>
       <c r="B132" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17372,26 +17372,30 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -17399,10 +17403,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>546421</v>
+        <v>546299</v>
       </c>
       <c r="R132" t="n">
-        <v>6999063</v>
+        <v>6999243</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17439,7 +17443,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en flerstammig gammal sälg.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17459,17 +17463,22 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -17487,10 +17496,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131273398</v>
+        <v>131273411</v>
       </c>
       <c r="B133" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17498,30 +17507,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -17529,10 +17534,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>546299</v>
+        <v>546421</v>
       </c>
       <c r="R133" t="n">
-        <v>6999243</v>
+        <v>6999063</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17569,7 +17574,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17589,22 +17594,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -18400,37 +18400,42 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131275208</v>
+        <v>131275147</v>
       </c>
       <c r="B140" t="n">
-        <v>80315</v>
+        <v>57888</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -18438,10 +18443,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546460</v>
+        <v>546137</v>
       </c>
       <c r="R140" t="n">
-        <v>6999073</v>
+        <v>6999148</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18476,13 +18481,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -18493,22 +18502,17 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -18526,7 +18530,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131275147</v>
+        <v>131275136</v>
       </c>
       <c r="B141" t="n">
         <v>57888</v>
@@ -18569,10 +18573,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546137</v>
+        <v>546148</v>
       </c>
       <c r="R141" t="n">
-        <v>6999148</v>
+        <v>6999041</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18656,7 +18660,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275136</v>
+        <v>131275138</v>
       </c>
       <c r="B142" t="n">
         <v>57888</v>
@@ -18699,10 +18703,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546148</v>
+        <v>546145</v>
       </c>
       <c r="R142" t="n">
-        <v>6999041</v>
+        <v>6999053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18786,42 +18790,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131275138</v>
+        <v>131275208</v>
       </c>
       <c r="B143" t="n">
-        <v>57888</v>
+        <v>80315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -18829,10 +18828,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>546145</v>
+        <v>546460</v>
       </c>
       <c r="R143" t="n">
-        <v>6999053</v>
+        <v>6999073</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18867,17 +18866,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -18888,17 +18883,22 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -19047,32 +19047,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131276485</v>
+        <v>131275210</v>
       </c>
       <c r="B145" t="n">
-        <v>80355</v>
+        <v>80315</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -19085,10 +19085,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>546409</v>
+        <v>546168</v>
       </c>
       <c r="R145" t="n">
-        <v>6999005</v>
+        <v>6999217</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -19140,12 +19140,12 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -19173,7 +19173,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131275183</v>
+        <v>131276485</v>
       </c>
       <c r="B146" t="n">
         <v>80355</v>
@@ -19211,10 +19211,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>546345</v>
+        <v>546409</v>
       </c>
       <c r="R146" t="n">
-        <v>6999035</v>
+        <v>6999005</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19262,6 +19262,26 @@
       <c r="AH146" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -19279,10 +19299,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275214</v>
+        <v>131275183</v>
       </c>
       <c r="B147" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19290,21 +19310,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19317,10 +19337,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546193</v>
+        <v>546345</v>
       </c>
       <c r="R147" t="n">
-        <v>6999241</v>
+        <v>6999035</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19368,21 +19388,6 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19400,10 +19405,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131273367</v>
+        <v>131275214</v>
       </c>
       <c r="B148" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19411,31 +19416,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -19443,10 +19443,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546103</v>
+        <v>546193</v>
       </c>
       <c r="R148" t="n">
-        <v>6999266</v>
+        <v>6999241</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19481,17 +19481,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -19510,14 +19506,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19535,7 +19526,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131276480</v>
+        <v>131273367</v>
       </c>
       <c r="B149" t="n">
         <v>57888</v>
@@ -19578,10 +19569,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546066</v>
+        <v>546103</v>
       </c>
       <c r="R149" t="n">
-        <v>6999401</v>
+        <v>6999266</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19618,7 +19609,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -19645,9 +19636,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19665,7 +19661,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131276479</v>
+        <v>131276480</v>
       </c>
       <c r="B150" t="n">
         <v>57888</v>
@@ -19708,10 +19704,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546062</v>
+        <v>546066</v>
       </c>
       <c r="R150" t="n">
-        <v>6999415</v>
+        <v>6999401</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19795,37 +19791,42 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131275210</v>
+        <v>131276479</v>
       </c>
       <c r="B151" t="n">
-        <v>80315</v>
+        <v>57888</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -19833,10 +19834,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546168</v>
+        <v>546062</v>
       </c>
       <c r="R151" t="n">
-        <v>6999217</v>
+        <v>6999415</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19871,13 +19872,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -19888,22 +19893,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131275215</v>
+        <v>131275145</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546164</v>
+        <v>546148</v>
       </c>
       <c r="R2" t="n">
-        <v>6999199</v>
+        <v>6999078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -801,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131273397</v>
+        <v>131276476</v>
       </c>
       <c r="B3" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +816,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546296</v>
+        <v>546050</v>
       </c>
       <c r="R3" t="n">
-        <v>6999259</v>
+        <v>6999453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +897,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,22 +907,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275180</v>
+        <v>131273378</v>
       </c>
       <c r="B4" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,26 +946,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546406</v>
+        <v>546094</v>
       </c>
       <c r="R4" t="n">
-        <v>6999201</v>
+        <v>6999329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1027,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,17 +1037,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131275187</v>
+        <v>131275160</v>
       </c>
       <c r="B5" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,26 +1081,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1096,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546202</v>
+        <v>546104</v>
       </c>
       <c r="R5" t="n">
-        <v>6999223</v>
+        <v>6999263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,7 +1153,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1162,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,17 +1172,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275145</v>
+        <v>131273413</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,31 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546148</v>
+        <v>546491</v>
       </c>
       <c r="R6" t="n">
-        <v>6999078</v>
+        <v>6998962</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,17 +1276,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1314,10 +1321,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131276476</v>
+        <v>131273422</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,31 +1332,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1357,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546050</v>
+        <v>546111</v>
       </c>
       <c r="R7" t="n">
-        <v>6999453</v>
+        <v>6999297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,7 +1399,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,6 +1408,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1444,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273413</v>
+        <v>131275215</v>
       </c>
       <c r="B8" t="n">
         <v>79254</v>
@@ -1482,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546491</v>
+        <v>546164</v>
       </c>
       <c r="R8" t="n">
-        <v>6998962</v>
+        <v>6999199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1518,6 +1521,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131273422</v>
+        <v>131273397</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>80359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,21 +1584,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1603,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546111</v>
+        <v>546296</v>
       </c>
       <c r="R9" t="n">
-        <v>6999297</v>
+        <v>6999259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,7 +1651,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,17 +1671,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1691,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131273378</v>
+        <v>131275180</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,31 +1715,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1734,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546094</v>
+        <v>546406</v>
       </c>
       <c r="R10" t="n">
-        <v>6999329</v>
+        <v>6999201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1774,7 +1782,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,6 +1791,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1793,22 +1802,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1826,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131275160</v>
+        <v>131275187</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,31 +1841,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1869,10 +1868,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546104</v>
+        <v>546202</v>
       </c>
       <c r="R11" t="n">
-        <v>6999263</v>
+        <v>6999223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1909,7 +1908,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,6 +1917,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131273410</v>
+        <v>131276478</v>
       </c>
       <c r="B51" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6920,26 +6920,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6947,10 +6952,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546342</v>
+        <v>546058</v>
       </c>
       <c r="R51" t="n">
-        <v>6999195</v>
+        <v>6999435</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6985,13 +6990,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7030,10 +7039,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131276478</v>
+        <v>131273410</v>
       </c>
       <c r="B52" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7041,31 +7050,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7073,10 +7077,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546058</v>
+        <v>546342</v>
       </c>
       <c r="R52" t="n">
-        <v>6999435</v>
+        <v>6999195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7111,17 +7115,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131275129</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,31 +7696,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546338</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999380</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7766,17 +7761,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7787,17 +7778,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7815,7 +7811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131275195</v>
+        <v>131273394</v>
       </c>
       <c r="B58" t="n">
         <v>80359</v>
@@ -7845,7 +7841,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546150</v>
+        <v>546346</v>
       </c>
       <c r="R58" t="n">
-        <v>6999197</v>
+        <v>6999078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7891,6 +7891,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7908,12 +7913,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7923,7 +7928,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7941,7 +7946,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273394</v>
+        <v>131276488</v>
       </c>
       <c r="B59" t="n">
         <v>80359</v>
@@ -7971,11 +7976,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7983,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546346</v>
+        <v>546062</v>
       </c>
       <c r="R59" t="n">
-        <v>6999078</v>
+        <v>6999441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8019,11 +8020,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8076,7 +8072,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276488</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
         <v>80359</v>
@@ -8114,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546062</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999441</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8202,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131276491</v>
+        <v>131273412</v>
       </c>
       <c r="B61" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8213,21 +8209,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8240,10 +8236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546074</v>
+        <v>546441</v>
       </c>
       <c r="R61" t="n">
-        <v>6999366</v>
+        <v>6999013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8295,22 +8291,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8328,10 +8319,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131273412</v>
+        <v>131275129</v>
       </c>
       <c r="B62" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8339,26 +8330,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8366,10 +8362,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>546441</v>
+        <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999013</v>
+        <v>6999380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8404,13 +8400,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131276481</v>
+        <v>131275211</v>
       </c>
       <c r="B65" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,29 +8725,24 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8757,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546070</v>
+        <v>546185</v>
       </c>
       <c r="R65" t="n">
-        <v>6999374</v>
+        <v>6999135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8795,17 +8790,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8835,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131275211</v>
+        <v>131273414</v>
       </c>
       <c r="B66" t="n">
-        <v>91842</v>
+        <v>79254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8855,26 +8846,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8882,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546185</v>
+        <v>546430</v>
       </c>
       <c r="R66" t="n">
-        <v>6999135</v>
+        <v>6998969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8965,10 +8956,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273414</v>
+        <v>131275200</v>
       </c>
       <c r="B67" t="n">
-        <v>79254</v>
+        <v>80359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8976,21 +8967,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9003,10 +8994,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546430</v>
+        <v>546174</v>
       </c>
       <c r="R67" t="n">
-        <v>6998969</v>
+        <v>6999354</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9058,17 +9049,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9086,7 +9082,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131275200</v>
+        <v>131273384</v>
       </c>
       <c r="B68" t="n">
         <v>80359</v>
@@ -9115,19 +9111,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546174</v>
+        <v>546286</v>
       </c>
       <c r="R68" t="n">
-        <v>6999354</v>
+        <v>6999257</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9162,40 +9155,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Fertil med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9212,10 +9184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273384</v>
+        <v>131273420</v>
       </c>
       <c r="B69" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9223,34 +9195,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546286</v>
+        <v>546204</v>
       </c>
       <c r="R69" t="n">
-        <v>6999257</v>
+        <v>6999267</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9287,7 +9262,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9296,8 +9271,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9314,10 +9310,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273420</v>
+        <v>131273386</v>
       </c>
       <c r="B70" t="n">
-        <v>79254</v>
+        <v>80359</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9325,26 +9321,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546204</v>
+        <v>546294</v>
       </c>
       <c r="R70" t="n">
-        <v>6999267</v>
+        <v>6999434</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9412,17 +9412,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9440,10 +9445,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273386</v>
+        <v>131273416</v>
       </c>
       <c r="B71" t="n">
-        <v>80359</v>
+        <v>79254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9451,30 +9456,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9482,10 +9483,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546294</v>
+        <v>546387</v>
       </c>
       <c r="R71" t="n">
-        <v>6999434</v>
+        <v>6999068</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9522,7 +9523,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9542,22 +9543,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9575,10 +9571,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273416</v>
+        <v>131273371</v>
       </c>
       <c r="B72" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9586,26 +9582,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9613,10 +9614,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546387</v>
+        <v>546089</v>
       </c>
       <c r="R72" t="n">
-        <v>6999068</v>
+        <v>6999267</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9653,7 +9654,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9662,7 +9663,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9701,7 +9701,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273371</v>
+        <v>131273372</v>
       </c>
       <c r="B73" t="n">
         <v>57892</v>
@@ -9734,7 +9734,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9747,7 +9747,7 @@
         <v>546089</v>
       </c>
       <c r="R73" t="n">
-        <v>6999267</v>
+        <v>6999297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9811,9 +9811,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9831,7 +9836,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273372</v>
+        <v>131276481</v>
       </c>
       <c r="B74" t="n">
         <v>57892</v>
@@ -9874,10 +9879,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546089</v>
+        <v>546070</v>
       </c>
       <c r="R74" t="n">
-        <v>6999297</v>
+        <v>6999374</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9914,7 +9919,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9941,14 +9946,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -11128,37 +11128,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131275170</v>
+        <v>131275164</v>
       </c>
       <c r="B84" t="n">
-        <v>83225</v>
+        <v>57892</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11166,10 +11171,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>546401</v>
+        <v>546097</v>
       </c>
       <c r="R84" t="n">
-        <v>6999141</v>
+        <v>6999287</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11204,13 +11209,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11221,22 +11230,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11254,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131275204</v>
+        <v>131275161</v>
       </c>
       <c r="B85" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11265,26 +11269,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11292,10 +11301,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546244</v>
+        <v>546100</v>
       </c>
       <c r="R85" t="n">
-        <v>6999418</v>
+        <v>6999276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11330,13 +11339,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11347,22 +11360,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11380,10 +11388,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131276483</v>
+        <v>131275165</v>
       </c>
       <c r="B86" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11391,26 +11399,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11418,10 +11431,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546404</v>
+        <v>546098</v>
       </c>
       <c r="R86" t="n">
-        <v>6999205</v>
+        <v>6999296</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11456,13 +11469,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11473,22 +11490,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11506,32 +11518,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131275205</v>
+        <v>131275170</v>
       </c>
       <c r="B87" t="n">
-        <v>80359</v>
+        <v>83225</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11544,10 +11556,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546149</v>
+        <v>546401</v>
       </c>
       <c r="R87" t="n">
-        <v>6999093</v>
+        <v>6999141</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11632,7 +11644,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131273388</v>
+        <v>131275204</v>
       </c>
       <c r="B88" t="n">
         <v>80359</v>
@@ -11662,11 +11674,7 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11674,10 +11682,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546370</v>
+        <v>546244</v>
       </c>
       <c r="R88" t="n">
-        <v>6999140</v>
+        <v>6999418</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11712,11 +11720,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11749,7 +11752,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11767,7 +11770,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131275188</v>
+        <v>131276483</v>
       </c>
       <c r="B89" t="n">
         <v>80359</v>
@@ -11805,10 +11808,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546149</v>
+        <v>546404</v>
       </c>
       <c r="R89" t="n">
-        <v>6999276</v>
+        <v>6999205</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11843,11 +11846,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -11865,17 +11863,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11893,10 +11896,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275164</v>
+        <v>131275205</v>
       </c>
       <c r="B90" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11904,31 +11907,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11936,10 +11934,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546097</v>
+        <v>546149</v>
       </c>
       <c r="R90" t="n">
-        <v>6999287</v>
+        <v>6999093</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11974,17 +11972,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11995,17 +11989,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12023,10 +12022,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131275161</v>
+        <v>131273388</v>
       </c>
       <c r="B91" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12034,29 +12033,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12066,10 +12064,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546100</v>
+        <v>546370</v>
       </c>
       <c r="R91" t="n">
-        <v>6999276</v>
+        <v>6999140</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12106,7 +12104,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12115,6 +12113,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12125,17 +12124,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275165</v>
+        <v>131275188</v>
       </c>
       <c r="B92" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12164,31 +12168,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12196,10 +12195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546098</v>
+        <v>546149</v>
       </c>
       <c r="R92" t="n">
-        <v>6999296</v>
+        <v>6999276</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12236,7 +12235,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12245,6 +12244,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131275137</v>
+        <v>131273409</v>
       </c>
       <c r="B101" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,29 +13359,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -13391,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546139</v>
+        <v>546299</v>
       </c>
       <c r="R101" t="n">
-        <v>6999047</v>
+        <v>6999454</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13431,7 +13426,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13440,6 +13435,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13458,9 +13454,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13478,7 +13479,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273380</v>
+        <v>131275137</v>
       </c>
       <c r="B102" t="n">
         <v>57892</v>
@@ -13521,10 +13522,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546091</v>
+        <v>546139</v>
       </c>
       <c r="R102" t="n">
-        <v>6999334</v>
+        <v>6999047</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13561,7 +13562,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13588,14 +13589,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13613,7 +13609,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131273377</v>
+        <v>131273380</v>
       </c>
       <c r="B103" t="n">
         <v>57892</v>
@@ -13656,10 +13652,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546077</v>
+        <v>546091</v>
       </c>
       <c r="R103" t="n">
-        <v>6999352</v>
+        <v>6999334</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13696,7 +13692,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13748,10 +13744,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131275207</v>
+        <v>131273377</v>
       </c>
       <c r="B104" t="n">
-        <v>78266</v>
+        <v>57892</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13759,26 +13755,31 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13786,10 +13787,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546365</v>
+        <v>546077</v>
       </c>
       <c r="R104" t="n">
-        <v>6998993</v>
+        <v>6999352</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13824,13 +13825,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13849,9 +13854,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13869,10 +13879,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131273409</v>
+        <v>131275207</v>
       </c>
       <c r="B105" t="n">
-        <v>91842</v>
+        <v>78266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13880,26 +13890,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13907,10 +13917,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546299</v>
+        <v>546365</v>
       </c>
       <c r="R105" t="n">
-        <v>6999454</v>
+        <v>6998993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13945,11 +13955,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -13975,14 +13980,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14267,37 +14267,42 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131275172</v>
+        <v>131275143</v>
       </c>
       <c r="B108" t="n">
-        <v>80263</v>
+        <v>57892</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -14305,10 +14310,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>546223</v>
+        <v>546149</v>
       </c>
       <c r="R108" t="n">
-        <v>6999048</v>
+        <v>6999065</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14343,13 +14348,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -14360,17 +14369,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14388,10 +14397,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131275190</v>
+        <v>131273379</v>
       </c>
       <c r="B109" t="n">
-        <v>80359</v>
+        <v>57892</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14399,26 +14408,31 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -14426,10 +14440,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>546145</v>
+        <v>546099</v>
       </c>
       <c r="R109" t="n">
-        <v>6999134</v>
+        <v>6999326</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14466,7 +14480,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14475,7 +14489,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -14486,22 +14499,22 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14519,7 +14532,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131275143</v>
+        <v>131273376</v>
       </c>
       <c r="B110" t="n">
         <v>57892</v>
@@ -14552,7 +14565,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -14562,10 +14575,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>546149</v>
+        <v>546086</v>
       </c>
       <c r="R110" t="n">
-        <v>6999065</v>
+        <v>6999336</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14602,7 +14615,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14629,9 +14642,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -14649,27 +14667,27 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131273379</v>
+        <v>131273382</v>
       </c>
       <c r="B111" t="n">
-        <v>57892</v>
+        <v>57733</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -14677,25 +14695,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>546099</v>
+        <v>546360</v>
       </c>
       <c r="R111" t="n">
-        <v>6999326</v>
+        <v>6999087</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14732,7 +14762,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14749,24 +14779,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -14784,42 +14799,37 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131273376</v>
+        <v>131275172</v>
       </c>
       <c r="B112" t="n">
-        <v>57892</v>
+        <v>80263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -14827,10 +14837,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>546086</v>
+        <v>546223</v>
       </c>
       <c r="R112" t="n">
-        <v>6999336</v>
+        <v>6999048</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14865,17 +14875,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -14886,22 +14892,17 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -14919,65 +14920,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131273382</v>
+        <v>131275190</v>
       </c>
       <c r="B113" t="n">
-        <v>57733</v>
+        <v>80359</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546360</v>
+        <v>546145</v>
       </c>
       <c r="R113" t="n">
-        <v>6999087</v>
+        <v>6999134</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15014,7 +14998,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Observation av en hane med tydlig sång under en lång stund vid skymningstid i äldre granskog med höga naturvärden.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15023,6 +15007,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -15031,9 +15016,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>Äldre bitvis flerskiktad granskog med inslag av björk, asp och sälg.</t>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -16085,10 +16085,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131275216</v>
+        <v>131275148</v>
       </c>
       <c r="B122" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16096,26 +16096,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -16123,10 +16128,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>546240</v>
+        <v>546118</v>
       </c>
       <c r="R122" t="n">
-        <v>6999411</v>
+        <v>6999179</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16163,7 +16168,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16172,7 +16177,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16211,7 +16215,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131275148</v>
+        <v>131275133</v>
       </c>
       <c r="B123" t="n">
         <v>57892</v>
@@ -16244,7 +16248,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -16254,10 +16258,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>546118</v>
+        <v>546213</v>
       </c>
       <c r="R123" t="n">
-        <v>6999179</v>
+        <v>6999200</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16294,7 +16298,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16341,10 +16345,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131275133</v>
+        <v>131275216</v>
       </c>
       <c r="B124" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16352,31 +16356,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -16384,10 +16383,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>546213</v>
+        <v>546240</v>
       </c>
       <c r="R124" t="n">
-        <v>6999200</v>
+        <v>6999411</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16424,7 +16423,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16433,6 +16432,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131275129</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,31 +7696,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546338</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999380</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7766,17 +7761,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7787,17 +7778,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7815,10 +7811,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131273373</v>
+        <v>131273394</v>
       </c>
       <c r="B58" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7826,29 +7822,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7858,10 +7853,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546097</v>
+        <v>546346</v>
       </c>
       <c r="R58" t="n">
-        <v>6999307</v>
+        <v>6999078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7898,7 +7893,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7907,6 +7902,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7917,22 +7913,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7950,10 +7946,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131276475</v>
+        <v>131276488</v>
       </c>
       <c r="B59" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7961,31 +7957,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7993,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546338</v>
+        <v>546062</v>
       </c>
       <c r="R59" t="n">
-        <v>6999168</v>
+        <v>6999441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8031,17 +8022,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8052,17 +8039,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8080,7 +8072,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131275195</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
         <v>80365</v>
@@ -8118,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546150</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999197</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8173,12 +8165,12 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -8188,7 +8180,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8206,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131273394</v>
+        <v>131273412</v>
       </c>
       <c r="B61" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8217,30 +8209,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8248,10 +8236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546346</v>
+        <v>546441</v>
       </c>
       <c r="R61" t="n">
-        <v>6999078</v>
+        <v>6999013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8286,11 +8274,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8308,22 +8291,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8341,10 +8319,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131276488</v>
+        <v>131275129</v>
       </c>
       <c r="B62" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8352,26 +8330,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8379,10 +8362,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>546062</v>
+        <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999441</v>
+        <v>6999380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8417,13 +8400,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8434,22 +8421,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8467,10 +8449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131276491</v>
+        <v>131273373</v>
       </c>
       <c r="B63" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8478,26 +8460,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8505,10 +8492,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546074</v>
+        <v>546097</v>
       </c>
       <c r="R63" t="n">
-        <v>6999366</v>
+        <v>6999307</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8543,13 +8530,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8560,22 +8551,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8593,10 +8584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131273412</v>
+        <v>131276475</v>
       </c>
       <c r="B64" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8604,26 +8595,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8631,10 +8627,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546441</v>
+        <v>546338</v>
       </c>
       <c r="R64" t="n">
-        <v>6999013</v>
+        <v>6999168</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8669,13 +8665,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131275200</v>
+        <v>131273371</v>
       </c>
       <c r="B65" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8757,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546174</v>
+        <v>546089</v>
       </c>
       <c r="R65" t="n">
-        <v>6999354</v>
+        <v>6999267</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8790,13 +8795,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8807,22 +8816,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8840,10 +8844,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273384</v>
+        <v>131276481</v>
       </c>
       <c r="B66" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8851,34 +8855,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546286</v>
+        <v>546070</v>
       </c>
       <c r="R66" t="n">
-        <v>6999257</v>
+        <v>6999374</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8915,7 +8927,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8926,6 +8938,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8942,10 +8974,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131275211</v>
+        <v>131273372</v>
       </c>
       <c r="B67" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8953,24 +8985,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8980,10 +9017,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546185</v>
+        <v>546089</v>
       </c>
       <c r="R67" t="n">
-        <v>6999135</v>
+        <v>6999297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9018,13 +9055,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9043,9 +9084,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9063,10 +9109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131273414</v>
+        <v>131275200</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9074,21 +9120,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9101,10 +9147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546430</v>
+        <v>546174</v>
       </c>
       <c r="R68" t="n">
-        <v>6998969</v>
+        <v>6999354</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9156,17 +9202,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9184,10 +9235,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273420</v>
+        <v>131273384</v>
       </c>
       <c r="B69" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9195,37 +9246,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546204</v>
+        <v>546286</v>
       </c>
       <c r="R69" t="n">
-        <v>6999267</v>
+        <v>6999257</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9262,7 +9310,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9271,29 +9319,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9310,10 +9337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273386</v>
+        <v>131275211</v>
       </c>
       <c r="B70" t="n">
-        <v>80365</v>
+        <v>91848</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9321,28 +9348,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9352,10 +9375,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546294</v>
+        <v>546185</v>
       </c>
       <c r="R70" t="n">
-        <v>6999434</v>
+        <v>6999135</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9390,11 +9413,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9412,22 +9430,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9445,7 +9458,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273416</v>
+        <v>131273414</v>
       </c>
       <c r="B71" t="n">
         <v>79260</v>
@@ -9483,10 +9496,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546387</v>
+        <v>546430</v>
       </c>
       <c r="R71" t="n">
-        <v>6999068</v>
+        <v>6998969</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9519,11 +9532,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9571,10 +9579,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273371</v>
+        <v>131273420</v>
       </c>
       <c r="B72" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9582,31 +9590,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9614,7 +9617,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546089</v>
+        <v>546204</v>
       </c>
       <c r="R72" t="n">
         <v>6999267</v>
@@ -9654,7 +9657,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9663,6 +9666,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9701,10 +9705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131276481</v>
+        <v>131273386</v>
       </c>
       <c r="B73" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9712,29 +9716,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9744,10 +9747,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546070</v>
+        <v>546294</v>
       </c>
       <c r="R73" t="n">
-        <v>6999374</v>
+        <v>6999434</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9784,7 +9787,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9793,6 +9796,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9803,17 +9807,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9831,10 +9840,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273372</v>
+        <v>131273416</v>
       </c>
       <c r="B74" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9842,31 +9851,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9874,10 +9878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546089</v>
+        <v>546387</v>
       </c>
       <c r="R74" t="n">
-        <v>6999297</v>
+        <v>6999068</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9914,7 +9918,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9923,6 +9927,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9941,14 +9946,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -12283,37 +12283,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131273424</v>
+        <v>131275217</v>
       </c>
       <c r="B93" t="n">
-        <v>79260</v>
+        <v>83227</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12321,10 +12333,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546090</v>
+        <v>546307</v>
       </c>
       <c r="R93" t="n">
-        <v>6999323</v>
+        <v>6999069</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12361,7 +12373,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12379,19 +12391,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12409,10 +12436,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131276477</v>
+        <v>131273362</v>
       </c>
       <c r="B94" t="n">
-        <v>57898</v>
+        <v>91828</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12420,29 +12447,28 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -12452,10 +12478,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546062</v>
+        <v>546302</v>
       </c>
       <c r="R94" t="n">
-        <v>6999442</v>
+        <v>6999463</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12492,7 +12518,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12501,6 +12527,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12519,9 +12546,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12539,10 +12571,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275135</v>
+        <v>131273424</v>
       </c>
       <c r="B95" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12550,31 +12582,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12582,10 +12609,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546142</v>
+        <v>546090</v>
       </c>
       <c r="R95" t="n">
-        <v>6999047</v>
+        <v>6999323</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12622,7 +12649,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12631,6 +12658,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12669,7 +12697,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131275158</v>
+        <v>131276477</v>
       </c>
       <c r="B96" t="n">
         <v>57898</v>
@@ -12712,10 +12740,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546100</v>
+        <v>546062</v>
       </c>
       <c r="R96" t="n">
-        <v>6999268</v>
+        <v>6999442</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12799,7 +12827,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131273366</v>
+        <v>131275135</v>
       </c>
       <c r="B97" t="n">
         <v>57898</v>
@@ -12842,10 +12870,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546100</v>
+        <v>546142</v>
       </c>
       <c r="R97" t="n">
-        <v>6999258</v>
+        <v>6999047</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12882,7 +12910,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12909,14 +12937,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12934,37 +12957,42 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131275209</v>
+        <v>131275158</v>
       </c>
       <c r="B98" t="n">
-        <v>80325</v>
+        <v>57898</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -12972,10 +13000,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546171</v>
+        <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999219</v>
+        <v>6999268</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13010,13 +13038,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13027,22 +13059,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13060,47 +13087,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131275217</v>
+        <v>131273366</v>
       </c>
       <c r="B99" t="n">
-        <v>83227</v>
+        <v>57898</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -13110,10 +13130,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546307</v>
+        <v>546100</v>
       </c>
       <c r="R99" t="n">
-        <v>6999069</v>
+        <v>6999258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13150,7 +13170,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13159,7 +13179,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13168,34 +13187,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13213,41 +13222,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131273362</v>
+        <v>131275209</v>
       </c>
       <c r="B100" t="n">
-        <v>91828</v>
+        <v>80325</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13255,10 +13260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546302</v>
+        <v>546171</v>
       </c>
       <c r="R100" t="n">
-        <v>6999463</v>
+        <v>6999219</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13293,11 +13298,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -13315,22 +13315,22 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131273385</v>
+        <v>131275148</v>
       </c>
       <c r="B120" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15829,28 +15829,29 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -15860,10 +15861,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546261</v>
+        <v>546118</v>
       </c>
       <c r="R120" t="n">
-        <v>6999479</v>
+        <v>6999179</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15900,7 +15901,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15909,7 +15910,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -15920,22 +15920,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15953,10 +15948,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131275216</v>
+        <v>131275133</v>
       </c>
       <c r="B121" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15964,26 +15959,31 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -15991,10 +15991,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>546240</v>
+        <v>546213</v>
       </c>
       <c r="R121" t="n">
-        <v>6999411</v>
+        <v>6999200</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16040,7 +16040,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16079,10 +16078,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131275148</v>
+        <v>131273385</v>
       </c>
       <c r="B122" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16090,29 +16089,28 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -16122,10 +16120,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>546118</v>
+        <v>546261</v>
       </c>
       <c r="R122" t="n">
-        <v>6999179</v>
+        <v>6999479</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16162,7 +16160,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16171,6 +16169,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16181,17 +16180,22 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16209,10 +16213,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131275133</v>
+        <v>131275216</v>
       </c>
       <c r="B123" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16220,31 +16224,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -16252,10 +16251,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>546213</v>
+        <v>546240</v>
       </c>
       <c r="R123" t="n">
-        <v>6999200</v>
+        <v>6999411</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16292,7 +16291,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16301,6 +16300,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -17872,10 +17872,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>131275208</v>
+        <v>131273408</v>
       </c>
       <c r="B136" t="n">
-        <v>80325</v>
+        <v>80401</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17883,26 +17883,30 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -17910,10 +17914,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>546460</v>
+        <v>546110</v>
       </c>
       <c r="R136" t="n">
-        <v>6999073</v>
+        <v>6999309</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17948,6 +17952,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På en flerstammig gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -17965,12 +17974,12 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -17980,7 +17989,7 @@
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -17998,39 +18007,39 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>131273408</v>
+        <v>131273390</v>
       </c>
       <c r="B137" t="n">
-        <v>80401</v>
+        <v>80365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -18040,10 +18049,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>546110</v>
+        <v>546420</v>
       </c>
       <c r="R137" t="n">
-        <v>6999309</v>
+        <v>6999089</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -18080,7 +18089,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -18115,7 +18124,7 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -18133,7 +18142,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>131273390</v>
+        <v>131275203</v>
       </c>
       <c r="B138" t="n">
         <v>80365</v>
@@ -18163,11 +18172,7 @@
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -18175,10 +18180,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>546420</v>
+        <v>546227</v>
       </c>
       <c r="R138" t="n">
-        <v>6999089</v>
+        <v>6999420</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -18213,11 +18218,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en grovbarkad flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18268,10 +18268,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131275203</v>
+        <v>131275147</v>
       </c>
       <c r="B139" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18279,26 +18279,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -18306,10 +18311,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>546227</v>
+        <v>546137</v>
       </c>
       <c r="R139" t="n">
-        <v>6999420</v>
+        <v>6999148</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18344,13 +18349,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -18361,22 +18370,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18394,7 +18398,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131275147</v>
+        <v>131275136</v>
       </c>
       <c r="B140" t="n">
         <v>57898</v>
@@ -18437,10 +18441,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546137</v>
+        <v>546148</v>
       </c>
       <c r="R140" t="n">
-        <v>6999148</v>
+        <v>6999041</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18524,7 +18528,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131275136</v>
+        <v>131275138</v>
       </c>
       <c r="B141" t="n">
         <v>57898</v>
@@ -18567,10 +18571,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546148</v>
+        <v>546145</v>
       </c>
       <c r="R141" t="n">
-        <v>6999041</v>
+        <v>6999053</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18654,42 +18658,37 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275138</v>
+        <v>131275208</v>
       </c>
       <c r="B142" t="n">
-        <v>57898</v>
+        <v>80325</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -18697,10 +18696,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546145</v>
+        <v>546460</v>
       </c>
       <c r="R142" t="n">
-        <v>6999053</v>
+        <v>6999073</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18735,17 +18734,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -18756,17 +18751,22 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -19268,42 +19268,37 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131273367</v>
+        <v>131275210</v>
       </c>
       <c r="B147" t="n">
-        <v>57898</v>
+        <v>80325</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -19311,10 +19306,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546103</v>
+        <v>546168</v>
       </c>
       <c r="R147" t="n">
-        <v>6999266</v>
+        <v>6999217</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19349,17 +19344,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -19370,22 +19361,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19403,7 +19394,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131276480</v>
+        <v>131273367</v>
       </c>
       <c r="B148" t="n">
         <v>57898</v>
@@ -19446,10 +19437,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546066</v>
+        <v>546103</v>
       </c>
       <c r="R148" t="n">
-        <v>6999401</v>
+        <v>6999266</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19486,7 +19477,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -19513,9 +19504,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19533,7 +19529,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131276479</v>
+        <v>131276480</v>
       </c>
       <c r="B149" t="n">
         <v>57898</v>
@@ -19576,10 +19572,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546062</v>
+        <v>546066</v>
       </c>
       <c r="R149" t="n">
-        <v>6999415</v>
+        <v>6999401</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19663,37 +19659,42 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131275210</v>
+        <v>131276479</v>
       </c>
       <c r="B150" t="n">
-        <v>80325</v>
+        <v>57898</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -19701,10 +19702,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546168</v>
+        <v>546062</v>
       </c>
       <c r="R150" t="n">
-        <v>6999217</v>
+        <v>6999415</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19739,13 +19740,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -19756,22 +19761,17 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131273413</v>
+        <v>131275180</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546491</v>
+        <v>546406</v>
       </c>
       <c r="R2" t="n">
-        <v>6998962</v>
+        <v>6999201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131273422</v>
+        <v>131275187</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546111</v>
+        <v>546202</v>
       </c>
       <c r="R3" t="n">
-        <v>6999297</v>
+        <v>6999223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,17 +899,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275215</v>
+        <v>131273378</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,26 +938,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546164</v>
+        <v>546094</v>
       </c>
       <c r="R4" t="n">
-        <v>6999199</v>
+        <v>6999329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,9 +1037,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131273397</v>
+        <v>131275145</v>
       </c>
       <c r="B5" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,26 +1073,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546296</v>
+        <v>546148</v>
       </c>
       <c r="R5" t="n">
-        <v>6999259</v>
+        <v>6999078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1145,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1154,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,22 +1164,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1192,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275180</v>
+        <v>131275160</v>
       </c>
       <c r="B6" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,26 +1203,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546406</v>
+        <v>546104</v>
       </c>
       <c r="R6" t="n">
-        <v>6999201</v>
+        <v>6999263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1284,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,17 +1294,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1322,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131275187</v>
+        <v>131276476</v>
       </c>
       <c r="B7" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1333,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1365,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546202</v>
+        <v>546050</v>
       </c>
       <c r="R7" t="n">
-        <v>6999223</v>
+        <v>6999453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1405,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1414,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,17 +1424,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1452,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273378</v>
+        <v>131273413</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,31 +1463,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1474,10 +1490,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546094</v>
+        <v>546491</v>
       </c>
       <c r="R8" t="n">
-        <v>6999329</v>
+        <v>6998962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,17 +1528,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,14 +1553,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131275145</v>
+        <v>131273422</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,31 +1584,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1609,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546148</v>
+        <v>546111</v>
       </c>
       <c r="R9" t="n">
-        <v>6999078</v>
+        <v>6999297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,7 +1651,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,6 +1660,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1696,10 +1699,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275160</v>
+        <v>131275215</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,31 +1710,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1739,10 +1737,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546104</v>
+        <v>546164</v>
       </c>
       <c r="R10" t="n">
-        <v>6999263</v>
+        <v>6999199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,7 +1777,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,6 +1786,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1826,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131276476</v>
+        <v>131273397</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,31 +1836,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1869,10 +1863,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546050</v>
+        <v>546296</v>
       </c>
       <c r="R11" t="n">
-        <v>6999453</v>
+        <v>6999259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1909,7 +1903,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,6 +1912,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,17 +1923,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131275185</v>
+        <v>131273407</v>
       </c>
       <c r="B13" t="n">
         <v>80365</v>
@@ -2116,7 +2116,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546230</v>
+        <v>546227</v>
       </c>
       <c r="R13" t="n">
-        <v>6999202</v>
+        <v>6999437</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2184,12 +2188,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2199,7 +2203,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2217,7 +2221,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131273407</v>
+        <v>131276484</v>
       </c>
       <c r="B14" t="n">
         <v>80365</v>
@@ -2247,11 +2251,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546227</v>
+        <v>546500</v>
       </c>
       <c r="R14" t="n">
-        <v>6999437</v>
+        <v>6998983</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2295,11 +2295,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2352,7 +2347,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131276484</v>
+        <v>131275184</v>
       </c>
       <c r="B15" t="n">
         <v>80365</v>
@@ -2390,10 +2385,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546500</v>
+        <v>546300</v>
       </c>
       <c r="R15" t="n">
-        <v>6998983</v>
+        <v>6999066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2441,26 +2436,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2478,7 +2453,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131275184</v>
+        <v>131275192</v>
       </c>
       <c r="B16" t="n">
         <v>80365</v>
@@ -2516,10 +2491,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546300</v>
+        <v>546168</v>
       </c>
       <c r="R16" t="n">
-        <v>6999066</v>
+        <v>6999218</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,6 +2542,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2584,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131273421</v>
+        <v>131275185</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,21 +2590,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546167</v>
+        <v>546230</v>
       </c>
       <c r="R17" t="n">
-        <v>6999264</v>
+        <v>6999202</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2660,6 +2655,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2677,17 +2677,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2705,10 +2710,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131275192</v>
+        <v>131273421</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2716,21 +2721,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2743,10 +2748,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546168</v>
+        <v>546167</v>
       </c>
       <c r="R18" t="n">
-        <v>6999218</v>
+        <v>6999264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2798,22 +2803,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131275193</v>
+        <v>131273389</v>
       </c>
       <c r="B36" t="n">
         <v>80365</v>
@@ -5043,19 +5043,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546158</v>
+        <v>546366</v>
       </c>
       <c r="R36" t="n">
-        <v>6999223</v>
+        <v>6999149</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5092,7 +5089,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Rikligt på en sälg. Fertil!</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5101,34 +5098,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5145,7 +5116,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131273389</v>
+        <v>131276492</v>
       </c>
       <c r="B37" t="n">
         <v>80365</v>
@@ -5174,16 +5145,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546366</v>
+        <v>546097</v>
       </c>
       <c r="R37" t="n">
-        <v>6999149</v>
+        <v>6999346</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5218,19 +5192,40 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt på en sälg. Fertil!</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5247,7 +5242,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131276492</v>
+        <v>131275193</v>
       </c>
       <c r="B38" t="n">
         <v>80365</v>
@@ -5285,10 +5280,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546097</v>
+        <v>546158</v>
       </c>
       <c r="R38" t="n">
-        <v>6999346</v>
+        <v>6999223</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5323,6 +5318,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5340,12 +5340,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131276487</v>
+        <v>131273410</v>
       </c>
       <c r="B44" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546313</v>
+        <v>546342</v>
       </c>
       <c r="R44" t="n">
-        <v>6999060</v>
+        <v>6999195</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6097,22 +6097,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6130,41 +6125,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131273381</v>
+        <v>131273426</v>
       </c>
       <c r="B45" t="n">
-        <v>80394</v>
+        <v>79260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6172,10 +6163,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546353</v>
+        <v>546172</v>
       </c>
       <c r="R45" t="n">
-        <v>6999084</v>
+        <v>6999385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6212,7 +6203,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6232,22 +6223,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6265,7 +6251,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131275194</v>
+        <v>131273406</v>
       </c>
       <c r="B46" t="n">
         <v>80365</v>
@@ -6303,10 +6289,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546153</v>
+        <v>546223</v>
       </c>
       <c r="R46" t="n">
-        <v>6999210</v>
+        <v>6999436</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6343,7 +6329,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6363,22 +6349,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6396,7 +6382,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131273410</v>
+        <v>131275213</v>
       </c>
       <c r="B47" t="n">
         <v>79260</v>
@@ -6434,10 +6420,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546342</v>
+        <v>546481</v>
       </c>
       <c r="R47" t="n">
-        <v>6999195</v>
+        <v>6998980</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6517,10 +6503,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131273426</v>
+        <v>131273374</v>
       </c>
       <c r="B48" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6528,26 +6514,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6555,10 +6546,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546172</v>
+        <v>546094</v>
       </c>
       <c r="R48" t="n">
-        <v>6999385</v>
+        <v>6999322</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6595,7 +6586,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6604,7 +6595,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6623,9 +6613,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6643,10 +6638,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131273401</v>
+        <v>131275151</v>
       </c>
       <c r="B49" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6654,28 +6649,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6685,10 +6681,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546279</v>
+        <v>546124</v>
       </c>
       <c r="R49" t="n">
-        <v>6999244</v>
+        <v>6999206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6725,7 +6721,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6734,7 +6730,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6745,22 +6740,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6778,10 +6768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131273406</v>
+        <v>131275159</v>
       </c>
       <c r="B50" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6789,26 +6779,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6816,10 +6811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546223</v>
+        <v>546099</v>
       </c>
       <c r="R50" t="n">
-        <v>6999436</v>
+        <v>6999277</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6856,7 +6851,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6865,7 +6860,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6884,14 +6878,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6909,10 +6898,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131275213</v>
+        <v>131276478</v>
       </c>
       <c r="B51" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6920,26 +6909,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6947,10 +6941,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546481</v>
+        <v>546058</v>
       </c>
       <c r="R51" t="n">
-        <v>6998980</v>
+        <v>6999435</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6985,13 +6979,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7030,7 +7028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131273374</v>
+        <v>131275139</v>
       </c>
       <c r="B52" t="n">
         <v>57898</v>
@@ -7073,10 +7071,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546094</v>
+        <v>546151</v>
       </c>
       <c r="R52" t="n">
-        <v>6999322</v>
+        <v>6999044</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7113,7 +7111,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7140,14 +7138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7165,10 +7158,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131275151</v>
+        <v>131276487</v>
       </c>
       <c r="B53" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7176,31 +7169,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7208,10 +7196,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546124</v>
+        <v>546313</v>
       </c>
       <c r="R53" t="n">
-        <v>6999206</v>
+        <v>6999060</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7246,17 +7234,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7267,17 +7251,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7295,40 +7284,39 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131275159</v>
+        <v>131273381</v>
       </c>
       <c r="B54" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7338,10 +7326,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546099</v>
+        <v>546353</v>
       </c>
       <c r="R54" t="n">
-        <v>6999277</v>
+        <v>6999084</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7378,7 +7366,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7387,6 +7375,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7397,17 +7386,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7425,10 +7419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131276478</v>
+        <v>131275194</v>
       </c>
       <c r="B55" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7436,31 +7430,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7468,10 +7457,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546058</v>
+        <v>546153</v>
       </c>
       <c r="R55" t="n">
-        <v>6999435</v>
+        <v>6999210</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7508,7 +7497,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7517,6 +7506,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7527,17 +7517,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7555,10 +7550,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131275139</v>
+        <v>131273401</v>
       </c>
       <c r="B56" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7566,29 +7561,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7598,10 +7592,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546151</v>
+        <v>546279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999044</v>
+        <v>6999244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7638,7 +7632,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7647,6 +7641,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7657,17 +7652,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131275195</v>
+        <v>131273394</v>
       </c>
       <c r="B57" t="n">
         <v>80365</v>
@@ -7715,7 +7715,11 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7723,10 +7727,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546150</v>
+        <v>546346</v>
       </c>
       <c r="R57" t="n">
-        <v>6999197</v>
+        <v>6999078</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7761,6 +7765,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7778,12 +7787,12 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -7793,7 +7802,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7811,7 +7820,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131273394</v>
+        <v>131276491</v>
       </c>
       <c r="B58" t="n">
         <v>80365</v>
@@ -7841,11 +7850,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7853,10 +7858,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546346</v>
+        <v>546074</v>
       </c>
       <c r="R58" t="n">
-        <v>6999078</v>
+        <v>6999366</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7889,11 +7894,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7946,10 +7946,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131276488</v>
+        <v>131273412</v>
       </c>
       <c r="B59" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7957,21 +7957,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546062</v>
+        <v>546441</v>
       </c>
       <c r="R59" t="n">
-        <v>6999441</v>
+        <v>6999013</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8039,22 +8039,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8072,10 +8067,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276491</v>
+        <v>131275129</v>
       </c>
       <c r="B60" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8083,26 +8078,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546074</v>
+        <v>546338</v>
       </c>
       <c r="R60" t="n">
-        <v>6999366</v>
+        <v>6999380</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8148,13 +8148,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8165,22 +8169,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8198,10 +8197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131273412</v>
+        <v>131273373</v>
       </c>
       <c r="B61" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8209,26 +8208,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8236,10 +8240,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546441</v>
+        <v>546097</v>
       </c>
       <c r="R61" t="n">
-        <v>6999013</v>
+        <v>6999307</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8274,13 +8278,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8299,9 +8307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8319,7 +8332,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131275129</v>
+        <v>131276475</v>
       </c>
       <c r="B62" t="n">
         <v>57898</v>
@@ -8352,7 +8365,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8365,7 +8378,7 @@
         <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999380</v>
+        <v>6999168</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8402,7 +8415,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8449,10 +8462,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131273373</v>
+        <v>131275195</v>
       </c>
       <c r="B63" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8460,31 +8473,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8492,10 +8500,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546097</v>
+        <v>546150</v>
       </c>
       <c r="R63" t="n">
-        <v>6999307</v>
+        <v>6999197</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8530,17 +8538,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8551,22 +8555,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8584,10 +8588,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276475</v>
+        <v>131276488</v>
       </c>
       <c r="B64" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8595,31 +8599,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8627,10 +8626,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546338</v>
+        <v>546062</v>
       </c>
       <c r="R64" t="n">
-        <v>6999168</v>
+        <v>6999441</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8665,17 +8664,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8686,17 +8681,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131273371</v>
+        <v>131273384</v>
       </c>
       <c r="B65" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,42 +8725,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546089</v>
+        <v>546286</v>
       </c>
       <c r="R65" t="n">
-        <v>6999267</v>
+        <v>6999257</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8797,7 +8789,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8808,26 +8800,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8844,10 +8816,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131276481</v>
+        <v>131275211</v>
       </c>
       <c r="B66" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8855,29 +8827,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8887,10 +8854,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546070</v>
+        <v>546185</v>
       </c>
       <c r="R66" t="n">
-        <v>6999374</v>
+        <v>6999135</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8925,17 +8892,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8974,10 +8937,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273372</v>
+        <v>131273414</v>
       </c>
       <c r="B67" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8985,31 +8948,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9017,10 +8975,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546089</v>
+        <v>546430</v>
       </c>
       <c r="R67" t="n">
-        <v>6999297</v>
+        <v>6998969</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9055,17 +9013,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9084,14 +9038,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9109,10 +9058,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131275200</v>
+        <v>131273420</v>
       </c>
       <c r="B68" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9120,21 +9069,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9147,10 +9096,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546174</v>
+        <v>546204</v>
       </c>
       <c r="R68" t="n">
-        <v>6999354</v>
+        <v>6999267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9185,6 +9134,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9202,22 +9156,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9235,7 +9184,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273384</v>
+        <v>131273386</v>
       </c>
       <c r="B69" t="n">
         <v>80365</v>
@@ -9264,16 +9213,23 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546286</v>
+        <v>546294</v>
       </c>
       <c r="R69" t="n">
-        <v>6999257</v>
+        <v>6999434</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9310,7 +9266,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9319,8 +9275,34 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9337,10 +9319,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131275211</v>
+        <v>131273416</v>
       </c>
       <c r="B70" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9348,26 +9330,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9375,10 +9357,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546185</v>
+        <v>546387</v>
       </c>
       <c r="R70" t="n">
-        <v>6999135</v>
+        <v>6999068</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9411,6 +9393,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9458,10 +9445,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273414</v>
+        <v>131273371</v>
       </c>
       <c r="B71" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9469,26 +9456,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9496,10 +9488,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546430</v>
+        <v>546089</v>
       </c>
       <c r="R71" t="n">
-        <v>6998969</v>
+        <v>6999267</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9534,13 +9526,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9579,10 +9575,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273420</v>
+        <v>131276481</v>
       </c>
       <c r="B72" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9590,26 +9586,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9617,10 +9618,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546204</v>
+        <v>546070</v>
       </c>
       <c r="R72" t="n">
-        <v>6999267</v>
+        <v>6999374</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9657,7 +9658,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9666,7 +9667,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273386</v>
+        <v>131273372</v>
       </c>
       <c r="B73" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9716,28 +9716,29 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9747,10 +9748,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546294</v>
+        <v>546089</v>
       </c>
       <c r="R73" t="n">
-        <v>6999434</v>
+        <v>6999297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9787,7 +9788,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9796,7 +9797,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9807,22 +9807,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273416</v>
+        <v>131275200</v>
       </c>
       <c r="B74" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9851,21 +9851,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546387</v>
+        <v>546174</v>
       </c>
       <c r="R74" t="n">
-        <v>6999068</v>
+        <v>6999354</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9916,11 +9916,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9938,17 +9933,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131276486</v>
+        <v>131276482</v>
       </c>
       <c r="B75" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9977,26 +9977,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10004,10 +10009,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>546356</v>
+        <v>546075</v>
       </c>
       <c r="R75" t="n">
-        <v>6999034</v>
+        <v>6999369</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10042,13 +10047,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10059,22 +10068,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10092,10 +10096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131275181</v>
+        <v>131275132</v>
       </c>
       <c r="B76" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10103,37 +10107,54 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>546435</v>
+        <v>546295</v>
       </c>
       <c r="R76" t="n">
-        <v>6999096</v>
+        <v>6999077</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10170,7 +10191,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10179,7 +10200,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10188,24 +10208,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10223,10 +10228,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131273393</v>
+        <v>131275144</v>
       </c>
       <c r="B77" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10234,28 +10239,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10265,10 +10271,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>546394</v>
+        <v>546124</v>
       </c>
       <c r="R77" t="n">
-        <v>6999043</v>
+        <v>6999127</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10303,13 +10309,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10320,22 +10330,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10353,7 +10358,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131275202</v>
+        <v>131276486</v>
       </c>
       <c r="B78" t="n">
         <v>80365</v>
@@ -10391,10 +10396,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>546230</v>
+        <v>546356</v>
       </c>
       <c r="R78" t="n">
-        <v>6999398</v>
+        <v>6999034</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10479,7 +10484,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131273402</v>
+        <v>131275181</v>
       </c>
       <c r="B79" t="n">
         <v>80365</v>
@@ -10517,10 +10522,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>546159</v>
+        <v>546435</v>
       </c>
       <c r="R79" t="n">
-        <v>6999249</v>
+        <v>6999096</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10557,7 +10562,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10577,22 +10582,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10610,7 +10615,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131273392</v>
+        <v>131273393</v>
       </c>
       <c r="B80" t="n">
         <v>80365</v>
@@ -10640,7 +10645,11 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10648,10 +10657,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>546398</v>
+        <v>546394</v>
       </c>
       <c r="R80" t="n">
-        <v>6998976</v>
+        <v>6999043</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10736,10 +10745,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131276482</v>
+        <v>131275202</v>
       </c>
       <c r="B81" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10747,31 +10756,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10779,10 +10783,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>546075</v>
+        <v>546230</v>
       </c>
       <c r="R81" t="n">
-        <v>6999369</v>
+        <v>6999398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10817,17 +10821,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10838,17 +10838,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10866,10 +10871,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131275132</v>
+        <v>131273402</v>
       </c>
       <c r="B82" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10877,54 +10882,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>546295</v>
+        <v>546159</v>
       </c>
       <c r="R82" t="n">
-        <v>6999077</v>
+        <v>6999249</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10961,7 +10949,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10970,6 +10958,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10978,9 +10967,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Äldre granskog med höga naturvärden.</t>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10998,10 +11002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131275144</v>
+        <v>131273392</v>
       </c>
       <c r="B83" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11009,31 +11013,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11041,10 +11040,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>546124</v>
+        <v>546398</v>
       </c>
       <c r="R83" t="n">
-        <v>6999127</v>
+        <v>6998976</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11079,17 +11078,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11100,17 +11095,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11128,32 +11128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131275170</v>
+        <v>131275204</v>
       </c>
       <c r="B84" t="n">
-        <v>83231</v>
+        <v>80365</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>546401</v>
+        <v>546244</v>
       </c>
       <c r="R84" t="n">
-        <v>6999141</v>
+        <v>6999418</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11254,7 +11254,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131275204</v>
+        <v>131273388</v>
       </c>
       <c r="B85" t="n">
         <v>80365</v>
@@ -11284,7 +11284,11 @@
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11292,10 +11296,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546244</v>
+        <v>546370</v>
       </c>
       <c r="R85" t="n">
-        <v>6999418</v>
+        <v>6999140</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11330,6 +11334,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11362,7 +11371,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11380,7 +11389,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131276483</v>
+        <v>131275188</v>
       </c>
       <c r="B86" t="n">
         <v>80365</v>
@@ -11418,10 +11427,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546404</v>
+        <v>546149</v>
       </c>
       <c r="R86" t="n">
-        <v>6999205</v>
+        <v>6999276</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11456,6 +11465,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -11473,22 +11487,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11506,32 +11515,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131275205</v>
+        <v>131275170</v>
       </c>
       <c r="B87" t="n">
-        <v>80365</v>
+        <v>83231</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11544,10 +11553,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546149</v>
+        <v>546401</v>
       </c>
       <c r="R87" t="n">
-        <v>6999093</v>
+        <v>6999141</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11632,10 +11641,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131273388</v>
+        <v>131275161</v>
       </c>
       <c r="B88" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11643,28 +11652,29 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -11674,10 +11684,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546370</v>
+        <v>546100</v>
       </c>
       <c r="R88" t="n">
-        <v>6999140</v>
+        <v>6999276</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11714,7 +11724,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11723,7 +11733,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11734,22 +11743,17 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11767,10 +11771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131275188</v>
+        <v>131275165</v>
       </c>
       <c r="B89" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11778,26 +11782,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11805,10 +11814,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546149</v>
+        <v>546098</v>
       </c>
       <c r="R89" t="n">
-        <v>6999276</v>
+        <v>6999296</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11845,7 +11854,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11854,7 +11863,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11865,17 +11873,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11893,7 +11901,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275161</v>
+        <v>131275164</v>
       </c>
       <c r="B90" t="n">
         <v>57898</v>
@@ -11936,10 +11944,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546100</v>
+        <v>546097</v>
       </c>
       <c r="R90" t="n">
-        <v>6999276</v>
+        <v>6999287</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11976,7 +11984,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12023,10 +12031,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131275165</v>
+        <v>131276483</v>
       </c>
       <c r="B91" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12034,31 +12042,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12066,10 +12069,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546098</v>
+        <v>546404</v>
       </c>
       <c r="R91" t="n">
-        <v>6999296</v>
+        <v>6999205</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12104,17 +12107,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12125,17 +12124,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275164</v>
+        <v>131275205</v>
       </c>
       <c r="B92" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12164,31 +12168,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12196,10 +12195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546097</v>
+        <v>546149</v>
       </c>
       <c r="R92" t="n">
-        <v>6999287</v>
+        <v>6999093</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12234,17 +12233,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12255,17 +12250,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12283,47 +12283,39 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131275217</v>
+        <v>131273362</v>
       </c>
       <c r="B93" t="n">
-        <v>83227</v>
+        <v>91828</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>307</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -12333,10 +12325,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546307</v>
+        <v>546302</v>
       </c>
       <c r="R93" t="n">
-        <v>6999069</v>
+        <v>6999463</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12373,7 +12365,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12391,34 +12383,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12436,41 +12418,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131273362</v>
+        <v>131275209</v>
       </c>
       <c r="B94" t="n">
-        <v>91828</v>
+        <v>80325</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12478,10 +12456,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546302</v>
+        <v>546171</v>
       </c>
       <c r="R94" t="n">
-        <v>6999463</v>
+        <v>6999219</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12516,11 +12494,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12538,22 +12511,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12571,37 +12544,49 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131273424</v>
+        <v>131275217</v>
       </c>
       <c r="B95" t="n">
-        <v>79260</v>
+        <v>83227</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12609,10 +12594,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546090</v>
+        <v>546307</v>
       </c>
       <c r="R95" t="n">
-        <v>6999323</v>
+        <v>6999069</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12649,7 +12634,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12667,19 +12652,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12697,10 +12697,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131276477</v>
+        <v>131273424</v>
       </c>
       <c r="B96" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12708,31 +12708,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -12740,10 +12735,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546062</v>
+        <v>546090</v>
       </c>
       <c r="R96" t="n">
-        <v>6999442</v>
+        <v>6999323</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12780,7 +12775,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12789,6 +12784,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12827,7 +12823,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131275135</v>
+        <v>131276477</v>
       </c>
       <c r="B97" t="n">
         <v>57898</v>
@@ -12870,10 +12866,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546142</v>
+        <v>546062</v>
       </c>
       <c r="R97" t="n">
-        <v>6999047</v>
+        <v>6999442</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12957,7 +12953,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131275158</v>
+        <v>131275135</v>
       </c>
       <c r="B98" t="n">
         <v>57898</v>
@@ -13000,10 +12996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546100</v>
+        <v>546142</v>
       </c>
       <c r="R98" t="n">
-        <v>6999268</v>
+        <v>6999047</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13087,7 +13083,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131273366</v>
+        <v>131275158</v>
       </c>
       <c r="B99" t="n">
         <v>57898</v>
@@ -13133,7 +13129,7 @@
         <v>546100</v>
       </c>
       <c r="R99" t="n">
-        <v>6999258</v>
+        <v>6999268</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13170,7 +13166,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13197,14 +13193,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13222,37 +13213,42 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131275209</v>
+        <v>131273366</v>
       </c>
       <c r="B100" t="n">
-        <v>80325</v>
+        <v>57898</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13260,10 +13256,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546171</v>
+        <v>546100</v>
       </c>
       <c r="R100" t="n">
-        <v>6999219</v>
+        <v>6999258</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13298,13 +13294,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13315,22 +13315,22 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131273395</v>
+        <v>131275137</v>
       </c>
       <c r="B103" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13626,26 +13626,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13653,10 +13658,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546313</v>
+        <v>546139</v>
       </c>
       <c r="R103" t="n">
-        <v>6999066</v>
+        <v>6999047</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13693,7 +13698,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13702,7 +13707,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13721,14 +13725,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13746,7 +13745,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131275137</v>
+        <v>131273380</v>
       </c>
       <c r="B104" t="n">
         <v>57898</v>
@@ -13789,10 +13788,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546139</v>
+        <v>546091</v>
       </c>
       <c r="R104" t="n">
-        <v>6999047</v>
+        <v>6999334</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13829,7 +13828,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13856,9 +13855,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13876,7 +13880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131273380</v>
+        <v>131273377</v>
       </c>
       <c r="B105" t="n">
         <v>57898</v>
@@ -13919,10 +13923,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546091</v>
+        <v>546077</v>
       </c>
       <c r="R105" t="n">
-        <v>6999334</v>
+        <v>6999352</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13959,7 +13963,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14011,10 +14015,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131273377</v>
+        <v>131275207</v>
       </c>
       <c r="B106" t="n">
-        <v>57898</v>
+        <v>78272</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14022,31 +14026,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14054,10 +14053,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546077</v>
+        <v>546365</v>
       </c>
       <c r="R106" t="n">
-        <v>6999352</v>
+        <v>6998993</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14092,17 +14091,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -14121,14 +14116,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14146,10 +14136,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131275207</v>
+        <v>131273395</v>
       </c>
       <c r="B107" t="n">
-        <v>78272</v>
+        <v>80365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14157,21 +14147,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14184,10 +14174,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546365</v>
+        <v>546313</v>
       </c>
       <c r="R107" t="n">
-        <v>6998993</v>
+        <v>6999066</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14222,6 +14212,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -14247,9 +14242,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14267,32 +14267,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131275172</v>
+        <v>131275190</v>
       </c>
       <c r="B108" t="n">
-        <v>80269</v>
+        <v>80365</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14305,10 +14305,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>546223</v>
+        <v>546145</v>
       </c>
       <c r="R108" t="n">
-        <v>6999048</v>
+        <v>6999134</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14343,6 +14343,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -14368,9 +14373,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14388,32 +14398,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131275190</v>
+        <v>131275172</v>
       </c>
       <c r="B109" t="n">
-        <v>80365</v>
+        <v>80269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14426,10 +14436,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>546145</v>
+        <v>546223</v>
       </c>
       <c r="R109" t="n">
-        <v>6999134</v>
+        <v>6999048</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14464,11 +14474,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -14494,14 +14499,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14919,10 +14919,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131275167</v>
+        <v>131273418</v>
       </c>
       <c r="B113" t="n">
-        <v>80231</v>
+        <v>79260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14930,21 +14930,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -14957,10 +14957,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546468</v>
+        <v>546329</v>
       </c>
       <c r="R113" t="n">
-        <v>6999037</v>
+        <v>6999224</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14995,6 +14995,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -15012,17 +15017,17 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15040,10 +15045,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131273363</v>
+        <v>131275174</v>
       </c>
       <c r="B114" t="n">
-        <v>92550</v>
+        <v>75238</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15051,30 +15056,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>6428</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15082,10 +15083,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546304</v>
+        <v>546222</v>
       </c>
       <c r="R114" t="n">
-        <v>6999379</v>
+        <v>6999408</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15122,7 +15123,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15142,22 +15143,22 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15175,10 +15176,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131273418</v>
+        <v>131275212</v>
       </c>
       <c r="B115" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15186,26 +15187,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15213,10 +15214,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546329</v>
+        <v>546213</v>
       </c>
       <c r="R115" t="n">
-        <v>6999224</v>
+        <v>6999022</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15249,11 +15250,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15301,10 +15297,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273387</v>
+        <v>131275166</v>
       </c>
       <c r="B116" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15312,28 +15308,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -15343,10 +15340,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546286</v>
+        <v>546208</v>
       </c>
       <c r="R116" t="n">
-        <v>6999419</v>
+        <v>6999393</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15383,7 +15380,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15392,7 +15389,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15403,22 +15399,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15436,10 +15427,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275174</v>
+        <v>131273363</v>
       </c>
       <c r="B117" t="n">
-        <v>75238</v>
+        <v>92550</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15447,26 +15438,30 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6428</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -15474,10 +15469,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546222</v>
+        <v>546304</v>
       </c>
       <c r="R117" t="n">
-        <v>6999408</v>
+        <v>6999379</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15514,7 +15509,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15534,22 +15529,22 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15567,10 +15562,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131275212</v>
+        <v>131273387</v>
       </c>
       <c r="B118" t="n">
-        <v>91848</v>
+        <v>80365</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15578,24 +15573,28 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -15605,10 +15604,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546213</v>
+        <v>546286</v>
       </c>
       <c r="R118" t="n">
-        <v>6999022</v>
+        <v>6999419</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15643,6 +15642,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -15660,17 +15664,22 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15688,10 +15697,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131275166</v>
+        <v>131275167</v>
       </c>
       <c r="B119" t="n">
-        <v>57898</v>
+        <v>80231</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15699,31 +15708,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15731,10 +15735,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546208</v>
+        <v>546468</v>
       </c>
       <c r="R119" t="n">
-        <v>6999393</v>
+        <v>6999037</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15769,17 +15773,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -15790,17 +15790,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275148</v>
+        <v>131273385</v>
       </c>
       <c r="B120" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15829,29 +15829,28 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -15861,10 +15860,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546118</v>
+        <v>546261</v>
       </c>
       <c r="R120" t="n">
-        <v>6999179</v>
+        <v>6999479</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15901,7 +15900,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15910,6 +15909,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -15920,17 +15920,22 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15948,10 +15953,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131275133</v>
+        <v>131275216</v>
       </c>
       <c r="B121" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15959,31 +15964,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -15991,10 +15991,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>546213</v>
+        <v>546240</v>
       </c>
       <c r="R121" t="n">
-        <v>6999200</v>
+        <v>6999411</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16040,6 +16040,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16078,10 +16079,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131273385</v>
+        <v>131275148</v>
       </c>
       <c r="B122" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16089,28 +16090,29 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -16120,10 +16122,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>546261</v>
+        <v>546118</v>
       </c>
       <c r="R122" t="n">
-        <v>6999479</v>
+        <v>6999179</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16160,7 +16162,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16169,7 +16171,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16180,22 +16181,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16213,10 +16209,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131275216</v>
+        <v>131275133</v>
       </c>
       <c r="B123" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16224,26 +16220,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -16251,10 +16252,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>546240</v>
+        <v>546213</v>
       </c>
       <c r="R123" t="n">
-        <v>6999411</v>
+        <v>6999200</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16291,7 +16292,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16300,7 +16301,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -16470,10 +16470,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131273364</v>
+        <v>131275199</v>
       </c>
       <c r="B125" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16481,31 +16481,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -16513,10 +16508,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>546403</v>
+        <v>546147</v>
       </c>
       <c r="R125" t="n">
-        <v>6998994</v>
+        <v>6999326</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16551,17 +16546,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -16582,12 +16573,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -16605,10 +16596,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131275134</v>
+        <v>131275197</v>
       </c>
       <c r="B126" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16616,31 +16607,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -16648,10 +16634,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546141</v>
+        <v>546130</v>
       </c>
       <c r="R126" t="n">
-        <v>6999039</v>
+        <v>6999313</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16686,17 +16672,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -16707,17 +16689,22 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16735,32 +16722,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275199</v>
+        <v>131275171</v>
       </c>
       <c r="B127" t="n">
-        <v>80365</v>
+        <v>80269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -16773,10 +16760,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546147</v>
+        <v>546230</v>
       </c>
       <c r="R127" t="n">
-        <v>6999326</v>
+        <v>6999202</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16828,22 +16815,17 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -16861,7 +16843,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>131275171</v>
+        <v>131275173</v>
       </c>
       <c r="B128" t="n">
         <v>80269</v>
@@ -16899,10 +16881,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>546230</v>
+        <v>546165</v>
       </c>
       <c r="R128" t="n">
-        <v>6999202</v>
+        <v>6999228</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -16982,10 +16964,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131275197</v>
+        <v>131273364</v>
       </c>
       <c r="B129" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16993,26 +16975,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -17020,10 +17007,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>546130</v>
+        <v>546403</v>
       </c>
       <c r="R129" t="n">
-        <v>6999313</v>
+        <v>6998994</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -17058,13 +17045,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -17075,22 +17066,22 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -17108,37 +17099,42 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131275173</v>
+        <v>131275134</v>
       </c>
       <c r="B130" t="n">
-        <v>80269</v>
+        <v>57898</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -17146,10 +17142,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>546165</v>
+        <v>546141</v>
       </c>
       <c r="R130" t="n">
-        <v>6999228</v>
+        <v>6999039</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -17184,13 +17180,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -17201,17 +17201,17 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -18915,10 +18915,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131276485</v>
+        <v>131275214</v>
       </c>
       <c r="B144" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18926,21 +18926,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -18953,10 +18953,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>546409</v>
+        <v>546193</v>
       </c>
       <c r="R144" t="n">
-        <v>6999005</v>
+        <v>6999241</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -19008,22 +19008,17 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -19041,32 +19036,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131275183</v>
+        <v>131275210</v>
       </c>
       <c r="B145" t="n">
-        <v>80365</v>
+        <v>80325</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -19079,10 +19074,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>546345</v>
+        <v>546168</v>
       </c>
       <c r="R145" t="n">
-        <v>6999035</v>
+        <v>6999217</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -19130,6 +19125,26 @@
       <c r="AH145" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -19147,10 +19162,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131275214</v>
+        <v>131276485</v>
       </c>
       <c r="B146" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19158,21 +19173,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -19185,10 +19200,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>546193</v>
+        <v>546409</v>
       </c>
       <c r="R146" t="n">
-        <v>6999241</v>
+        <v>6999005</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19240,17 +19255,22 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -19268,32 +19288,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275210</v>
+        <v>131275183</v>
       </c>
       <c r="B147" t="n">
-        <v>80325</v>
+        <v>80365</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19306,10 +19326,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546168</v>
+        <v>546345</v>
       </c>
       <c r="R147" t="n">
-        <v>6999217</v>
+        <v>6999035</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19357,26 +19377,6 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19789,7 +19789,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>131275189</v>
+        <v>131275196</v>
       </c>
       <c r="B151" t="n">
         <v>80365</v>
@@ -19827,10 +19827,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>546224</v>
+        <v>546124</v>
       </c>
       <c r="R151" t="n">
-        <v>6999013</v>
+        <v>6999220</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -19865,11 +19865,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -19887,12 +19882,12 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -19902,7 +19897,7 @@
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -19920,10 +19915,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131273405</v>
+        <v>131275177</v>
       </c>
       <c r="B152" t="n">
-        <v>80365</v>
+        <v>83235</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19931,21 +19926,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -19958,10 +19953,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546169</v>
+        <v>546303</v>
       </c>
       <c r="R152" t="n">
-        <v>6999410</v>
+        <v>6999065</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19998,7 +19993,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Enstaka bålar på asp.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20016,6 +20011,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ152" t="inlineStr">
         <is>
           <t>asp</t>
@@ -20028,12 +20028,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20051,7 +20051,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275196</v>
+        <v>131275189</v>
       </c>
       <c r="B153" t="n">
         <v>80365</v>
@@ -20089,10 +20089,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546124</v>
+        <v>546224</v>
       </c>
       <c r="R153" t="n">
-        <v>6999220</v>
+        <v>6999013</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20127,6 +20127,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -20144,12 +20149,12 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -20159,7 +20164,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -20177,10 +20182,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131275177</v>
+        <v>131273405</v>
       </c>
       <c r="B154" t="n">
-        <v>83235</v>
+        <v>80365</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20188,21 +20193,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -20215,10 +20220,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>546303</v>
+        <v>546169</v>
       </c>
       <c r="R154" t="n">
-        <v>6999065</v>
+        <v>6999410</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -20255,7 +20260,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20273,11 +20278,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ154" t="inlineStr">
         <is>
           <t>asp</t>
@@ -20290,12 +20290,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -20443,10 +20443,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>131275168</v>
+        <v>131273417</v>
       </c>
       <c r="B156" t="n">
-        <v>80231</v>
+        <v>79260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20454,21 +20454,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -20481,10 +20481,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>546465</v>
+        <v>546334</v>
       </c>
       <c r="R156" t="n">
-        <v>6999031</v>
+        <v>6999084</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20519,6 +20519,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -20536,17 +20541,22 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -20564,10 +20574,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131273403</v>
+        <v>131275141</v>
       </c>
       <c r="B157" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20575,26 +20585,31 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -20602,10 +20617,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>546109</v>
+        <v>546148</v>
       </c>
       <c r="R157" t="n">
-        <v>6999309</v>
+        <v>6999053</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -20642,7 +20657,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -20651,7 +20666,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -20670,14 +20684,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -20695,10 +20704,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131273400</v>
+        <v>131275162</v>
       </c>
       <c r="B158" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20706,26 +20715,31 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -20733,10 +20747,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>546297</v>
+        <v>546103</v>
       </c>
       <c r="R158" t="n">
-        <v>6999244</v>
+        <v>6999294</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -20773,7 +20787,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20782,7 +20796,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -20793,22 +20806,17 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -20826,10 +20834,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131273417</v>
+        <v>131275154</v>
       </c>
       <c r="B159" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20837,26 +20845,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -20864,10 +20877,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>546334</v>
+        <v>546118</v>
       </c>
       <c r="R159" t="n">
-        <v>6999084</v>
+        <v>6999237</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20904,7 +20917,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20913,7 +20926,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -20932,14 +20944,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -20957,7 +20964,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131275141</v>
+        <v>131275157</v>
       </c>
       <c r="B160" t="n">
         <v>57898</v>
@@ -21000,10 +21007,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>546148</v>
+        <v>546111</v>
       </c>
       <c r="R160" t="n">
-        <v>6999053</v>
+        <v>6999255</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -21087,10 +21094,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131275162</v>
+        <v>131273403</v>
       </c>
       <c r="B161" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21098,31 +21105,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -21130,10 +21132,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>546103</v>
+        <v>546109</v>
       </c>
       <c r="R161" t="n">
-        <v>6999294</v>
+        <v>6999309</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -21170,7 +21172,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Lunglav på en liten gran.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21179,6 +21181,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -21197,9 +21200,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -21217,10 +21225,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131275154</v>
+        <v>131273400</v>
       </c>
       <c r="B162" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21228,31 +21236,26 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -21260,10 +21263,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>546118</v>
+        <v>546297</v>
       </c>
       <c r="R162" t="n">
-        <v>6999237</v>
+        <v>6999244</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -21300,7 +21303,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21309,6 +21312,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -21319,17 +21323,22 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
@@ -21347,10 +21356,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131275157</v>
+        <v>131275168</v>
       </c>
       <c r="B163" t="n">
-        <v>57898</v>
+        <v>80231</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21358,31 +21367,26 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -21390,10 +21394,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>546111</v>
+        <v>546465</v>
       </c>
       <c r="R163" t="n">
-        <v>6999255</v>
+        <v>6999031</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -21428,17 +21432,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -21449,17 +21449,17 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131275180</v>
+        <v>131273413</v>
       </c>
       <c r="B2" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546406</v>
+        <v>546491</v>
       </c>
       <c r="R2" t="n">
-        <v>6999201</v>
+        <v>6998962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,17 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131275187</v>
+        <v>131273422</v>
       </c>
       <c r="B3" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546202</v>
+        <v>546111</v>
       </c>
       <c r="R3" t="n">
-        <v>6999223</v>
+        <v>6999297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>I god mängd på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,17 +894,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131273378</v>
+        <v>131275215</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,31 +933,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -970,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546094</v>
+        <v>546164</v>
       </c>
       <c r="R4" t="n">
-        <v>6999329</v>
+        <v>6999199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,14 +1028,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131275145</v>
+        <v>131273397</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,31 +1059,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1105,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546148</v>
+        <v>546296</v>
       </c>
       <c r="R5" t="n">
-        <v>6999078</v>
+        <v>6999259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,6 +1135,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1164,17 +1146,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275160</v>
+        <v>131275180</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,31 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1235,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546104</v>
+        <v>546406</v>
       </c>
       <c r="R6" t="n">
-        <v>6999263</v>
+        <v>6999201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1266,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1294,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1322,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131276476</v>
+        <v>131275187</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1365,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546050</v>
+        <v>546202</v>
       </c>
       <c r="R7" t="n">
-        <v>6999453</v>
+        <v>6999223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1424,17 +1403,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1452,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273413</v>
+        <v>131273378</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,26 +1442,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1490,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546491</v>
+        <v>546094</v>
       </c>
       <c r="R8" t="n">
-        <v>6998962</v>
+        <v>6999329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,13 +1512,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1553,9 +1541,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1573,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131273422</v>
+        <v>131275145</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,26 +1577,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1611,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546111</v>
+        <v>546148</v>
       </c>
       <c r="R9" t="n">
-        <v>6999297</v>
+        <v>6999078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,7 +1649,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I god mängd på flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,7 +1658,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1699,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275215</v>
+        <v>131275160</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,26 +1707,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1737,10 +1739,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546164</v>
+        <v>546104</v>
       </c>
       <c r="R10" t="n">
-        <v>6999199</v>
+        <v>6999263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,7 +1779,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,7 +1788,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131273397</v>
+        <v>131276476</v>
       </c>
       <c r="B11" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,26 +1837,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1863,10 +1869,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546296</v>
+        <v>546050</v>
       </c>
       <c r="R11" t="n">
-        <v>6999259</v>
+        <v>6999453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1903,7 +1909,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,7 +1918,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1923,22 +1928,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275191</v>
+        <v>131275206</v>
       </c>
       <c r="B30" t="n">
-        <v>80365</v>
+        <v>78272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546174</v>
+        <v>546408</v>
       </c>
       <c r="R30" t="n">
-        <v>6999215</v>
+        <v>6999129</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4349,11 +4349,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4371,12 +4366,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4386,7 +4381,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4404,7 +4399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275201</v>
+        <v>131275191</v>
       </c>
       <c r="B31" t="n">
         <v>80365</v>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546222</v>
+        <v>546174</v>
       </c>
       <c r="R31" t="n">
-        <v>6999418</v>
+        <v>6999215</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4480,6 +4475,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275178</v>
+        <v>131275201</v>
       </c>
       <c r="B32" t="n">
         <v>80365</v>
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546403</v>
+        <v>546222</v>
       </c>
       <c r="R32" t="n">
-        <v>6999213</v>
+        <v>6999418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4619,6 +4619,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4636,10 +4656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275206</v>
+        <v>131275178</v>
       </c>
       <c r="B33" t="n">
-        <v>78272</v>
+        <v>80365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4647,21 +4667,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4674,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546408</v>
+        <v>546403</v>
       </c>
       <c r="R33" t="n">
-        <v>6999129</v>
+        <v>6999213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4725,26 +4745,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131273374</v>
+        <v>131276487</v>
       </c>
       <c r="B48" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6514,31 +6514,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6546,10 +6541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546094</v>
+        <v>546313</v>
       </c>
       <c r="R48" t="n">
-        <v>6999322</v>
+        <v>6999060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6584,17 +6579,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6605,22 +6596,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6638,40 +6629,39 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131275151</v>
+        <v>131273381</v>
       </c>
       <c r="B49" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6681,10 +6671,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546124</v>
+        <v>546353</v>
       </c>
       <c r="R49" t="n">
-        <v>6999206</v>
+        <v>6999084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6721,7 +6711,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6730,6 +6720,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6740,17 +6731,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6768,10 +6764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131275159</v>
+        <v>131275194</v>
       </c>
       <c r="B50" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6779,31 +6775,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6811,10 +6802,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546099</v>
+        <v>546153</v>
       </c>
       <c r="R50" t="n">
-        <v>6999277</v>
+        <v>6999210</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6851,7 +6842,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6860,6 +6851,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6870,17 +6862,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6898,10 +6895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131276478</v>
+        <v>131273401</v>
       </c>
       <c r="B51" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6909,29 +6906,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6941,10 +6937,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546058</v>
+        <v>546279</v>
       </c>
       <c r="R51" t="n">
-        <v>6999435</v>
+        <v>6999244</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6981,7 +6977,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6990,6 +6986,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7000,17 +6997,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7028,7 +7030,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131275139</v>
+        <v>131273374</v>
       </c>
       <c r="B52" t="n">
         <v>57898</v>
@@ -7071,10 +7073,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546151</v>
+        <v>546094</v>
       </c>
       <c r="R52" t="n">
-        <v>6999044</v>
+        <v>6999322</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7111,7 +7113,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7138,9 +7140,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7158,10 +7165,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131276487</v>
+        <v>131275151</v>
       </c>
       <c r="B53" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7169,26 +7176,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7196,10 +7208,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546313</v>
+        <v>546124</v>
       </c>
       <c r="R53" t="n">
-        <v>6999060</v>
+        <v>6999206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7234,13 +7246,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7251,22 +7267,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7284,39 +7295,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131273381</v>
+        <v>131275159</v>
       </c>
       <c r="B54" t="n">
-        <v>80394</v>
+        <v>57898</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7326,10 +7338,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546353</v>
+        <v>546099</v>
       </c>
       <c r="R54" t="n">
-        <v>6999084</v>
+        <v>6999277</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7366,7 +7378,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7375,7 +7387,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7386,22 +7397,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7419,10 +7425,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131275194</v>
+        <v>131276478</v>
       </c>
       <c r="B55" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7430,26 +7436,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7457,10 +7468,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546153</v>
+        <v>546058</v>
       </c>
       <c r="R55" t="n">
-        <v>6999210</v>
+        <v>6999435</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7497,7 +7508,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7506,7 +7517,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7517,22 +7527,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7550,10 +7555,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131273401</v>
+        <v>131275139</v>
       </c>
       <c r="B56" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7561,28 +7566,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7592,10 +7598,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546279</v>
+        <v>546151</v>
       </c>
       <c r="R56" t="n">
-        <v>6999244</v>
+        <v>6999044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7632,7 +7638,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7641,7 +7647,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7652,22 +7657,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131273394</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
         <v>80365</v>
@@ -7715,11 +7715,7 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7727,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546346</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999078</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7765,11 +7761,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7787,12 +7778,12 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -7802,7 +7793,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7820,7 +7811,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131276491</v>
+        <v>131276488</v>
       </c>
       <c r="B58" t="n">
         <v>80365</v>
@@ -7858,10 +7849,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546074</v>
+        <v>546062</v>
       </c>
       <c r="R58" t="n">
-        <v>6999366</v>
+        <v>6999441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7946,10 +7937,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273412</v>
+        <v>131273394</v>
       </c>
       <c r="B59" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7957,26 +7948,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546441</v>
+        <v>546346</v>
       </c>
       <c r="R59" t="n">
-        <v>6999013</v>
+        <v>6999078</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8022,6 +8017,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8039,17 +8039,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8067,10 +8072,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131275129</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8078,31 +8083,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546338</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999380</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8148,17 +8148,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8169,17 +8165,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8197,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131273373</v>
+        <v>131273412</v>
       </c>
       <c r="B61" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8208,31 +8209,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8240,10 +8236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546097</v>
+        <v>546441</v>
       </c>
       <c r="R61" t="n">
-        <v>6999307</v>
+        <v>6999013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8278,17 +8274,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8307,14 +8299,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8332,7 +8319,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131276475</v>
+        <v>131275129</v>
       </c>
       <c r="B62" t="n">
         <v>57898</v>
@@ -8365,7 +8352,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8378,7 +8365,7 @@
         <v>546338</v>
       </c>
       <c r="R62" t="n">
-        <v>6999168</v>
+        <v>6999380</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8415,7 +8402,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8462,10 +8449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131275195</v>
+        <v>131273373</v>
       </c>
       <c r="B63" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8473,26 +8460,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8500,10 +8492,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>546150</v>
+        <v>546097</v>
       </c>
       <c r="R63" t="n">
-        <v>6999197</v>
+        <v>6999307</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8538,13 +8530,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8555,22 +8551,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8588,10 +8584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131276488</v>
+        <v>131276475</v>
       </c>
       <c r="B64" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8599,26 +8595,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8626,10 +8627,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>546062</v>
+        <v>546338</v>
       </c>
       <c r="R64" t="n">
-        <v>6999441</v>
+        <v>6999168</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8664,13 +8665,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8681,22 +8686,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131273384</v>
+        <v>131275211</v>
       </c>
       <c r="B65" t="n">
-        <v>80365</v>
+        <v>91848</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,34 +8725,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546286</v>
+        <v>546185</v>
       </c>
       <c r="R65" t="n">
-        <v>6999257</v>
+        <v>6999135</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8787,19 +8790,35 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Fertil med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8816,10 +8835,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131275211</v>
+        <v>131273414</v>
       </c>
       <c r="B66" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8827,26 +8846,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8854,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546185</v>
+        <v>546430</v>
       </c>
       <c r="R66" t="n">
-        <v>6999135</v>
+        <v>6998969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8937,7 +8956,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273414</v>
+        <v>131273420</v>
       </c>
       <c r="B67" t="n">
         <v>79260</v>
@@ -8975,10 +8994,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546430</v>
+        <v>546204</v>
       </c>
       <c r="R67" t="n">
-        <v>6998969</v>
+        <v>6999267</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9011,6 +9030,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9058,10 +9082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131273420</v>
+        <v>131273386</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9069,26 +9093,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9096,10 +9124,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546204</v>
+        <v>546294</v>
       </c>
       <c r="R68" t="n">
-        <v>6999267</v>
+        <v>6999434</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9136,7 +9164,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9156,17 +9184,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9184,10 +9217,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273386</v>
+        <v>131273416</v>
       </c>
       <c r="B69" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9195,30 +9228,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9226,10 +9255,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546294</v>
+        <v>546387</v>
       </c>
       <c r="R69" t="n">
-        <v>6999434</v>
+        <v>6999068</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9266,7 +9295,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9286,22 +9315,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9319,10 +9343,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273416</v>
+        <v>131275200</v>
       </c>
       <c r="B70" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9330,21 +9354,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9357,10 +9381,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546387</v>
+        <v>546174</v>
       </c>
       <c r="R70" t="n">
-        <v>6999068</v>
+        <v>6999354</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9395,11 +9419,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9417,17 +9436,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9445,10 +9469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273371</v>
+        <v>131273384</v>
       </c>
       <c r="B71" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9456,42 +9480,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546089</v>
+        <v>546286</v>
       </c>
       <c r="R71" t="n">
-        <v>6999267</v>
+        <v>6999257</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9528,7 +9544,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9539,26 +9555,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9575,7 +9571,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131276481</v>
+        <v>131273371</v>
       </c>
       <c r="B72" t="n">
         <v>57898</v>
@@ -9608,7 +9604,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9618,10 +9614,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546070</v>
+        <v>546089</v>
       </c>
       <c r="R72" t="n">
-        <v>6999374</v>
+        <v>6999267</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9658,7 +9654,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9705,7 +9701,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131273372</v>
+        <v>131276481</v>
       </c>
       <c r="B73" t="n">
         <v>57898</v>
@@ -9748,10 +9744,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546089</v>
+        <v>546070</v>
       </c>
       <c r="R73" t="n">
-        <v>6999297</v>
+        <v>6999374</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9788,7 +9784,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9815,14 +9811,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9840,10 +9831,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131275200</v>
+        <v>131273372</v>
       </c>
       <c r="B74" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9851,26 +9842,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9878,10 +9874,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546174</v>
+        <v>546089</v>
       </c>
       <c r="R74" t="n">
-        <v>6999354</v>
+        <v>6999297</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9916,13 +9912,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9933,22 +9933,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131276482</v>
+        <v>131276486</v>
       </c>
       <c r="B75" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9977,31 +9977,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10009,10 +10004,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>546075</v>
+        <v>546356</v>
       </c>
       <c r="R75" t="n">
-        <v>6999369</v>
+        <v>6999034</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10047,17 +10042,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10068,17 +10059,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10096,10 +10092,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131275132</v>
+        <v>131275181</v>
       </c>
       <c r="B76" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10107,54 +10103,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>546295</v>
+        <v>546435</v>
       </c>
       <c r="R76" t="n">
-        <v>6999077</v>
+        <v>6999096</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10191,7 +10170,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10200,6 +10179,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10208,9 +10188,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Äldre granskog med höga naturvärden.</t>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10228,10 +10223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131275144</v>
+        <v>131273393</v>
       </c>
       <c r="B77" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10239,29 +10234,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10271,10 +10265,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>546124</v>
+        <v>546394</v>
       </c>
       <c r="R77" t="n">
-        <v>6999127</v>
+        <v>6999043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10309,17 +10303,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10330,17 +10320,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10358,7 +10353,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131276486</v>
+        <v>131275202</v>
       </c>
       <c r="B78" t="n">
         <v>80365</v>
@@ -10396,10 +10391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>546356</v>
+        <v>546230</v>
       </c>
       <c r="R78" t="n">
-        <v>6999034</v>
+        <v>6999398</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10484,7 +10479,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131275181</v>
+        <v>131273402</v>
       </c>
       <c r="B79" t="n">
         <v>80365</v>
@@ -10522,10 +10517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>546435</v>
+        <v>546159</v>
       </c>
       <c r="R79" t="n">
-        <v>6999096</v>
+        <v>6999249</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10562,7 +10557,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10582,22 +10577,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10615,7 +10610,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131273393</v>
+        <v>131273392</v>
       </c>
       <c r="B80" t="n">
         <v>80365</v>
@@ -10645,11 +10640,7 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10657,10 +10648,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>546394</v>
+        <v>546398</v>
       </c>
       <c r="R80" t="n">
-        <v>6999043</v>
+        <v>6998976</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10745,10 +10736,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131275202</v>
+        <v>131276482</v>
       </c>
       <c r="B81" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10756,26 +10747,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10783,10 +10779,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>546230</v>
+        <v>546075</v>
       </c>
       <c r="R81" t="n">
-        <v>6999398</v>
+        <v>6999369</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10821,13 +10817,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10838,22 +10838,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10871,10 +10866,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131273402</v>
+        <v>131275132</v>
       </c>
       <c r="B82" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10882,37 +10877,54 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>546159</v>
+        <v>546295</v>
       </c>
       <c r="R82" t="n">
-        <v>6999249</v>
+        <v>6999077</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10949,7 +10961,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
+          <t>Synobservation av 1 hane som födosökte på en stående död gran. Fyndplatsen finns i en yta med en volym stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10958,7 +10970,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10967,24 +10978,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Äldre granskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11002,10 +10998,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131273392</v>
+        <v>131275144</v>
       </c>
       <c r="B83" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11013,26 +11009,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11040,10 +11041,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>546398</v>
+        <v>546124</v>
       </c>
       <c r="R83" t="n">
-        <v>6998976</v>
+        <v>6999127</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11078,13 +11079,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11095,22 +11100,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11515,32 +11515,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131275170</v>
+        <v>131276483</v>
       </c>
       <c r="B87" t="n">
-        <v>83231</v>
+        <v>80365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11553,10 +11553,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546401</v>
+        <v>546404</v>
       </c>
       <c r="R87" t="n">
-        <v>6999141</v>
+        <v>6999205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11641,10 +11641,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131275161</v>
+        <v>131275205</v>
       </c>
       <c r="B88" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11652,31 +11652,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11684,10 +11679,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546100</v>
+        <v>546149</v>
       </c>
       <c r="R88" t="n">
-        <v>6999276</v>
+        <v>6999093</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11722,17 +11717,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11743,17 +11734,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11771,7 +11767,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131275165</v>
+        <v>131275161</v>
       </c>
       <c r="B89" t="n">
         <v>57898</v>
@@ -11814,10 +11810,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546098</v>
+        <v>546100</v>
       </c>
       <c r="R89" t="n">
-        <v>6999296</v>
+        <v>6999276</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11854,7 +11850,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11901,7 +11897,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275164</v>
+        <v>131275165</v>
       </c>
       <c r="B90" t="n">
         <v>57898</v>
@@ -11944,10 +11940,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546097</v>
+        <v>546098</v>
       </c>
       <c r="R90" t="n">
-        <v>6999287</v>
+        <v>6999296</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12031,10 +12027,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131276483</v>
+        <v>131275164</v>
       </c>
       <c r="B91" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12042,26 +12038,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12069,10 +12070,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546404</v>
+        <v>546097</v>
       </c>
       <c r="R91" t="n">
-        <v>6999205</v>
+        <v>6999287</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12107,13 +12108,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12124,22 +12129,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12157,32 +12157,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275205</v>
+        <v>131275170</v>
       </c>
       <c r="B92" t="n">
-        <v>80365</v>
+        <v>83231</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12195,10 +12195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546149</v>
+        <v>546401</v>
       </c>
       <c r="R92" t="n">
-        <v>6999093</v>
+        <v>6999141</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12283,39 +12283,47 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131273362</v>
+        <v>131275217</v>
       </c>
       <c r="B93" t="n">
-        <v>91828</v>
+        <v>83227</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -12325,10 +12333,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546302</v>
+        <v>546307</v>
       </c>
       <c r="R93" t="n">
-        <v>6999463</v>
+        <v>6999069</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12365,7 +12373,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12383,24 +12391,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12418,37 +12436,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131275209</v>
+        <v>131273362</v>
       </c>
       <c r="B94" t="n">
-        <v>80325</v>
+        <v>91828</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12456,10 +12478,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546171</v>
+        <v>546302</v>
       </c>
       <c r="R94" t="n">
-        <v>6999219</v>
+        <v>6999463</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12494,6 +12516,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12511,22 +12538,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12544,47 +12571,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275217</v>
+        <v>131276477</v>
       </c>
       <c r="B95" t="n">
-        <v>83227</v>
+        <v>57898</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -12594,10 +12614,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546307</v>
+        <v>546062</v>
       </c>
       <c r="R95" t="n">
-        <v>6999069</v>
+        <v>6999442</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12634,7 +12654,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12643,7 +12663,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12652,34 +12671,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12697,10 +12701,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131273424</v>
+        <v>131275135</v>
       </c>
       <c r="B96" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12708,26 +12712,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -12735,10 +12744,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546090</v>
+        <v>546142</v>
       </c>
       <c r="R96" t="n">
-        <v>6999323</v>
+        <v>6999047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12775,7 +12784,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12784,7 +12793,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12823,7 +12831,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131276477</v>
+        <v>131275158</v>
       </c>
       <c r="B97" t="n">
         <v>57898</v>
@@ -12866,10 +12874,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546062</v>
+        <v>546100</v>
       </c>
       <c r="R97" t="n">
-        <v>6999442</v>
+        <v>6999268</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12953,7 +12961,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131275135</v>
+        <v>131273366</v>
       </c>
       <c r="B98" t="n">
         <v>57898</v>
@@ -12996,10 +13004,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546142</v>
+        <v>546100</v>
       </c>
       <c r="R98" t="n">
-        <v>6999047</v>
+        <v>6999258</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13036,7 +13044,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13063,9 +13071,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13083,10 +13096,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131275158</v>
+        <v>131273424</v>
       </c>
       <c r="B99" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13094,31 +13107,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13126,10 +13134,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546100</v>
+        <v>546090</v>
       </c>
       <c r="R99" t="n">
-        <v>6999268</v>
+        <v>6999323</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13166,7 +13174,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13175,6 +13183,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13213,42 +13222,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131273366</v>
+        <v>131275209</v>
       </c>
       <c r="B100" t="n">
-        <v>57898</v>
+        <v>80325</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13256,10 +13260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546100</v>
+        <v>546171</v>
       </c>
       <c r="R100" t="n">
-        <v>6999258</v>
+        <v>6999219</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13294,17 +13298,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13315,22 +13315,22 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -14919,37 +14919,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131273418</v>
+        <v>131273363</v>
       </c>
       <c r="B113" t="n">
-        <v>79260</v>
+        <v>92550</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14957,10 +14961,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546329</v>
+        <v>546304</v>
       </c>
       <c r="R113" t="n">
-        <v>6999224</v>
+        <v>6999379</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14997,7 +15001,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15025,9 +15029,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15045,37 +15054,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131275174</v>
+        <v>131273387</v>
       </c>
       <c r="B114" t="n">
-        <v>75238</v>
+        <v>80365</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15083,10 +15096,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546222</v>
+        <v>546286</v>
       </c>
       <c r="R114" t="n">
-        <v>6999408</v>
+        <v>6999419</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15123,7 +15136,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15176,10 +15189,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275212</v>
+        <v>131275167</v>
       </c>
       <c r="B115" t="n">
-        <v>91848</v>
+        <v>80231</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15187,26 +15200,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15214,10 +15227,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546213</v>
+        <v>546468</v>
       </c>
       <c r="R115" t="n">
-        <v>6999022</v>
+        <v>6999037</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15269,17 +15282,17 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15297,10 +15310,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131275166</v>
+        <v>131273418</v>
       </c>
       <c r="B116" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15308,31 +15321,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15340,10 +15348,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546208</v>
+        <v>546329</v>
       </c>
       <c r="R116" t="n">
-        <v>6999393</v>
+        <v>6999224</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15380,7 +15388,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15389,6 +15397,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15427,10 +15436,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131273363</v>
+        <v>131275174</v>
       </c>
       <c r="B117" t="n">
-        <v>92550</v>
+        <v>75238</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15438,30 +15447,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>6428</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -15469,10 +15474,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546304</v>
+        <v>546222</v>
       </c>
       <c r="R117" t="n">
-        <v>6999379</v>
+        <v>6999408</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15509,7 +15514,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15529,22 +15534,22 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15562,10 +15567,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131273387</v>
+        <v>131275212</v>
       </c>
       <c r="B118" t="n">
-        <v>80365</v>
+        <v>91848</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15573,28 +15578,24 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -15604,10 +15605,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546286</v>
+        <v>546213</v>
       </c>
       <c r="R118" t="n">
-        <v>6999419</v>
+        <v>6999022</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15642,11 +15643,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -15664,22 +15660,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15697,10 +15688,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131275167</v>
+        <v>131275166</v>
       </c>
       <c r="B119" t="n">
-        <v>80231</v>
+        <v>57898</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15708,26 +15699,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15735,10 +15731,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>546468</v>
+        <v>546208</v>
       </c>
       <c r="R119" t="n">
-        <v>6999037</v>
+        <v>6999393</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15773,13 +15769,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -15790,17 +15790,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -18268,42 +18268,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>131275147</v>
+        <v>131275208</v>
       </c>
       <c r="B139" t="n">
-        <v>57898</v>
+        <v>80325</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -18311,10 +18306,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>546137</v>
+        <v>546460</v>
       </c>
       <c r="R139" t="n">
-        <v>6999148</v>
+        <v>6999073</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18349,17 +18344,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -18370,17 +18361,22 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18398,7 +18394,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131275136</v>
+        <v>131275147</v>
       </c>
       <c r="B140" t="n">
         <v>57898</v>
@@ -18441,10 +18437,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>546148</v>
+        <v>546137</v>
       </c>
       <c r="R140" t="n">
-        <v>6999041</v>
+        <v>6999148</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18528,7 +18524,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>131275138</v>
+        <v>131275136</v>
       </c>
       <c r="B141" t="n">
         <v>57898</v>
@@ -18571,10 +18567,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>546145</v>
+        <v>546148</v>
       </c>
       <c r="R141" t="n">
-        <v>6999053</v>
+        <v>6999041</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -18658,37 +18654,42 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>131275208</v>
+        <v>131275138</v>
       </c>
       <c r="B142" t="n">
-        <v>80325</v>
+        <v>57898</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -18696,10 +18697,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>546460</v>
+        <v>546145</v>
       </c>
       <c r="R142" t="n">
-        <v>6999073</v>
+        <v>6999053</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -18734,13 +18735,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -18751,22 +18756,17 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -19915,10 +19915,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131275177</v>
+        <v>131273405</v>
       </c>
       <c r="B152" t="n">
-        <v>83235</v>
+        <v>80365</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19926,21 +19926,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -19953,10 +19953,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546303</v>
+        <v>546169</v>
       </c>
       <c r="R152" t="n">
-        <v>6999065</v>
+        <v>6999410</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På grov bark av en grov asphögstubbe.</t>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20011,11 +20011,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>Äldre granskog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ152" t="inlineStr">
         <is>
           <t>asp</t>
@@ -20028,12 +20023,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20051,10 +20046,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>131275189</v>
+        <v>131275177</v>
       </c>
       <c r="B153" t="n">
-        <v>80365</v>
+        <v>83235</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20062,21 +20057,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -20089,10 +20084,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>546224</v>
+        <v>546303</v>
       </c>
       <c r="R153" t="n">
-        <v>6999013</v>
+        <v>6999065</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -20129,7 +20124,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grov bark av en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -20147,24 +20142,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Äldre granskog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -20182,7 +20182,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>131273405</v>
+        <v>131275189</v>
       </c>
       <c r="B154" t="n">
         <v>80365</v>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>546169</v>
+        <v>546224</v>
       </c>
       <c r="R154" t="n">
-        <v>6999410</v>
+        <v>6999013</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Enstaka bålar på asp.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20280,12 +20280,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131275215</v>
+        <v>131273378</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,26 +933,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546164</v>
+        <v>546094</v>
       </c>
       <c r="R4" t="n">
-        <v>6999199</v>
+        <v>6999329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1014,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,9 +1032,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131273397</v>
+        <v>131275145</v>
       </c>
       <c r="B5" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,26 +1068,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546296</v>
+        <v>546148</v>
       </c>
       <c r="R5" t="n">
-        <v>6999259</v>
+        <v>6999078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1140,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1149,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,22 +1159,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275180</v>
+        <v>131275160</v>
       </c>
       <c r="B6" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,26 +1198,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1230,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546406</v>
+        <v>546104</v>
       </c>
       <c r="R6" t="n">
-        <v>6999201</v>
+        <v>6999263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1270,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1279,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,17 +1289,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1317,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131275187</v>
+        <v>131276476</v>
       </c>
       <c r="B7" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1328,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1360,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546202</v>
+        <v>546050</v>
       </c>
       <c r="R7" t="n">
-        <v>6999223</v>
+        <v>6999453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1400,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1409,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1403,17 +1419,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1447,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131273378</v>
+        <v>131275215</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,31 +1458,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1474,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546094</v>
+        <v>546164</v>
       </c>
       <c r="R8" t="n">
-        <v>6999329</v>
+        <v>6999199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1525,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,6 +1534,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1541,14 +1553,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131275145</v>
+        <v>131273397</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,31 +1584,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1609,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546148</v>
+        <v>546296</v>
       </c>
       <c r="R9" t="n">
-        <v>6999078</v>
+        <v>6999259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,7 +1651,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,6 +1660,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1668,17 +1671,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275160</v>
+        <v>131275180</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,31 +1715,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1739,10 +1742,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546104</v>
+        <v>546406</v>
       </c>
       <c r="R10" t="n">
-        <v>6999263</v>
+        <v>6999201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,7 +1782,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,6 +1791,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1798,17 +1802,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1826,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131276476</v>
+        <v>131275187</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,31 +1841,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1869,10 +1868,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546050</v>
+        <v>546202</v>
       </c>
       <c r="R11" t="n">
-        <v>6999453</v>
+        <v>6999223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1909,7 +1908,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,6 +1917,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273391</v>
+        <v>131273421</v>
       </c>
       <c r="B12" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,30 +1967,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1998,10 +1994,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546459</v>
+        <v>546167</v>
       </c>
       <c r="R12" t="n">
-        <v>6998921</v>
+        <v>6999264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2053,22 +2049,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2086,7 +2077,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131273407</v>
+        <v>131273391</v>
       </c>
       <c r="B13" t="n">
         <v>80365</v>
@@ -2118,7 +2109,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2128,10 +2119,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546227</v>
+        <v>546459</v>
       </c>
       <c r="R13" t="n">
-        <v>6999437</v>
+        <v>6998921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2164,11 +2155,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,7 +2207,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131276484</v>
+        <v>131275185</v>
       </c>
       <c r="B14" t="n">
         <v>80365</v>
@@ -2259,10 +2245,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546500</v>
+        <v>546230</v>
       </c>
       <c r="R14" t="n">
-        <v>6998983</v>
+        <v>6999202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2297,6 +2283,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2314,12 +2305,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2329,7 +2320,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2347,7 +2338,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131275184</v>
+        <v>131273407</v>
       </c>
       <c r="B15" t="n">
         <v>80365</v>
@@ -2377,7 +2368,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546300</v>
+        <v>546227</v>
       </c>
       <c r="R15" t="n">
-        <v>6999066</v>
+        <v>6999437</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2423,6 +2418,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2436,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2453,7 +2473,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131275192</v>
+        <v>131276484</v>
       </c>
       <c r="B16" t="n">
         <v>80365</v>
@@ -2491,10 +2511,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546168</v>
+        <v>546500</v>
       </c>
       <c r="R16" t="n">
-        <v>6999218</v>
+        <v>6998983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2579,7 +2599,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131275185</v>
+        <v>131275184</v>
       </c>
       <c r="B17" t="n">
         <v>80365</v>
@@ -2617,10 +2637,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546230</v>
+        <v>546300</v>
       </c>
       <c r="R17" t="n">
-        <v>6999202</v>
+        <v>6999066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2655,11 +2675,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2673,26 +2688,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2710,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131273421</v>
+        <v>131275192</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,21 +2716,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546167</v>
+        <v>546168</v>
       </c>
       <c r="R18" t="n">
-        <v>6999264</v>
+        <v>6999218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2803,17 +2798,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275175</v>
+        <v>131275191</v>
       </c>
       <c r="B29" t="n">
-        <v>75350</v>
+        <v>80365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546372</v>
+        <v>546174</v>
       </c>
       <c r="R29" t="n">
-        <v>6998999</v>
+        <v>6999215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark av gran i äldre granskog.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275206</v>
+        <v>131275201</v>
       </c>
       <c r="B30" t="n">
-        <v>78272</v>
+        <v>80365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546408</v>
+        <v>546222</v>
       </c>
       <c r="R30" t="n">
-        <v>6999129</v>
+        <v>6999418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275191</v>
+        <v>131275178</v>
       </c>
       <c r="B31" t="n">
         <v>80365</v>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546174</v>
+        <v>546403</v>
       </c>
       <c r="R31" t="n">
-        <v>6999215</v>
+        <v>6999213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4475,11 +4475,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4493,26 +4488,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4530,10 +4505,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275201</v>
+        <v>131275206</v>
       </c>
       <c r="B32" t="n">
-        <v>80365</v>
+        <v>78272</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4541,21 +4516,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4568,10 +4543,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546222</v>
+        <v>546408</v>
       </c>
       <c r="R32" t="n">
-        <v>6999418</v>
+        <v>6999129</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4623,12 +4598,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4638,7 +4613,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4656,10 +4631,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275178</v>
+        <v>131275175</v>
       </c>
       <c r="B33" t="n">
-        <v>80365</v>
+        <v>75350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,21 +4642,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4694,10 +4669,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546403</v>
+        <v>546372</v>
       </c>
       <c r="R33" t="n">
-        <v>6999213</v>
+        <v>6998999</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,6 +4707,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark av gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4745,6 +4725,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131276490</v>
+        <v>131273365</v>
       </c>
       <c r="B34" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4773,26 +4773,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4800,10 +4805,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546070</v>
+        <v>546239</v>
       </c>
       <c r="R34" t="n">
-        <v>6999377</v>
+        <v>6999263</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4838,13 +4843,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4855,22 +4864,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4888,10 +4897,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131276489</v>
+        <v>131275146</v>
       </c>
       <c r="B35" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4899,26 +4908,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4926,10 +4940,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546065</v>
+        <v>546130</v>
       </c>
       <c r="R35" t="n">
-        <v>6999434</v>
+        <v>6999093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4964,13 +4978,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4981,22 +4999,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5014,10 +5027,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131273389</v>
+        <v>131275152</v>
       </c>
       <c r="B36" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5025,34 +5038,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546366</v>
+        <v>546122</v>
       </c>
       <c r="R36" t="n">
-        <v>6999149</v>
+        <v>6999205</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5089,7 +5110,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på en sälg. Fertil!</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5100,6 +5121,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5116,10 +5157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131276492</v>
+        <v>131275155</v>
       </c>
       <c r="B37" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5127,26 +5168,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5154,10 +5200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546097</v>
+        <v>546116</v>
       </c>
       <c r="R37" t="n">
-        <v>6999346</v>
+        <v>6999243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5192,13 +5238,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5209,22 +5259,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5242,7 +5287,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131275193</v>
+        <v>131276490</v>
       </c>
       <c r="B38" t="n">
         <v>80365</v>
@@ -5280,10 +5325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546158</v>
+        <v>546070</v>
       </c>
       <c r="R38" t="n">
-        <v>6999223</v>
+        <v>6999377</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5318,11 +5363,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5340,12 +5380,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5355,7 +5395,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5373,10 +5413,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131273365</v>
+        <v>131276489</v>
       </c>
       <c r="B39" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5384,31 +5424,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5416,10 +5451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546239</v>
+        <v>546065</v>
       </c>
       <c r="R39" t="n">
-        <v>6999263</v>
+        <v>6999434</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5454,17 +5489,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5475,22 +5506,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5508,10 +5539,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131275146</v>
+        <v>131275193</v>
       </c>
       <c r="B40" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5519,31 +5550,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5551,10 +5577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546130</v>
+        <v>546158</v>
       </c>
       <c r="R40" t="n">
-        <v>6999093</v>
+        <v>6999223</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5591,7 +5617,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5600,6 +5626,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5610,17 +5637,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5638,10 +5670,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131275152</v>
+        <v>131273389</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5649,42 +5681,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546122</v>
+        <v>546366</v>
       </c>
       <c r="R41" t="n">
-        <v>6999205</v>
+        <v>6999149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5721,7 +5745,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt på en sälg. Fertil!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5732,26 +5756,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5768,10 +5772,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131275155</v>
+        <v>131276492</v>
       </c>
       <c r="B42" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5779,31 +5783,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5811,10 +5810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546116</v>
+        <v>546097</v>
       </c>
       <c r="R42" t="n">
-        <v>6999243</v>
+        <v>6999346</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5849,17 +5848,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5870,17 +5865,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131275182</v>
+        <v>131273410</v>
       </c>
       <c r="B43" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546357</v>
+        <v>546342</v>
       </c>
       <c r="R43" t="n">
-        <v>6999022</v>
+        <v>6999195</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5987,6 +5987,21 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6004,7 +6019,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131273410</v>
+        <v>131273426</v>
       </c>
       <c r="B44" t="n">
         <v>79260</v>
@@ -6042,10 +6057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546342</v>
+        <v>546172</v>
       </c>
       <c r="R44" t="n">
-        <v>6999195</v>
+        <v>6999385</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6078,6 +6093,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6125,7 +6145,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131273426</v>
+        <v>131275213</v>
       </c>
       <c r="B45" t="n">
         <v>79260</v>
@@ -6163,10 +6183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546172</v>
+        <v>546481</v>
       </c>
       <c r="R45" t="n">
-        <v>6999385</v>
+        <v>6998980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6199,11 +6219,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6251,10 +6266,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131273406</v>
+        <v>131273374</v>
       </c>
       <c r="B46" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6262,26 +6277,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6289,10 +6309,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546223</v>
+        <v>546094</v>
       </c>
       <c r="R46" t="n">
-        <v>6999436</v>
+        <v>6999322</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6329,7 +6349,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6338,7 +6358,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6359,12 +6378,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6382,10 +6401,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131275213</v>
+        <v>131275151</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6393,26 +6412,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6420,10 +6444,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546481</v>
+        <v>546124</v>
       </c>
       <c r="R47" t="n">
-        <v>6998980</v>
+        <v>6999206</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6458,13 +6482,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6503,10 +6531,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131276487</v>
+        <v>131275159</v>
       </c>
       <c r="B48" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6514,26 +6542,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6541,10 +6574,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546313</v>
+        <v>546099</v>
       </c>
       <c r="R48" t="n">
-        <v>6999060</v>
+        <v>6999277</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6579,13 +6612,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6596,22 +6633,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6629,39 +6661,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131273381</v>
+        <v>131276478</v>
       </c>
       <c r="B49" t="n">
-        <v>80394</v>
+        <v>57898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6671,10 +6704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546353</v>
+        <v>546058</v>
       </c>
       <c r="R49" t="n">
-        <v>6999084</v>
+        <v>6999435</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6711,7 +6744,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6720,7 +6753,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6731,22 +6763,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6764,10 +6791,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131275194</v>
+        <v>131275139</v>
       </c>
       <c r="B50" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6775,26 +6802,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6802,10 +6834,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546153</v>
+        <v>546151</v>
       </c>
       <c r="R50" t="n">
-        <v>6999210</v>
+        <v>6999044</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6842,7 +6874,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6851,7 +6883,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6862,22 +6893,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6895,7 +6921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131273401</v>
+        <v>131275182</v>
       </c>
       <c r="B51" t="n">
         <v>80365</v>
@@ -6925,11 +6951,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6937,10 +6959,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546279</v>
+        <v>546357</v>
       </c>
       <c r="R51" t="n">
-        <v>6999244</v>
+        <v>6999022</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6975,11 +6997,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6993,26 +7010,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7030,10 +7027,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131273374</v>
+        <v>131276487</v>
       </c>
       <c r="B52" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7041,31 +7038,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7073,10 +7065,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546094</v>
+        <v>546313</v>
       </c>
       <c r="R52" t="n">
-        <v>6999322</v>
+        <v>6999060</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7111,17 +7103,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7132,22 +7120,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7165,40 +7153,39 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131275151</v>
+        <v>131273381</v>
       </c>
       <c r="B53" t="n">
-        <v>57898</v>
+        <v>80394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7208,10 +7195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546124</v>
+        <v>546353</v>
       </c>
       <c r="R53" t="n">
-        <v>6999206</v>
+        <v>6999084</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7248,7 +7235,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7257,6 +7244,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7267,17 +7255,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7295,10 +7288,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131275159</v>
+        <v>131275194</v>
       </c>
       <c r="B54" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7306,31 +7299,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7338,10 +7326,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546099</v>
+        <v>546153</v>
       </c>
       <c r="R54" t="n">
-        <v>6999277</v>
+        <v>6999210</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7378,7 +7366,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7387,6 +7375,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7397,17 +7386,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7425,10 +7419,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131276478</v>
+        <v>131273401</v>
       </c>
       <c r="B55" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7436,29 +7430,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7468,10 +7461,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546058</v>
+        <v>546279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999435</v>
+        <v>6999244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7508,7 +7501,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7517,6 +7510,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7527,17 +7521,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7555,10 +7554,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131275139</v>
+        <v>131273406</v>
       </c>
       <c r="B56" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7566,31 +7565,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7598,10 +7592,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546151</v>
+        <v>546223</v>
       </c>
       <c r="R56" t="n">
-        <v>6999044</v>
+        <v>6999436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7638,7 +7632,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7647,6 +7641,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7665,9 +7660,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131275195</v>
+        <v>131273412</v>
       </c>
       <c r="B57" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,21 +7696,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546150</v>
+        <v>546441</v>
       </c>
       <c r="R57" t="n">
-        <v>6999197</v>
+        <v>6999013</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7778,22 +7778,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7811,7 +7806,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131276488</v>
+        <v>131275195</v>
       </c>
       <c r="B58" t="n">
         <v>80365</v>
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546062</v>
+        <v>546150</v>
       </c>
       <c r="R58" t="n">
-        <v>6999441</v>
+        <v>6999197</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7904,12 +7899,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7919,7 +7914,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8072,7 +8067,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276491</v>
+        <v>131276488</v>
       </c>
       <c r="B60" t="n">
         <v>80365</v>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546074</v>
+        <v>546062</v>
       </c>
       <c r="R60" t="n">
-        <v>6999366</v>
+        <v>6999441</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8198,10 +8193,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131273412</v>
+        <v>131276491</v>
       </c>
       <c r="B61" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8209,21 +8204,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8236,10 +8231,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546441</v>
+        <v>546074</v>
       </c>
       <c r="R61" t="n">
-        <v>6999013</v>
+        <v>6999366</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8291,17 +8286,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131275211</v>
+        <v>131273414</v>
       </c>
       <c r="B65" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546185</v>
+        <v>546430</v>
       </c>
       <c r="R65" t="n">
-        <v>6999135</v>
+        <v>6998969</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8835,7 +8835,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273414</v>
+        <v>131273420</v>
       </c>
       <c r="B66" t="n">
         <v>79260</v>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546430</v>
+        <v>546204</v>
       </c>
       <c r="R66" t="n">
-        <v>6998969</v>
+        <v>6999267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8909,6 +8909,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8956,10 +8961,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131273420</v>
+        <v>131275211</v>
       </c>
       <c r="B67" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8967,26 +8972,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8994,10 +8999,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546204</v>
+        <v>546185</v>
       </c>
       <c r="R67" t="n">
-        <v>6999267</v>
+        <v>6999135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9030,11 +9035,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131273386</v>
+        <v>131273416</v>
       </c>
       <c r="B68" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9093,30 +9093,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9124,10 +9120,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546294</v>
+        <v>546387</v>
       </c>
       <c r="R68" t="n">
-        <v>6999434</v>
+        <v>6999068</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9164,7 +9160,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9184,22 +9180,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9217,10 +9208,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131273416</v>
+        <v>131275200</v>
       </c>
       <c r="B69" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9228,21 +9219,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9255,10 +9246,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546387</v>
+        <v>546174</v>
       </c>
       <c r="R69" t="n">
-        <v>6999068</v>
+        <v>6999354</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9293,11 +9284,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9315,17 +9301,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9343,7 +9334,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131275200</v>
+        <v>131273384</v>
       </c>
       <c r="B70" t="n">
         <v>80365</v>
@@ -9372,19 +9363,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546174</v>
+        <v>546286</v>
       </c>
       <c r="R70" t="n">
-        <v>6999354</v>
+        <v>6999257</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9419,40 +9407,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fertil med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9469,7 +9436,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273384</v>
+        <v>131273386</v>
       </c>
       <c r="B71" t="n">
         <v>80365</v>
@@ -9498,16 +9465,23 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546286</v>
+        <v>546294</v>
       </c>
       <c r="R71" t="n">
-        <v>6999257</v>
+        <v>6999434</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9544,7 +9518,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fertil med apothecier på sälg.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9553,8 +9527,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9966,7 +9966,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131276486</v>
+        <v>131275202</v>
       </c>
       <c r="B75" t="n">
         <v>80365</v>
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>546356</v>
+        <v>546230</v>
       </c>
       <c r="R75" t="n">
-        <v>6999034</v>
+        <v>6999398</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10092,7 +10092,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131275181</v>
+        <v>131273402</v>
       </c>
       <c r="B76" t="n">
         <v>80365</v>
@@ -10130,10 +10130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>546435</v>
+        <v>546159</v>
       </c>
       <c r="R76" t="n">
-        <v>6999096</v>
+        <v>6999249</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10190,22 +10190,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10223,7 +10223,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131273393</v>
+        <v>131273392</v>
       </c>
       <c r="B77" t="n">
         <v>80365</v>
@@ -10253,11 +10253,7 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10265,10 +10261,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>546394</v>
+        <v>546398</v>
       </c>
       <c r="R77" t="n">
-        <v>6999043</v>
+        <v>6998976</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10353,7 +10349,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131275202</v>
+        <v>131276486</v>
       </c>
       <c r="B78" t="n">
         <v>80365</v>
@@ -10391,10 +10387,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>546230</v>
+        <v>546356</v>
       </c>
       <c r="R78" t="n">
-        <v>6999398</v>
+        <v>6999034</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10479,7 +10475,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131273402</v>
+        <v>131275181</v>
       </c>
       <c r="B79" t="n">
         <v>80365</v>
@@ -10517,10 +10513,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>546159</v>
+        <v>546435</v>
       </c>
       <c r="R79" t="n">
-        <v>6999249</v>
+        <v>6999096</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10557,7 +10553,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10577,22 +10573,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10610,7 +10606,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131273392</v>
+        <v>131273393</v>
       </c>
       <c r="B80" t="n">
         <v>80365</v>
@@ -10640,7 +10636,11 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>546398</v>
+        <v>546394</v>
       </c>
       <c r="R80" t="n">
-        <v>6998976</v>
+        <v>6999043</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11128,32 +11128,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131275204</v>
+        <v>131275170</v>
       </c>
       <c r="B84" t="n">
-        <v>80365</v>
+        <v>83231</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>546244</v>
+        <v>546401</v>
       </c>
       <c r="R84" t="n">
-        <v>6999418</v>
+        <v>6999141</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131273388</v>
+        <v>131275161</v>
       </c>
       <c r="B85" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11265,28 +11265,29 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11296,10 +11297,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546370</v>
+        <v>546100</v>
       </c>
       <c r="R85" t="n">
-        <v>6999140</v>
+        <v>6999276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11336,7 +11337,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11345,7 +11346,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11356,22 +11356,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11389,10 +11384,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131275188</v>
+        <v>131275165</v>
       </c>
       <c r="B86" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11400,26 +11395,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546149</v>
+        <v>546098</v>
       </c>
       <c r="R86" t="n">
-        <v>6999276</v>
+        <v>6999296</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11476,7 +11476,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11487,17 +11486,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11515,10 +11514,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131276483</v>
+        <v>131275164</v>
       </c>
       <c r="B87" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11526,26 +11525,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11553,10 +11557,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546404</v>
+        <v>546097</v>
       </c>
       <c r="R87" t="n">
-        <v>6999205</v>
+        <v>6999287</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11591,13 +11595,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11608,22 +11616,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11641,7 +11644,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131275205</v>
+        <v>131275204</v>
       </c>
       <c r="B88" t="n">
         <v>80365</v>
@@ -11679,10 +11682,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546149</v>
+        <v>546244</v>
       </c>
       <c r="R88" t="n">
-        <v>6999093</v>
+        <v>6999418</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11767,10 +11770,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131275161</v>
+        <v>131276483</v>
       </c>
       <c r="B89" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11778,31 +11781,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -11810,10 +11808,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546100</v>
+        <v>546404</v>
       </c>
       <c r="R89" t="n">
-        <v>6999276</v>
+        <v>6999205</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11848,17 +11846,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11869,17 +11863,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11897,10 +11896,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275165</v>
+        <v>131275205</v>
       </c>
       <c r="B90" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11908,31 +11907,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11940,10 +11934,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546098</v>
+        <v>546149</v>
       </c>
       <c r="R90" t="n">
-        <v>6999296</v>
+        <v>6999093</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11978,17 +11972,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11999,17 +11989,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12027,10 +12022,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131275164</v>
+        <v>131273388</v>
       </c>
       <c r="B91" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12038,29 +12033,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12070,10 +12064,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546097</v>
+        <v>546370</v>
       </c>
       <c r="R91" t="n">
-        <v>6999287</v>
+        <v>6999140</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12110,7 +12104,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12119,6 +12113,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12129,17 +12124,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12157,32 +12157,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275170</v>
+        <v>131275188</v>
       </c>
       <c r="B92" t="n">
-        <v>83231</v>
+        <v>80365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12195,10 +12195,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546401</v>
+        <v>546149</v>
       </c>
       <c r="R92" t="n">
-        <v>6999141</v>
+        <v>6999276</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12233,6 +12233,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -12250,22 +12255,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12283,47 +12283,40 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131275217</v>
+        <v>131276477</v>
       </c>
       <c r="B93" t="n">
-        <v>83227</v>
+        <v>57898</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>307</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blekskaftad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca cinerea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Tibell</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -12333,10 +12326,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546307</v>
+        <v>546062</v>
       </c>
       <c r="R93" t="n">
-        <v>6999069</v>
+        <v>6999442</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12373,7 +12366,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12382,7 +12375,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12391,34 +12383,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av asp.</t>
-        </is>
-      </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12436,10 +12413,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131273362</v>
+        <v>131275135</v>
       </c>
       <c r="B94" t="n">
-        <v>91828</v>
+        <v>57898</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12447,28 +12424,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -12478,10 +12456,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546302</v>
+        <v>546142</v>
       </c>
       <c r="R94" t="n">
-        <v>6999463</v>
+        <v>6999047</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12518,7 +12496,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12527,7 +12505,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12546,14 +12523,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12571,7 +12543,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131276477</v>
+        <v>131275158</v>
       </c>
       <c r="B95" t="n">
         <v>57898</v>
@@ -12614,10 +12586,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546062</v>
+        <v>546100</v>
       </c>
       <c r="R95" t="n">
-        <v>6999442</v>
+        <v>6999268</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12701,7 +12673,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131275135</v>
+        <v>131273366</v>
       </c>
       <c r="B96" t="n">
         <v>57898</v>
@@ -12744,10 +12716,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>546142</v>
+        <v>546100</v>
       </c>
       <c r="R96" t="n">
-        <v>6999047</v>
+        <v>6999258</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12784,7 +12756,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12811,9 +12783,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12831,42 +12808,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131275158</v>
+        <v>131275209</v>
       </c>
       <c r="B97" t="n">
-        <v>57898</v>
+        <v>80325</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12874,10 +12846,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546100</v>
+        <v>546171</v>
       </c>
       <c r="R97" t="n">
-        <v>6999268</v>
+        <v>6999219</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12912,17 +12884,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12933,17 +12901,22 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12961,40 +12934,47 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131273366</v>
+        <v>131275217</v>
       </c>
       <c r="B98" t="n">
-        <v>57898</v>
+        <v>83227</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blekskaftad nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca cinerea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -13004,10 +12984,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>546100</v>
+        <v>546307</v>
       </c>
       <c r="R98" t="n">
-        <v>6999258</v>
+        <v>6999069</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13044,7 +13024,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Väl utbredd (ca 3,5 dm2) på grov bark på nedre delen av en grov asphögstubbe med 66 cm i brösthöjdsdiameter och ca 7 meters höjd.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13053,6 +13033,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13061,24 +13042,34 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av asp.</t>
+        </is>
+      </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Särskilt grov bark. # Populus tremula # En ca 7 meter hög asphögstubbe med 66 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13096,10 +13087,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131273424</v>
+        <v>131273362</v>
       </c>
       <c r="B99" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13107,26 +13098,30 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13134,10 +13129,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>546090</v>
+        <v>546302</v>
       </c>
       <c r="R99" t="n">
-        <v>6999323</v>
+        <v>6999463</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13174,7 +13169,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Riktigt med fruktkroppar i en relativt grov granlåga.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13202,9 +13197,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13222,32 +13222,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131275209</v>
+        <v>131273424</v>
       </c>
       <c r="B100" t="n">
-        <v>80325</v>
+        <v>79260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13260,10 +13260,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>546171</v>
+        <v>546090</v>
       </c>
       <c r="R100" t="n">
-        <v>6999219</v>
+        <v>6999323</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13298,6 +13298,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -13315,22 +13320,17 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273409</v>
+        <v>131273419</v>
       </c>
       <c r="B101" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,26 +13359,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546299</v>
+        <v>546230</v>
       </c>
       <c r="R101" t="n">
-        <v>6999454</v>
+        <v>6999267</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13454,14 +13454,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13479,10 +13484,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273419</v>
+        <v>131273409</v>
       </c>
       <c r="B102" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13490,26 +13495,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13517,10 +13522,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546230</v>
+        <v>546299</v>
       </c>
       <c r="R102" t="n">
-        <v>6999267</v>
+        <v>6999454</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13557,7 +13562,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13572,7 +13577,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13585,19 +13590,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131275137</v>
+        <v>131273395</v>
       </c>
       <c r="B103" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13626,31 +13626,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13658,10 +13653,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>546139</v>
+        <v>546313</v>
       </c>
       <c r="R103" t="n">
-        <v>6999047</v>
+        <v>6999066</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13698,7 +13693,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13707,6 +13702,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13725,9 +13721,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13745,10 +13746,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131273380</v>
+        <v>131275207</v>
       </c>
       <c r="B104" t="n">
-        <v>57898</v>
+        <v>78272</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13756,31 +13757,26 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13788,10 +13784,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546091</v>
+        <v>546365</v>
       </c>
       <c r="R104" t="n">
-        <v>6999334</v>
+        <v>6998993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13826,17 +13822,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13855,14 +13847,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -13880,7 +13867,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131273377</v>
+        <v>131275137</v>
       </c>
       <c r="B105" t="n">
         <v>57898</v>
@@ -13923,10 +13910,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546077</v>
+        <v>546139</v>
       </c>
       <c r="R105" t="n">
-        <v>6999352</v>
+        <v>6999047</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13963,7 +13950,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13990,14 +13977,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14015,10 +13997,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131275207</v>
+        <v>131273380</v>
       </c>
       <c r="B106" t="n">
-        <v>78272</v>
+        <v>57898</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14026,26 +14008,31 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14053,10 +14040,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546365</v>
+        <v>546091</v>
       </c>
       <c r="R106" t="n">
-        <v>6998993</v>
+        <v>6999334</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14091,13 +14078,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -14116,9 +14107,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14136,10 +14132,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131273395</v>
+        <v>131273377</v>
       </c>
       <c r="B107" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14147,26 +14143,31 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14174,10 +14175,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546313</v>
+        <v>546077</v>
       </c>
       <c r="R107" t="n">
-        <v>6999066</v>
+        <v>6999352</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14214,7 +14215,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran vid en grov asphögstubbe.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14223,7 +14224,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14267,32 +14267,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131275190</v>
+        <v>131275172</v>
       </c>
       <c r="B108" t="n">
-        <v>80365</v>
+        <v>80269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14305,10 +14305,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>546145</v>
+        <v>546223</v>
       </c>
       <c r="R108" t="n">
-        <v>6999134</v>
+        <v>6999048</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14343,11 +14343,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -14373,14 +14368,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -14398,32 +14388,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131275172</v>
+        <v>131275190</v>
       </c>
       <c r="B109" t="n">
-        <v>80269</v>
+        <v>80365</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14436,10 +14426,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>546223</v>
+        <v>546145</v>
       </c>
       <c r="R109" t="n">
-        <v>6999048</v>
+        <v>6999134</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14474,6 +14464,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -14499,9 +14494,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -14919,41 +14919,37 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131273363</v>
+        <v>131275167</v>
       </c>
       <c r="B113" t="n">
-        <v>92550</v>
+        <v>80231</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3298</v>
+        <v>388</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14961,10 +14957,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>546304</v>
+        <v>546468</v>
       </c>
       <c r="R113" t="n">
-        <v>6999379</v>
+        <v>6999037</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14999,11 +14995,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -15021,22 +15012,17 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -15054,10 +15040,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131273387</v>
+        <v>131273418</v>
       </c>
       <c r="B114" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15065,30 +15051,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15096,10 +15078,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>546286</v>
+        <v>546329</v>
       </c>
       <c r="R114" t="n">
-        <v>6999419</v>
+        <v>6999224</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15136,7 +15118,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15156,22 +15138,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15189,32 +15166,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275167</v>
+        <v>131275174</v>
       </c>
       <c r="B115" t="n">
-        <v>80231</v>
+        <v>75238</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>388</v>
+        <v>6428</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15227,10 +15204,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546468</v>
+        <v>546222</v>
       </c>
       <c r="R115" t="n">
-        <v>6999037</v>
+        <v>6999408</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15265,6 +15242,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15282,17 +15264,22 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15310,37 +15297,41 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273418</v>
+        <v>131273363</v>
       </c>
       <c r="B116" t="n">
-        <v>79260</v>
+        <v>92551</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -15348,10 +15339,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546329</v>
+        <v>546304</v>
       </c>
       <c r="R116" t="n">
-        <v>6999224</v>
+        <v>6999379</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15388,7 +15379,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15416,9 +15407,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15436,37 +15432,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275174</v>
+        <v>131275212</v>
       </c>
       <c r="B117" t="n">
-        <v>75238</v>
+        <v>91848</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Leight.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -15474,10 +15470,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546222</v>
+        <v>546213</v>
       </c>
       <c r="R117" t="n">
-        <v>6999408</v>
+        <v>6999022</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15512,11 +15508,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -15534,22 +15525,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15567,10 +15553,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131275212</v>
+        <v>131273387</v>
       </c>
       <c r="B118" t="n">
-        <v>91848</v>
+        <v>80365</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15578,24 +15564,28 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -15605,10 +15595,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546213</v>
+        <v>546286</v>
       </c>
       <c r="R118" t="n">
-        <v>6999022</v>
+        <v>6999419</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15643,6 +15633,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -15660,17 +15655,22 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131273385</v>
+        <v>131275216</v>
       </c>
       <c r="B120" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15829,30 +15829,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15860,10 +15856,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546261</v>
+        <v>546240</v>
       </c>
       <c r="R120" t="n">
-        <v>6999479</v>
+        <v>6999411</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15900,7 +15896,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>På en gammal sälg.</t>
+          <t>Rikligt med garnlav här.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15920,22 +15916,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15953,10 +15944,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131275216</v>
+        <v>131273385</v>
       </c>
       <c r="B121" t="n">
-        <v>79260</v>
+        <v>80365</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15964,26 +15955,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -15991,10 +15986,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>546240</v>
+        <v>546261</v>
       </c>
       <c r="R121" t="n">
-        <v>6999411</v>
+        <v>6999479</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16031,7 +16026,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -16051,17 +16046,22 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16596,32 +16596,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131275197</v>
+        <v>131275171</v>
       </c>
       <c r="B126" t="n">
-        <v>80365</v>
+        <v>80269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -16634,10 +16634,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>546130</v>
+        <v>546230</v>
       </c>
       <c r="R126" t="n">
-        <v>6999313</v>
+        <v>6999202</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16689,22 +16689,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -16722,32 +16717,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>131275171</v>
+        <v>131275197</v>
       </c>
       <c r="B127" t="n">
-        <v>80269</v>
+        <v>80365</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -16760,10 +16755,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>546230</v>
+        <v>546130</v>
       </c>
       <c r="R127" t="n">
-        <v>6999202</v>
+        <v>6999313</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16815,17 +16810,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -17229,10 +17229,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131273398</v>
+        <v>131273425</v>
       </c>
       <c r="B131" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17240,30 +17240,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -17271,10 +17267,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>546299</v>
+        <v>546106</v>
       </c>
       <c r="R131" t="n">
-        <v>6999243</v>
+        <v>6999416</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17311,7 +17307,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>På en flerstammig gammal sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17331,22 +17327,22 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -17364,10 +17360,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131275125</v>
+        <v>131275149</v>
       </c>
       <c r="B132" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17375,26 +17371,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -17402,10 +17403,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>546375</v>
+        <v>546120</v>
       </c>
       <c r="R132" t="n">
-        <v>6998987</v>
+        <v>6999185</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17440,13 +17441,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -17485,10 +17490,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131273411</v>
+        <v>131275125</v>
       </c>
       <c r="B133" t="n">
-        <v>79260</v>
+        <v>83240</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17496,21 +17501,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -17523,10 +17528,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>546421</v>
+        <v>546375</v>
       </c>
       <c r="R133" t="n">
-        <v>6999063</v>
+        <v>6998987</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17559,11 +17564,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17611,7 +17611,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131273425</v>
+        <v>131273411</v>
       </c>
       <c r="B134" t="n">
         <v>79260</v>
@@ -17649,10 +17649,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>546106</v>
+        <v>546421</v>
       </c>
       <c r="R134" t="n">
-        <v>6999416</v>
+        <v>6999063</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17717,14 +17717,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -17742,10 +17737,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131275149</v>
+        <v>131273398</v>
       </c>
       <c r="B135" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17753,29 +17748,28 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -17785,10 +17779,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>546120</v>
+        <v>546299</v>
       </c>
       <c r="R135" t="n">
-        <v>6999185</v>
+        <v>6999243</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17825,7 +17819,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en flerstammig gammal sälg.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17834,6 +17828,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -17844,17 +17839,22 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -18784,10 +18784,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>131275186</v>
+        <v>131275214</v>
       </c>
       <c r="B143" t="n">
-        <v>80365</v>
+        <v>79260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18795,21 +18795,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -18822,10 +18822,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>546206</v>
+        <v>546193</v>
       </c>
       <c r="R143" t="n">
-        <v>6999203</v>
+        <v>6999241</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -18860,11 +18860,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -18882,22 +18877,17 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
@@ -18915,10 +18905,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>131275214</v>
+        <v>131273367</v>
       </c>
       <c r="B144" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18926,26 +18916,31 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -18953,10 +18948,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>546193</v>
+        <v>546103</v>
       </c>
       <c r="R144" t="n">
-        <v>6999241</v>
+        <v>6999266</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18991,13 +18986,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -19016,9 +19015,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -19036,37 +19040,42 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131275210</v>
+        <v>131276480</v>
       </c>
       <c r="B145" t="n">
-        <v>80325</v>
+        <v>57898</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -19074,10 +19083,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>546168</v>
+        <v>546066</v>
       </c>
       <c r="R145" t="n">
-        <v>6999217</v>
+        <v>6999401</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -19112,13 +19121,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -19129,22 +19142,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -19162,10 +19170,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131276485</v>
+        <v>131276479</v>
       </c>
       <c r="B146" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19173,26 +19181,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -19200,10 +19213,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>546409</v>
+        <v>546062</v>
       </c>
       <c r="R146" t="n">
-        <v>6999005</v>
+        <v>6999415</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -19238,13 +19251,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -19255,22 +19272,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -19288,32 +19300,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>131275183</v>
+        <v>131275210</v>
       </c>
       <c r="B147" t="n">
-        <v>80365</v>
+        <v>80325</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19326,10 +19338,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>546345</v>
+        <v>546168</v>
       </c>
       <c r="R147" t="n">
-        <v>6999035</v>
+        <v>6999217</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -19377,6 +19389,26 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -19394,10 +19426,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131273367</v>
+        <v>131275186</v>
       </c>
       <c r="B148" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19405,31 +19437,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -19437,10 +19464,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>546103</v>
+        <v>546206</v>
       </c>
       <c r="R148" t="n">
-        <v>6999266</v>
+        <v>6999203</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -19477,7 +19504,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -19486,6 +19513,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -19496,22 +19524,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -19529,10 +19557,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>131276480</v>
+        <v>131276485</v>
       </c>
       <c r="B149" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -19540,31 +19568,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -19572,10 +19595,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>546066</v>
+        <v>546409</v>
       </c>
       <c r="R149" t="n">
-        <v>6999401</v>
+        <v>6999005</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -19610,17 +19633,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -19631,17 +19650,22 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -19659,10 +19683,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>131276479</v>
+        <v>131275183</v>
       </c>
       <c r="B150" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19670,31 +19694,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -19702,10 +19721,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>546062</v>
+        <v>546345</v>
       </c>
       <c r="R150" t="n">
-        <v>6999415</v>
+        <v>6999035</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -19740,38 +19759,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -19915,10 +19915,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>131273405</v>
+        <v>131275130</v>
       </c>
       <c r="B152" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19926,26 +19926,31 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -19953,10 +19958,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>546169</v>
+        <v>546460</v>
       </c>
       <c r="R152" t="n">
-        <v>6999410</v>
+        <v>6999069</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19993,7 +19998,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Enstaka bålar på asp.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -20002,7 +20007,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -20013,22 +20017,17 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr"/>
@@ -20313,10 +20312,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>131275130</v>
+        <v>131273405</v>
       </c>
       <c r="B155" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20324,31 +20323,26 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -20356,10 +20350,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>546460</v>
+        <v>546169</v>
       </c>
       <c r="R155" t="n">
-        <v>6999069</v>
+        <v>6999410</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -20396,7 +20390,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Enstaka bålar på asp.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -20405,6 +20399,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -20415,17 +20410,22 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -20574,10 +20574,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>131275141</v>
+        <v>131273403</v>
       </c>
       <c r="B157" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20585,31 +20585,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -20617,10 +20612,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>546148</v>
+        <v>546109</v>
       </c>
       <c r="R157" t="n">
-        <v>6999053</v>
+        <v>6999309</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -20657,7 +20652,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Lunglav på en liten gran.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -20666,6 +20661,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -20684,9 +20680,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -20704,10 +20705,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>131275162</v>
+        <v>131273400</v>
       </c>
       <c r="B158" t="n">
-        <v>57898</v>
+        <v>80365</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20715,31 +20716,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -20747,10 +20743,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>546103</v>
+        <v>546297</v>
       </c>
       <c r="R158" t="n">
-        <v>6999294</v>
+        <v>6999244</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -20787,7 +20783,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -20796,6 +20792,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -20806,17 +20803,22 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -20834,7 +20836,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>131275154</v>
+        <v>131275141</v>
       </c>
       <c r="B159" t="n">
         <v>57898</v>
@@ -20877,10 +20879,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>546118</v>
+        <v>546148</v>
       </c>
       <c r="R159" t="n">
-        <v>6999237</v>
+        <v>6999053</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -20964,7 +20966,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>131275157</v>
+        <v>131275162</v>
       </c>
       <c r="B160" t="n">
         <v>57898</v>
@@ -21007,10 +21009,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>546111</v>
+        <v>546103</v>
       </c>
       <c r="R160" t="n">
-        <v>6999255</v>
+        <v>6999294</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -21047,7 +21049,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -21094,10 +21096,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>131273403</v>
+        <v>131275154</v>
       </c>
       <c r="B161" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21105,26 +21107,31 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -21132,10 +21139,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>546109</v>
+        <v>546118</v>
       </c>
       <c r="R161" t="n">
-        <v>6999309</v>
+        <v>6999237</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -21172,7 +21179,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Lunglav på en liten gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21181,7 +21188,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -21200,14 +21206,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -21225,10 +21226,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>131273400</v>
+        <v>131275157</v>
       </c>
       <c r="B162" t="n">
-        <v>80365</v>
+        <v>57898</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21236,26 +21237,31 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -21263,10 +21269,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>546297</v>
+        <v>546111</v>
       </c>
       <c r="R162" t="n">
-        <v>6999244</v>
+        <v>6999255</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -21303,7 +21309,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21312,7 +21318,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -21323,22 +21328,17 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>

--- a/artfynd/A 50055-2025 artfynd.xlsx
+++ b/artfynd/A 50055-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131273413</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131273422</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131273378</v>
+        <v>131275215</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,31 +933,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546094</v>
+        <v>546164</v>
       </c>
       <c r="R4" t="n">
-        <v>6999329</v>
+        <v>6999199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,14 +1028,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131275145</v>
+        <v>131273397</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,31 +1059,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1100,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546148</v>
+        <v>546296</v>
       </c>
       <c r="R5" t="n">
-        <v>6999078</v>
+        <v>6999259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en lutande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1135,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1159,17 +1146,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131275160</v>
+        <v>131275180</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,31 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1230,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546104</v>
+        <v>546406</v>
       </c>
       <c r="R6" t="n">
-        <v>6999263</v>
+        <v>6999201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1270,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,6 +1266,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1289,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131276476</v>
+        <v>131275187</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1360,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546050</v>
+        <v>546202</v>
       </c>
       <c r="R7" t="n">
-        <v>6999453</v>
+        <v>6999223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1419,17 +1403,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1447,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131275215</v>
+        <v>131273378</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,26 +1442,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1485,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546164</v>
+        <v>546094</v>
       </c>
       <c r="R8" t="n">
-        <v>6999199</v>
+        <v>6999329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1525,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på gran.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1523,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1553,9 +1541,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1573,10 +1566,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131273397</v>
+        <v>131275145</v>
       </c>
       <c r="B9" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,26 +1577,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1611,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546296</v>
+        <v>546148</v>
       </c>
       <c r="R9" t="n">
-        <v>6999259</v>
+        <v>6999078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,7 +1649,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en lutande sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,7 +1658,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1671,22 +1668,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1704,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131275180</v>
+        <v>131275160</v>
       </c>
       <c r="B10" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,26 +1707,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1742,10 +1739,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546406</v>
+        <v>546104</v>
       </c>
       <c r="R10" t="n">
-        <v>6999201</v>
+        <v>6999263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1782,7 +1779,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,7 +1788,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1802,17 +1798,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1830,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131275187</v>
+        <v>131276476</v>
       </c>
       <c r="B11" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,26 +1837,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1868,10 +1869,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546202</v>
+        <v>546050</v>
       </c>
       <c r="R11" t="n">
-        <v>6999223</v>
+        <v>6999453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,7 +1918,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131273421</v>
+        <v>131273391</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1967,26 +1967,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1994,10 +1998,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546167</v>
+        <v>546459</v>
       </c>
       <c r="R12" t="n">
-        <v>6999264</v>
+        <v>6998921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2049,17 +2053,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2077,10 +2086,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131273391</v>
+        <v>131275185</v>
       </c>
       <c r="B13" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,11 +2116,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2119,10 +2124,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546230</v>
       </c>
       <c r="R13" t="n">
-        <v>6998921</v>
+        <v>6999202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,6 +2162,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2174,12 +2184,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2189,7 +2199,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,10 +2217,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131275185</v>
+        <v>131273407</v>
       </c>
       <c r="B14" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2237,7 +2247,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2245,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546230</v>
+        <v>546227</v>
       </c>
       <c r="R14" t="n">
-        <v>6999202</v>
+        <v>6999437</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,7 +2299,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,12 +2319,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2320,7 +2334,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2338,10 +2352,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131273407</v>
+        <v>131276484</v>
       </c>
       <c r="B15" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,11 +2382,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2380,10 +2390,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546227</v>
+        <v>546500</v>
       </c>
       <c r="R15" t="n">
-        <v>6999437</v>
+        <v>6998983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2416,11 +2426,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs minst 7 meter på en högväxt sälg. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2473,10 +2478,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131276484</v>
+        <v>131275184</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546500</v>
+        <v>546300</v>
       </c>
       <c r="R16" t="n">
-        <v>6998983</v>
+        <v>6999066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2562,26 +2567,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2599,10 +2584,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131275184</v>
+        <v>131273421</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,21 +2595,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2637,10 +2622,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546300</v>
+        <v>546167</v>
       </c>
       <c r="R17" t="n">
-        <v>6999066</v>
+        <v>6999264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2688,6 +2673,21 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
         <v>131275192</v>
       </c>
       <c r="B18" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>131273396</v>
       </c>
       <c r="B19" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131273375</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131275142</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131275131</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131275156</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131273368</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131275150</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>131275153</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>131275163</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131275176</v>
+        <v>131275206</v>
       </c>
       <c r="B28" t="n">
-        <v>75350</v>
+        <v>78273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1460</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546399</v>
+        <v>546408</v>
       </c>
       <c r="R28" t="n">
-        <v>6998994</v>
+        <v>6999129</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131275191</v>
+        <v>131275176</v>
       </c>
       <c r="B29" t="n">
-        <v>80365</v>
+        <v>75351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546174</v>
+        <v>546399</v>
       </c>
       <c r="R29" t="n">
-        <v>6999215</v>
+        <v>6998994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4218,11 +4218,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På asp.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4240,12 +4235,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4255,7 +4250,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4273,10 +4268,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131275201</v>
+        <v>131275175</v>
       </c>
       <c r="B30" t="n">
-        <v>80365</v>
+        <v>75351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4284,21 +4279,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4311,10 +4306,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546222</v>
+        <v>546372</v>
       </c>
       <c r="R30" t="n">
-        <v>6999418</v>
+        <v>6998999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4349,6 +4344,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark av gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131275178</v>
+        <v>131275191</v>
       </c>
       <c r="B31" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546403</v>
+        <v>546174</v>
       </c>
       <c r="R31" t="n">
-        <v>6999213</v>
+        <v>6999215</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4475,6 +4475,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asp.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4488,6 +4493,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4505,10 +4530,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131275206</v>
+        <v>131275201</v>
       </c>
       <c r="B32" t="n">
-        <v>78272</v>
+        <v>80366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4516,21 +4541,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4543,10 +4568,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546408</v>
+        <v>546222</v>
       </c>
       <c r="R32" t="n">
-        <v>6999129</v>
+        <v>6999418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4598,12 +4623,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4613,7 +4638,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4631,10 +4656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131275175</v>
+        <v>131275178</v>
       </c>
       <c r="B33" t="n">
-        <v>75350</v>
+        <v>80366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4642,21 +4667,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4669,10 +4694,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546372</v>
+        <v>546403</v>
       </c>
       <c r="R33" t="n">
-        <v>6998999</v>
+        <v>6999213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4707,11 +4732,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På bark av gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4725,26 +4745,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131273365</v>
+        <v>131276490</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4773,31 +4773,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4805,10 +4800,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546239</v>
+        <v>546070</v>
       </c>
       <c r="R34" t="n">
-        <v>6999263</v>
+        <v>6999377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4843,17 +4838,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4864,22 +4855,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4897,10 +4888,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131275146</v>
+        <v>131276489</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4908,31 +4899,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4940,10 +4926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546130</v>
+        <v>546065</v>
       </c>
       <c r="R35" t="n">
-        <v>6999093</v>
+        <v>6999434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4978,17 +4964,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4999,17 +4981,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5027,10 +5014,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131275152</v>
+        <v>131275193</v>
       </c>
       <c r="B36" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5038,31 +5025,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5070,10 +5052,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546122</v>
+        <v>546158</v>
       </c>
       <c r="R36" t="n">
-        <v>6999205</v>
+        <v>6999223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5110,7 +5092,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5119,6 +5101,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5129,17 +5112,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5157,10 +5145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131275155</v>
+        <v>131273389</v>
       </c>
       <c r="B37" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5168,42 +5156,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546116</v>
+        <v>546366</v>
       </c>
       <c r="R37" t="n">
-        <v>6999243</v>
+        <v>6999149</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5240,7 +5220,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Rikligt på en sälg. Fertil!</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5251,26 +5231,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5287,10 +5247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131276490</v>
+        <v>131276492</v>
       </c>
       <c r="B38" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5325,10 +5285,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546070</v>
+        <v>546097</v>
       </c>
       <c r="R38" t="n">
-        <v>6999377</v>
+        <v>6999346</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5413,10 +5373,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131276489</v>
+        <v>131273365</v>
       </c>
       <c r="B39" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5424,26 +5384,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5451,10 +5416,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546065</v>
+        <v>546239</v>
       </c>
       <c r="R39" t="n">
-        <v>6999434</v>
+        <v>6999263</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5489,13 +5454,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5506,22 +5475,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5539,10 +5508,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131275193</v>
+        <v>131275146</v>
       </c>
       <c r="B40" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5550,26 +5519,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5577,10 +5551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546158</v>
+        <v>546130</v>
       </c>
       <c r="R40" t="n">
-        <v>6999223</v>
+        <v>6999093</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5617,7 +5591,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5626,7 +5600,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5637,22 +5610,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5670,10 +5638,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131273389</v>
+        <v>131275152</v>
       </c>
       <c r="B41" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5681,34 +5649,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546366</v>
+        <v>546122</v>
       </c>
       <c r="R41" t="n">
-        <v>6999149</v>
+        <v>6999205</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5745,7 +5721,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på en sälg. Fertil!</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5756,6 +5732,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5772,10 +5768,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131276492</v>
+        <v>131275155</v>
       </c>
       <c r="B42" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5783,26 +5779,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5810,10 +5811,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546097</v>
+        <v>546116</v>
       </c>
       <c r="R42" t="n">
-        <v>6999346</v>
+        <v>6999243</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5848,13 +5849,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5865,22 +5870,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131273410</v>
+        <v>131273374</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5909,26 +5909,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5936,10 +5941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546342</v>
+        <v>546094</v>
       </c>
       <c r="R43" t="n">
-        <v>6999195</v>
+        <v>6999322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5974,13 +5979,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5999,9 +6008,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6019,10 +6033,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131273426</v>
+        <v>131275151</v>
       </c>
       <c r="B44" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6030,26 +6044,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6057,10 +6076,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546172</v>
+        <v>546124</v>
       </c>
       <c r="R44" t="n">
-        <v>6999385</v>
+        <v>6999206</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6097,7 +6116,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6106,7 +6125,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6145,10 +6163,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131275213</v>
+        <v>131275159</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6156,26 +6174,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6183,10 +6206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546481</v>
+        <v>546099</v>
       </c>
       <c r="R45" t="n">
-        <v>6998980</v>
+        <v>6999277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6221,13 +6244,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6266,10 +6293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131273374</v>
+        <v>131276478</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6309,10 +6336,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546094</v>
+        <v>546058</v>
       </c>
       <c r="R46" t="n">
-        <v>6999322</v>
+        <v>6999435</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6349,7 +6376,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran intill en björkhögstubbe vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6376,14 +6403,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6401,10 +6423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131275151</v>
+        <v>131275139</v>
       </c>
       <c r="B47" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6444,10 +6466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546124</v>
+        <v>546151</v>
       </c>
       <c r="R47" t="n">
-        <v>6999206</v>
+        <v>6999044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6531,10 +6553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131275159</v>
+        <v>131275182</v>
       </c>
       <c r="B48" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6542,31 +6564,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6574,10 +6591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546099</v>
+        <v>546357</v>
       </c>
       <c r="R48" t="n">
-        <v>6999277</v>
+        <v>6999022</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6612,38 +6629,19 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6661,10 +6659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131276478</v>
+        <v>131276487</v>
       </c>
       <c r="B49" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6672,31 +6670,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6704,10 +6697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546058</v>
+        <v>546313</v>
       </c>
       <c r="R49" t="n">
-        <v>6999435</v>
+        <v>6999060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6742,17 +6735,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6763,17 +6752,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6791,40 +6785,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131275139</v>
+        <v>131273381</v>
       </c>
       <c r="B50" t="n">
-        <v>57898</v>
+        <v>80395</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6834,10 +6827,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546151</v>
+        <v>546353</v>
       </c>
       <c r="R50" t="n">
-        <v>6999044</v>
+        <v>6999084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6874,7 +6867,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6883,6 +6876,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6893,17 +6887,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6921,10 +6920,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131275182</v>
+        <v>131275194</v>
       </c>
       <c r="B51" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6959,10 +6958,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>546357</v>
+        <v>546153</v>
       </c>
       <c r="R51" t="n">
-        <v>6999022</v>
+        <v>6999210</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6997,6 +6996,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7010,6 +7014,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7027,10 +7051,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131276487</v>
+        <v>131273410</v>
       </c>
       <c r="B52" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7038,21 +7062,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7065,10 +7089,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>546313</v>
+        <v>546342</v>
       </c>
       <c r="R52" t="n">
-        <v>6999060</v>
+        <v>6999195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7120,22 +7144,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7153,41 +7172,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131273381</v>
+        <v>131273426</v>
       </c>
       <c r="B53" t="n">
-        <v>80394</v>
+        <v>79261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7195,10 +7210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>546353</v>
+        <v>546172</v>
       </c>
       <c r="R53" t="n">
-        <v>6999084</v>
+        <v>6999385</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7235,7 +7250,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7255,22 +7270,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7288,10 +7298,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131275194</v>
+        <v>131273401</v>
       </c>
       <c r="B54" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7318,7 +7328,11 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7326,10 +7340,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>546153</v>
+        <v>546279</v>
       </c>
       <c r="R54" t="n">
-        <v>6999210</v>
+        <v>6999244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7366,7 +7380,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7386,12 +7400,12 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -7401,7 +7415,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7419,10 +7433,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131273401</v>
+        <v>131273406</v>
       </c>
       <c r="B55" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7449,11 +7463,7 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7461,10 +7471,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>546279</v>
+        <v>546223</v>
       </c>
       <c r="R55" t="n">
-        <v>6999244</v>
+        <v>6999436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7501,7 +7511,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en rakväxt grovbarkad sälg.</t>
+          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7521,22 +7531,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7554,10 +7564,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131273406</v>
+        <v>131275213</v>
       </c>
       <c r="B56" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7565,21 +7575,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7592,10 +7602,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>546223</v>
+        <v>546481</v>
       </c>
       <c r="R56" t="n">
-        <v>6999436</v>
+        <v>6998980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7630,11 +7640,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På en klen liten gran intill en sälg med rikligt av lunglav.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7660,14 +7665,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7685,10 +7685,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131273412</v>
+        <v>131275195</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7696,21 +7696,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>546441</v>
+        <v>546150</v>
       </c>
       <c r="R57" t="n">
-        <v>6999013</v>
+        <v>6999197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7778,17 +7778,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7806,10 +7811,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131275195</v>
+        <v>131273394</v>
       </c>
       <c r="B58" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7836,7 +7841,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7844,10 +7853,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>546150</v>
+        <v>546346</v>
       </c>
       <c r="R58" t="n">
-        <v>6999197</v>
+        <v>6999078</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7882,6 +7891,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertila bålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7899,12 +7913,12 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -7914,7 +7928,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7932,10 +7946,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131273394</v>
+        <v>131276488</v>
       </c>
       <c r="B59" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7962,11 +7976,7 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7974,10 +7984,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>546346</v>
+        <v>546062</v>
       </c>
       <c r="R59" t="n">
-        <v>6999078</v>
+        <v>6999441</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8010,11 +8020,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fertila bålar på sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8067,10 +8072,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131276488</v>
+        <v>131276491</v>
       </c>
       <c r="B60" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>546062</v>
+        <v>546074</v>
       </c>
       <c r="R60" t="n">
-        <v>6999441</v>
+        <v>6999366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8193,10 +8198,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131276491</v>
+        <v>131273412</v>
       </c>
       <c r="B61" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8204,21 +8209,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8231,10 +8236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>546074</v>
+        <v>546441</v>
       </c>
       <c r="R61" t="n">
-        <v>6999366</v>
+        <v>6999013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8286,22 +8291,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>131275129</v>
       </c>
       <c r="B62" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>131273373</v>
       </c>
       <c r="B63" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>131276475</v>
       </c>
       <c r="B64" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131273414</v>
+        <v>131273371</v>
       </c>
       <c r="B65" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8725,26 +8725,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8752,10 +8757,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>546430</v>
+        <v>546089</v>
       </c>
       <c r="R65" t="n">
-        <v>6998969</v>
+        <v>6999267</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8790,13 +8795,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8835,10 +8844,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131273420</v>
+        <v>131276481</v>
       </c>
       <c r="B66" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8846,26 +8855,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8873,10 +8887,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>546204</v>
+        <v>546070</v>
       </c>
       <c r="R66" t="n">
-        <v>6999267</v>
+        <v>6999374</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8913,7 +8927,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8922,7 +8936,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8961,10 +8974,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131275211</v>
+        <v>131273372</v>
       </c>
       <c r="B67" t="n">
-        <v>91848</v>
+        <v>57899</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8972,24 +8985,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8999,10 +9017,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>546185</v>
+        <v>546089</v>
       </c>
       <c r="R67" t="n">
-        <v>6999135</v>
+        <v>6999297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9037,13 +9055,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9062,9 +9084,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9082,10 +9109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131273416</v>
+        <v>131273420</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9120,10 +9147,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>546387</v>
+        <v>546204</v>
       </c>
       <c r="R68" t="n">
-        <v>6999068</v>
+        <v>6999267</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9160,7 +9187,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9208,10 +9235,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131275200</v>
+        <v>131273416</v>
       </c>
       <c r="B69" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9219,21 +9246,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9246,10 +9273,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>546174</v>
+        <v>546387</v>
       </c>
       <c r="R69" t="n">
-        <v>6999354</v>
+        <v>6999068</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9284,6 +9311,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9301,22 +9333,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9334,10 +9361,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131273384</v>
+        <v>131275200</v>
       </c>
       <c r="B70" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9363,16 +9390,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>546286</v>
+        <v>546174</v>
       </c>
       <c r="R70" t="n">
-        <v>6999257</v>
+        <v>6999354</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9407,19 +9437,40 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Fertil med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9436,10 +9487,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131273386</v>
+        <v>131273384</v>
       </c>
       <c r="B71" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9465,23 +9516,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjässmyrhöjden Väst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>546294</v>
+        <v>546286</v>
       </c>
       <c r="R71" t="n">
-        <v>6999434</v>
+        <v>6999257</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9518,7 +9562,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Fertil med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9527,34 +9571,8 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9571,10 +9589,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131273371</v>
+        <v>131273414</v>
       </c>
       <c r="B72" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9582,31 +9600,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9614,10 +9627,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>546089</v>
+        <v>546430</v>
       </c>
       <c r="R72" t="n">
-        <v>6999267</v>
+        <v>6998969</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9652,17 +9665,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gränssnitslad gran vid en hyggeskant. Snitslad av Rödins trä inom en avverkningsanmälan med aktivt revir för tretåig hackspett där ingen hänsyn är planerad för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9701,10 +9710,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131276481</v>
+        <v>131273386</v>
       </c>
       <c r="B73" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9712,29 +9721,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9744,10 +9752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>546070</v>
+        <v>546294</v>
       </c>
       <c r="R73" t="n">
-        <v>6999374</v>
+        <v>6999434</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9784,7 +9792,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9793,6 +9801,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9803,17 +9812,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9831,10 +9845,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131273372</v>
+        <v>131275211</v>
       </c>
       <c r="B74" t="n">
-        <v>57898</v>
+        <v>91849</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9842,29 +9856,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9874,10 +9883,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>546089</v>
+        <v>546185</v>
       </c>
       <c r="R74" t="n">
-        <v>6999297</v>
+        <v>6999135</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9912,17 +9921,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9941,14 +9946,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131275202</v>
+        <v>131276486</v>
       </c>
       <c r="B75" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10004,10 +10004,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>546230</v>
+        <v>546356</v>
       </c>
       <c r="R75" t="n">
-        <v>6999398</v>
+        <v>6999034</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10092,10 +10092,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131273402</v>
+        <v>131275181</v>
       </c>
       <c r="B76" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10130,10 +10130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>546159</v>
+        <v>546435</v>
       </c>
       <c r="R76" t="n">
-        <v>6999249</v>
+        <v>6999096</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10190,22 +10190,22 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131273392</v>
+        <v>131273393</v>
       </c>
       <c r="B77" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10253,7 +10253,11 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10261,10 +10265,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>546398</v>
+        <v>546394</v>
       </c>
       <c r="R77" t="n">
-        <v>6998976</v>
+        <v>6999043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10349,10 +10353,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131276486</v>
+        <v>131275202</v>
       </c>
       <c r="B78" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10387,10 +10391,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>546356</v>
+        <v>546230</v>
       </c>
       <c r="R78" t="n">
-        <v>6999034</v>
+        <v>6999398</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10475,10 +10479,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131275181</v>
+        <v>131273402</v>
       </c>
       <c r="B79" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10513,10 +10517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>546435</v>
+        <v>546159</v>
       </c>
       <c r="R79" t="n">
-        <v>6999096</v>
+        <v>6999249</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10553,7 +10557,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>Lunglav på en högstubbe av björk med 44 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10573,22 +10577,22 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10606,10 +10610,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131273393</v>
+        <v>131273392</v>
       </c>
       <c r="B80" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10636,11 +10640,7 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>546394</v>
+        <v>546398</v>
       </c>
       <c r="R80" t="n">
-        <v>6999043</v>
+        <v>6998976</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10739,7 +10739,7 @@
         <v>131276482</v>
       </c>
       <c r="B81" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>131275132</v>
       </c>
       <c r="B82" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>131275144</v>
       </c>
       <c r="B83" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>131275170</v>
       </c>
       <c r="B84" t="n">
-        <v>83231</v>
+        <v>83232</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131275161</v>
+        <v>131275204</v>
       </c>
       <c r="B85" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11265,31 +11265,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11297,10 +11292,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>546100</v>
+        <v>546244</v>
       </c>
       <c r="R85" t="n">
-        <v>6999276</v>
+        <v>6999418</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11335,17 +11330,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11356,17 +11347,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11384,10 +11380,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131275165</v>
+        <v>131276483</v>
       </c>
       <c r="B86" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11395,31 +11391,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11427,10 +11418,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>546098</v>
+        <v>546404</v>
       </c>
       <c r="R86" t="n">
-        <v>6999296</v>
+        <v>6999205</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11465,17 +11456,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11486,17 +11473,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11514,10 +11506,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131275164</v>
+        <v>131275205</v>
       </c>
       <c r="B87" t="n">
-        <v>57898</v>
+        <v>80366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11525,31 +11517,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11557,10 +11544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>546097</v>
+        <v>546149</v>
       </c>
       <c r="R87" t="n">
-        <v>6999287</v>
+        <v>6999093</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11595,17 +11582,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11616,17 +11599,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11644,10 +11632,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131275204</v>
+        <v>131273388</v>
       </c>
       <c r="B88" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11674,7 +11662,11 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11682,10 +11674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>546244</v>
+        <v>546370</v>
       </c>
       <c r="R88" t="n">
-        <v>6999418</v>
+        <v>6999140</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11720,6 +11712,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11752,7 +11749,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11770,10 +11767,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131276483</v>
+        <v>131275188</v>
       </c>
       <c r="B89" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11808,10 +11805,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>546404</v>
+        <v>546149</v>
       </c>
       <c r="R89" t="n">
-        <v>6999205</v>
+        <v>6999276</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11846,6 +11843,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -11863,22 +11865,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11896,10 +11893,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131275205</v>
+        <v>131275161</v>
       </c>
       <c r="B90" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11907,26 +11904,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11934,10 +11936,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>546149</v>
+        <v>546100</v>
       </c>
       <c r="R90" t="n">
-        <v>6999093</v>
+        <v>6999276</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11972,13 +11974,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11989,22 +11995,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12022,10 +12023,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131273388</v>
+        <v>131275165</v>
       </c>
       <c r="B91" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12033,28 +12034,29 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12064,10 +12066,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>546370</v>
+        <v>546098</v>
       </c>
       <c r="R91" t="n">
-        <v>6999140</v>
+        <v>6999296</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12104,7 +12106,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12113,7 +12115,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12124,22 +12125,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12157,10 +12153,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131275188</v>
+        <v>131275164</v>
       </c>
       <c r="B92" t="n">
-        <v>80365</v>
+        <v>57899</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12168,26 +12164,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12195,10 +12196,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>546149</v>
+        <v>546097</v>
       </c>
       <c r="R92" t="n">
-        <v>6999276</v>
+        <v>6999287</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12235,7 +12236,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12244,7 +12245,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12283,42 +12283,37 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131276477</v>
+        <v>131275209</v>
       </c>
       <c r="B93" t="n">
-        <v>57898</v>
+        <v>80326</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12326,10 +12321,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>546062</v>
+        <v>546171</v>
       </c>
       <c r="R93" t="n">
-        <v>6999442</v>
+        <v>6999219</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12364,17 +12359,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12385,17 +12376,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12413,10 +12409,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131275135</v>
+        <v>131276477</v>
       </c>
       <c r="B94" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12456,10 +12452,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>546142</v>
+        <v>546062</v>
       </c>
       <c r="R94" t="n">
-        <v>6999047</v>
+        <v>6999442</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12543,10 +12539,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131275158</v>
+        <v>131275135</v>
       </c>
       <c r="B95" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12586,10 +12582,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>546100</v>
+        <v>546142</v>
       </c>
       <c r="R95" t="n">
-        <v>6999268</v>
+        <v>6999047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12673,10 +12669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131273366</v>
+        <v>131275158</v>
       </c>
       <c r="B96" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12719,7 +12715,7 @@
         <v>546100</v>
       </c>
       <c r="R96" t="n">
-        <v>6999258</v>
+        <v>6999268</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12756,7 +12752,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12783,14 +12779,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12808,37 +12799,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131275209</v>
+        <v>131273366</v>
       </c>
       <c r="B97" t="n">
-        <v>80325</v>
+        <v>57899</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12846,10 +12842,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>546171</v>
+        <v>546100</v>
       </c>
       <c r="R97" t="n">
-        <v>6999219</v>
+        <v>6999258</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12884,13 +12880,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -12901,22 +12901,22 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
         <v>131275217</v>
       </c>
       <c r="B98" t="n">
-        <v>83227</v>
+        <v>83228</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>131273362</v>
       </c>
       <c r="B99" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>131273424</v>
       </c>
       <c r="B100" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13348,10 +13348,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131273419</v>
+        <v>131273409</v>
       </c>
       <c r="B101" t="n">
-        <v>79260</v>
+        <v>91849</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13359,26 +13359,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -13386,10 +13386,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>546230</v>
+        <v>546299</v>
       </c>
       <c r="R101" t="n">
-        <v>6999267</v>
+        <v>6999454</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
+          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -13454,19 +13454,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Flertalet granar.</t>
-        </is>
-      </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13484,10 +13479,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131273409</v>
+        <v>131273419</v>
       </c>
       <c r="B102" t="n">
-        <v>91848</v>
+        <v>79261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13495,26 +13490,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13522,10 +13517,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>546299</v>
+        <v>546230</v>
       </c>
       <c r="R102" t="n">
-        <v>6999454</v>
+        <v>6999267</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13562,7 +13557,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen granhögstubbe.</t>
+          <t>Rikligt med garnlav på flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13577,7 +13572,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13590,14 +13585,19 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
         <v>131273395</v>
       </c>
       <c r="B103" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13746,10 +13746,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131275207</v>
+        <v>131275137</v>
       </c>
       <c r="B104" t="n">
-        <v>78272</v>
+        <v>57899</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13757,26 +13757,31 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13784,10 +13789,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>546365</v>
+        <v>546139</v>
       </c>
       <c r="R104" t="n">
-        <v>6998993</v>
+        <v>6999047</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13822,13 +13827,17 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -13867,10 +13876,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131275137</v>
+        <v>131273380</v>
       </c>
       <c r="B105" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13910,10 +13919,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>546139</v>
+        <v>546091</v>
       </c>
       <c r="R105" t="n">
-        <v>6999047</v>
+        <v>6999334</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13950,7 +13959,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13977,9 +13986,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13997,10 +14011,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131273380</v>
+        <v>131273377</v>
       </c>
       <c r="B106" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,10 +14054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>546091</v>
+        <v>546077</v>
       </c>
       <c r="R106" t="n">
-        <v>6999334</v>
+        <v>6999352</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14080,7 +14094,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14132,10 +14146,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131273377</v>
+        <v>131275207</v>
       </c>
       <c r="B107" t="n">
-        <v>57898</v>
+        <v>78273</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14143,31 +14157,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14175,10 +14184,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>546077</v>
+        <v>546365</v>
       </c>
       <c r="R107" t="n">
-        <v>6999352</v>
+        <v>6998993</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14213,17 +14222,13 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -14242,14 +14247,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14270,7 +14270,7 @@
         <v>131275172</v>
       </c>
       <c r="B108" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>131275190</v>
       </c>
       <c r="B109" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>131275143</v>
       </c>
       <c r="B110" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>131273379</v>
       </c>
       <c r="B111" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>131273376</v>
       </c>
       <c r="B112" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>131275167</v>
       </c>
       <c r="B113" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>131273418</v>
       </c>
       <c r="B114" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15166,10 +15166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131275174</v>
+        <v>131273363</v>
       </c>
       <c r="B115" t="n">
-        <v>75238</v>
+        <v>92552</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15177,26 +15177,30 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6428</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15204,10 +15208,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>546222</v>
+        <v>546304</v>
       </c>
       <c r="R115" t="n">
-        <v>6999408</v>
+        <v>6999379</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15244,7 +15248,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15264,22 +15268,22 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -15297,34 +15301,30 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131273363</v>
+        <v>131275212</v>
       </c>
       <c r="B116" t="n">
-        <v>92551</v>
+        <v>91849</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>546304</v>
+        <v>546213</v>
       </c>
       <c r="R116" t="n">
-        <v>6999379</v>
+        <v>6999022</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15377,11 +15377,6 @@
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -15407,14 +15402,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -15432,10 +15422,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131275212</v>
+        <v>131273387</v>
       </c>
       <c r="B117" t="n">
-        <v>91848</v>
+        <v>80366</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15443,24 +15433,28 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15470,10 +15464,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>546213</v>
+        <v>546286</v>
       </c>
       <c r="R117" t="n">
-        <v>6999022</v>
+        <v>6999419</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15508,6 +15502,11 @@
           <t>2026-02-22</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -15525,17 +15524,22 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -15553,41 +15557,37 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131273387</v>
+        <v>131275174</v>
       </c>
       <c r="B118" t="n">
-        <v>80365</v>
+        <v>75239</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15595,10 +15595,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>546286</v>
+        <v>546222</v>
       </c>
       <c r="R118" t="n">
-        <v>6999419</v>
+        <v>6999408</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en klen sälg tätt intill en björk.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15691,7 +15691,7 @@
         <v>131275166</v>
       </c>
       <c r="B119" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15818,10 +15818,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131275216</v>
+        <v>131273385</v>
       </c>
       <c r="B120" t="n">
-        <v>79260</v>
+        <v>80366</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15829,26 +15829,30 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15856,10 +15860,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>546240</v>
+        <v>546261</v>
       </c>
       <c r="R120" t="n">
-        <v>6999411</v>
+        <v>6999479</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15896,7 +15900,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här.</t>
+          <t>På en gammal sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15916,17 +15920,22 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15944,10 +15953,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131273385</v>
+        <v>131275216</v>
       </c>
       <c r="B121" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D121" t="inlineStr">
  